--- a/Essity modell.xlsx
+++ b/Essity modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C600B6BD-87FD-1A46-AF8B-8185B819043B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECF6C5E-764E-9D47-94E3-04D2EB8DE757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25220" yWindow="520" windowWidth="25980" windowHeight="26740" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17200" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="218">
   <si>
     <t>Kapitalstruktur</t>
   </si>
@@ -638,9 +638,6 @@
     <t xml:space="preserve">Akkumelert kjøp </t>
   </si>
   <si>
-    <t>06.05.26: Essity initierer strategisk review ac consumer tissue business area. Review er antatt å ta 6-12 månender</t>
-  </si>
-  <si>
     <t>17.06.2024</t>
   </si>
   <si>
@@ -690,17 +687,48 @@
   </si>
   <si>
     <t>25.05.26: Essity kjøper tilbake 324 469 B-aksjer</t>
+  </si>
+  <si>
+    <t>01.06.26: Essity kjøper tilbake 311 814 B-aksjer</t>
+  </si>
+  <si>
+    <t>06.05.26: Essity initierer strategisk review av consumer tissue business area. Review er antatt å ta 6-12 månender</t>
+  </si>
+  <si>
+    <t>08.06.26: Essity kjøper tilbake 319 589 B-aksjer</t>
+  </si>
+  <si>
+    <t>15.06.26: Essity kjøper tilbake 307 819 B-aksjer</t>
+  </si>
+  <si>
+    <t>22.06.26: Essity kjøper tilbake 243 164 B-aksjer</t>
+  </si>
+  <si>
+    <t>29.06.26: Essity kjøper tilbake 294 782 B-aksjer</t>
+  </si>
+  <si>
+    <t>06.07.26: Essity kjøper tilbake 290 631 B-aksjer</t>
+  </si>
+  <si>
+    <t>EBITDA 26E</t>
+  </si>
+  <si>
+    <t>13.07.26: Essity kjøper tilbake 286 149 B-aksjer</t>
+  </si>
+  <si>
+    <t>Gearing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="8" formatCode="&quot;kr&quot;\ #,##0.00_);[Red]\(&quot;kr&quot;\ #,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="172" formatCode="0.0\ %"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -928,7 +956,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -981,7 +1009,6 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1008,6 +1035,19 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1844,7 +1884,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="940506" y="5405261"/>
+              <a:off x="940506" y="5583061"/>
               <a:ext cx="8464550" cy="5975349"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2215,2125 +2255,2185 @@
   <dimension ref="A1:AF92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="29" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="6" width="10.83203125" style="56"/>
-    <col min="7" max="7" width="18.83203125" style="56" customWidth="1"/>
-    <col min="8" max="17" width="10.83203125" style="56"/>
-    <col min="18" max="18" width="33.5" style="56" customWidth="1"/>
-    <col min="19" max="19" width="29.6640625" style="58" customWidth="1"/>
-    <col min="20" max="20" width="44.33203125" style="60" customWidth="1"/>
-    <col min="21" max="21" width="27.83203125" style="58" customWidth="1"/>
-    <col min="22" max="22" width="47.83203125" style="58" customWidth="1"/>
-    <col min="23" max="23" width="27.33203125" style="58" customWidth="1"/>
-    <col min="24" max="24" width="28" style="58" customWidth="1"/>
-    <col min="25" max="25" width="34.33203125" style="56" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.83203125" style="56" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="41.1640625" style="56" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.83203125" style="56" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="28.1640625" style="56" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="10.83203125" style="56"/>
-    <col min="32" max="32" width="22.6640625" style="56" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="10.83203125" style="56"/>
+    <col min="1" max="6" width="10.83203125" style="55"/>
+    <col min="7" max="7" width="18.83203125" style="55" customWidth="1"/>
+    <col min="8" max="17" width="10.83203125" style="55"/>
+    <col min="18" max="18" width="33.5" style="55" customWidth="1"/>
+    <col min="19" max="19" width="29.6640625" style="59" customWidth="1"/>
+    <col min="20" max="20" width="28.1640625" style="64" customWidth="1"/>
+    <col min="21" max="21" width="40.6640625" style="57" customWidth="1"/>
+    <col min="22" max="22" width="47.83203125" style="57" customWidth="1"/>
+    <col min="23" max="23" width="27.33203125" style="57" customWidth="1"/>
+    <col min="24" max="24" width="28" style="57" customWidth="1"/>
+    <col min="25" max="25" width="34.33203125" style="55" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.83203125" style="55" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="41.1640625" style="55" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.83203125" style="55" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="28.1640625" style="55" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="10.83203125" style="55"/>
+    <col min="32" max="32" width="22.6640625" style="55" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="10.83203125" style="55"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
+      <c r="W1" s="55"/>
+      <c r="X1" s="55"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
-      <c r="V2" s="56"/>
-      <c r="W2" s="56"/>
-      <c r="X2" s="56"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="55"/>
+      <c r="X2" s="55"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="S3" s="55" t="s">
+      <c r="S3" s="54" t="s">
         <v>185</v>
       </c>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="56"/>
-      <c r="X3" s="56"/>
-      <c r="Y3" s="55" t="s">
+      <c r="T3" s="55"/>
+      <c r="U3" s="55"/>
+      <c r="V3" s="55"/>
+      <c r="W3" s="55"/>
+      <c r="X3" s="55"/>
+      <c r="Y3" s="54" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="S4" s="62" t="s">
+      <c r="S4" s="61" t="s">
         <v>186</v>
       </c>
-      <c r="T4" s="62" t="s">
+      <c r="T4" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="U4" s="62" t="s">
+      <c r="U4" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="V4" s="62" t="s">
+      <c r="V4" s="61" t="s">
         <v>189</v>
       </c>
-      <c r="W4" s="62" t="s">
+      <c r="W4" s="61" t="s">
         <v>190</v>
       </c>
-      <c r="X4" s="56"/>
-      <c r="Y4" s="62" t="s">
+      <c r="X4" s="55"/>
+      <c r="Y4" s="61" t="s">
         <v>186</v>
       </c>
-      <c r="Z4" s="62" t="s">
+      <c r="Z4" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="AA4" s="62" t="s">
+      <c r="AA4" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="AB4" s="62" t="s">
+      <c r="AB4" s="61" t="s">
         <v>189</v>
       </c>
-      <c r="AC4" s="62" t="s">
+      <c r="AC4" s="61" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="S5" s="61">
+      <c r="A5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="S5" s="60">
         <v>46160</v>
       </c>
-      <c r="T5" s="58">
+      <c r="T5" s="57">
         <v>198501</v>
       </c>
-      <c r="U5" s="58">
+      <c r="U5" s="57">
         <f>T5</f>
         <v>198501</v>
       </c>
-      <c r="V5" s="58">
+      <c r="V5" s="57">
         <v>49255563</v>
       </c>
-      <c r="W5" s="58">
+      <c r="W5" s="57">
         <f>V5</f>
         <v>49255563</v>
       </c>
-      <c r="X5" s="56"/>
-      <c r="Y5" s="61" t="s">
-        <v>192</v>
-      </c>
-      <c r="Z5" s="58">
+      <c r="X5" s="55"/>
+      <c r="Y5" s="60" t="s">
+        <v>191</v>
+      </c>
+      <c r="Z5" s="57">
         <v>216000</v>
       </c>
-      <c r="AA5" s="58">
+      <c r="AA5" s="57">
         <v>216000</v>
       </c>
-      <c r="AB5" s="58">
+      <c r="AB5" s="57">
         <v>59463893</v>
       </c>
-      <c r="AC5" s="58">
+      <c r="AC5" s="57">
         <v>59463893</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A6" s="55"/>
-      <c r="S6" s="61">
+      <c r="A6" s="54"/>
+      <c r="S6" s="59">
         <v>46167</v>
       </c>
-      <c r="T6" s="58">
+      <c r="T6" s="57">
         <v>324469</v>
       </c>
-      <c r="U6" s="58">
+      <c r="U6" s="57">
         <f>SUM(T5:T6)</f>
         <v>522970</v>
       </c>
-      <c r="V6" s="58">
+      <c r="V6" s="57">
         <v>82497532</v>
       </c>
-      <c r="W6" s="58">
+      <c r="W6" s="57">
         <f>SUM(V5:V6)</f>
         <v>131753095</v>
       </c>
-      <c r="X6" s="56"/>
-      <c r="Y6" s="60">
+      <c r="X6" s="55"/>
+      <c r="Y6" s="59">
         <v>45474</v>
       </c>
-      <c r="Z6" s="58">
+      <c r="Z6" s="57">
         <v>270000</v>
       </c>
-      <c r="AA6" s="58">
+      <c r="AA6" s="57">
         <f>SUM(Z5:Z6)</f>
         <v>486000</v>
       </c>
-      <c r="AB6" s="58">
+      <c r="AB6" s="57">
         <v>74186113</v>
       </c>
-      <c r="AC6" s="58">
+      <c r="AC6" s="57">
         <f>SUM(AB5:AB6)</f>
         <v>133650006</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A7" s="55"/>
-      <c r="S7" s="60"/>
-      <c r="T7" s="58"/>
-      <c r="U7" s="58">
+      <c r="A7" s="54"/>
+      <c r="S7" s="59">
+        <v>46174</v>
+      </c>
+      <c r="T7" s="57">
+        <v>311814</v>
+      </c>
+      <c r="U7" s="57">
         <f>SUM(T5:T7)</f>
-        <v>522970</v>
-      </c>
-      <c r="W7" s="58">
+        <v>834784</v>
+      </c>
+      <c r="V7" s="57">
+        <v>81517876</v>
+      </c>
+      <c r="W7" s="57">
         <f>SUM(V5:V7)</f>
-        <v>131753095</v>
-      </c>
-      <c r="X7" s="56"/>
-      <c r="Y7" s="60">
+        <v>213270971</v>
+      </c>
+      <c r="X7" s="55"/>
+      <c r="Y7" s="59">
         <v>45481</v>
       </c>
-      <c r="Z7" s="58">
+      <c r="Z7" s="57">
         <v>270000</v>
       </c>
-      <c r="AA7" s="58">
+      <c r="AA7" s="57">
         <f>SUM(Z5:Z7)</f>
         <v>756000</v>
       </c>
-      <c r="AB7" s="58">
+      <c r="AB7" s="57">
         <v>74019641</v>
       </c>
-      <c r="AC7" s="58">
+      <c r="AC7" s="57">
         <f>SUM(AB5:AB7)</f>
         <v>207669647</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A8" s="55"/>
-      <c r="S8" s="60"/>
-      <c r="T8" s="58"/>
-      <c r="U8" s="58">
+      <c r="A8" s="54"/>
+      <c r="S8" s="59">
+        <v>46181</v>
+      </c>
+      <c r="T8" s="57">
+        <v>319589</v>
+      </c>
+      <c r="U8" s="57">
         <f>SUM(T5:T8)</f>
-        <v>522970</v>
-      </c>
-      <c r="W8" s="58">
+        <v>1154373</v>
+      </c>
+      <c r="V8" s="57">
+        <v>81966522</v>
+      </c>
+      <c r="W8" s="57">
         <f>SUM(V5:V8)</f>
-        <v>131753095</v>
-      </c>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="60">
+        <v>295237493</v>
+      </c>
+      <c r="X8" s="55"/>
+      <c r="Y8" s="59">
         <v>45488</v>
       </c>
-      <c r="Z8" s="58">
+      <c r="Z8" s="57">
         <v>270000</v>
       </c>
-      <c r="AA8" s="58">
+      <c r="AA8" s="57">
         <f>SUM(Z5:Z8)</f>
         <v>1026000</v>
       </c>
-      <c r="AB8" s="58">
+      <c r="AB8" s="57">
         <v>75127338</v>
       </c>
-      <c r="AC8" s="58">
+      <c r="AC8" s="57">
         <f>SUM(AB5:AB8)</f>
         <v>282796985</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="S9" s="60"/>
-      <c r="T9" s="58"/>
-      <c r="U9" s="58">
+      <c r="S9" s="59">
+        <v>46188</v>
+      </c>
+      <c r="T9" s="57">
+        <v>307819</v>
+      </c>
+      <c r="U9" s="57">
         <f>SUM(T$5:T9)</f>
-        <v>522970</v>
-      </c>
-      <c r="W9" s="58">
+        <v>1462192</v>
+      </c>
+      <c r="V9" s="57">
+        <v>80348681</v>
+      </c>
+      <c r="W9" s="57">
         <f>SUM(V$5:V9)</f>
-        <v>131753095</v>
-      </c>
-      <c r="Y9" s="60">
+        <v>375586174</v>
+      </c>
+      <c r="Y9" s="59">
         <v>45495</v>
       </c>
-      <c r="Z9" s="58">
+      <c r="Z9" s="57">
         <v>270000</v>
       </c>
-      <c r="AA9" s="58">
+      <c r="AA9" s="57">
         <f>SUM(Z$5:Z9)</f>
         <v>1296000</v>
       </c>
-      <c r="AB9" s="58">
+      <c r="AB9" s="57">
         <v>77475047</v>
       </c>
-      <c r="AC9" s="58">
+      <c r="AC9" s="57">
         <f>SUM(AB$5:AB9)</f>
         <v>360272032</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="S10" s="60"/>
-      <c r="T10" s="58"/>
-      <c r="U10" s="58">
+      <c r="S10" s="59">
+        <v>46195</v>
+      </c>
+      <c r="T10" s="57">
+        <v>243164</v>
+      </c>
+      <c r="U10" s="57">
         <f>SUM(T$5:T10)</f>
-        <v>522970</v>
-      </c>
-      <c r="W10" s="58">
+        <v>1705356</v>
+      </c>
+      <c r="V10" s="57">
+        <v>64724062</v>
+      </c>
+      <c r="W10" s="57">
         <f>SUM(V$5:V10)</f>
-        <v>131753095</v>
-      </c>
-      <c r="X10" s="56"/>
-      <c r="Y10" s="60">
+        <v>440310236</v>
+      </c>
+      <c r="X10" s="55"/>
+      <c r="Y10" s="59">
         <v>45502</v>
       </c>
-      <c r="Z10" s="58">
+      <c r="Z10" s="57">
         <v>270000</v>
       </c>
-      <c r="AA10" s="58">
+      <c r="AA10" s="57">
         <f>SUM(Z$5:Z10)</f>
         <v>1566000</v>
       </c>
-      <c r="AB10" s="58">
+      <c r="AB10" s="57">
         <v>82200820</v>
       </c>
-      <c r="AC10" s="58">
+      <c r="AC10" s="57">
         <f>SUM(AB$5:AB10)</f>
         <v>442472852</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="T11" s="56"/>
-      <c r="U11" s="56"/>
-      <c r="V11" s="56"/>
-      <c r="W11" s="56"/>
-      <c r="X11" s="56"/>
-      <c r="Y11" s="60">
+      <c r="S11" s="59">
+        <v>46202</v>
+      </c>
+      <c r="T11" s="57">
+        <v>294782</v>
+      </c>
+      <c r="U11" s="57">
+        <f>SUM(T5:T11)</f>
+        <v>2000138</v>
+      </c>
+      <c r="V11" s="57">
+        <v>80607860</v>
+      </c>
+      <c r="W11" s="57">
+        <f>SUM(V5:V11)</f>
+        <v>520918096</v>
+      </c>
+      <c r="X11" s="55"/>
+      <c r="Y11" s="59">
         <v>45509</v>
       </c>
-      <c r="Z11" s="58">
+      <c r="Z11" s="57">
         <v>270000</v>
       </c>
-      <c r="AA11" s="58">
+      <c r="AA11" s="57">
         <f>SUM(Z$5:Z11)</f>
         <v>1836000</v>
       </c>
-      <c r="AB11" s="58">
+      <c r="AB11" s="57">
         <v>81870529</v>
       </c>
-      <c r="AC11" s="58">
+      <c r="AC11" s="57">
         <f>SUM(AB$5:AB11)</f>
         <v>524343381</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="R12" s="57"/>
-      <c r="T12" s="56"/>
-      <c r="U12" s="56"/>
-      <c r="V12" s="56"/>
-      <c r="W12" s="56"/>
-      <c r="X12" s="56"/>
-      <c r="Y12" s="60">
+      <c r="R12" s="56"/>
+      <c r="S12" s="59">
+        <v>46209</v>
+      </c>
+      <c r="T12" s="57">
+        <v>290631</v>
+      </c>
+      <c r="U12" s="57">
+        <f>SUM(T5:T12)</f>
+        <v>2290769</v>
+      </c>
+      <c r="V12" s="57">
+        <v>80079360</v>
+      </c>
+      <c r="W12" s="57">
+        <f>SUM(V5:V12)</f>
+        <v>600997456</v>
+      </c>
+      <c r="X12" s="55"/>
+      <c r="Y12" s="59">
         <v>45516</v>
       </c>
-      <c r="Z12" s="58">
+      <c r="Z12" s="57">
         <v>270000</v>
       </c>
-      <c r="AA12" s="58">
+      <c r="AA12" s="57">
         <f>SUM(Z$5:Z12)</f>
         <v>2106000</v>
       </c>
-      <c r="AB12" s="58">
+      <c r="AB12" s="57">
         <v>81082015</v>
       </c>
-      <c r="AC12" s="58">
+      <c r="AC12" s="57">
         <f>SUM(AB$5:AB12)</f>
         <v>605425396</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="R13" s="57"/>
-      <c r="T13" s="56"/>
-      <c r="U13" s="56"/>
-      <c r="V13" s="56"/>
-      <c r="W13" s="56"/>
-      <c r="X13" s="56"/>
-      <c r="Y13" s="60">
+      <c r="R13" s="56"/>
+      <c r="S13" s="59">
+        <v>46216</v>
+      </c>
+      <c r="T13" s="57">
+        <v>286149</v>
+      </c>
+      <c r="U13" s="57">
+        <f>SUM(T5:T13)</f>
+        <v>2576918</v>
+      </c>
+      <c r="V13" s="57">
+        <v>79530196</v>
+      </c>
+      <c r="W13" s="57">
+        <f>SUM(V5:V13)</f>
+        <v>680527652</v>
+      </c>
+      <c r="X13" s="55"/>
+      <c r="Y13" s="59">
         <v>45523</v>
       </c>
-      <c r="Z13" s="58">
+      <c r="Z13" s="57">
         <v>270000</v>
       </c>
-      <c r="AA13" s="58">
+      <c r="AA13" s="57">
         <f>SUM(Z$5:Z13)</f>
         <v>2376000</v>
       </c>
-      <c r="AB13" s="58">
+      <c r="AB13" s="57">
         <v>80157875</v>
       </c>
-      <c r="AC13" s="58">
+      <c r="AC13" s="57">
         <f>SUM(AB$5:AB13)</f>
         <v>685583271</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y14" s="60">
+      <c r="Y14" s="59">
         <v>45530</v>
       </c>
-      <c r="Z14" s="58">
+      <c r="Z14" s="57">
         <v>270000</v>
       </c>
-      <c r="AA14" s="58">
+      <c r="AA14" s="57">
         <f>SUM(Z$5:Z14)</f>
         <v>2646000</v>
       </c>
-      <c r="AB14" s="58">
+      <c r="AB14" s="57">
         <v>80749121</v>
       </c>
-      <c r="AC14" s="58">
+      <c r="AC14" s="57">
         <f>SUM(AB$5:AB14)</f>
         <v>766332392</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y15" s="60">
+      <c r="Y15" s="59">
         <v>45537</v>
       </c>
-      <c r="Z15" s="58">
+      <c r="Z15" s="57">
         <v>270000</v>
       </c>
-      <c r="AA15" s="58">
+      <c r="AA15" s="57">
         <f>SUM(Z$5:Z15)</f>
         <v>2916000</v>
       </c>
-      <c r="AB15" s="58">
+      <c r="AB15" s="57">
         <v>82629245</v>
       </c>
-      <c r="AC15" s="58">
+      <c r="AC15" s="57">
         <f>SUM(AB$5:AB15)</f>
         <v>848961637</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y16" s="60">
+      <c r="Y16" s="59">
         <v>45544</v>
       </c>
-      <c r="Z16" s="58">
+      <c r="Z16" s="57">
         <v>270000</v>
       </c>
-      <c r="AA16" s="58">
+      <c r="AA16" s="57">
         <f>SUM(Z$5:Z16)</f>
         <v>3186000</v>
       </c>
-      <c r="AB16" s="58">
+      <c r="AB16" s="57">
         <v>84947821</v>
       </c>
-      <c r="AC16" s="58">
+      <c r="AC16" s="57">
         <f>SUM(AB$5:AB16)</f>
         <v>933909458</v>
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="55" t="s">
         <v>183</v>
       </c>
-      <c r="T17" s="56"/>
-      <c r="U17" s="56"/>
-      <c r="V17" s="56"/>
-      <c r="W17" s="56"/>
-      <c r="X17" s="56"/>
-      <c r="Y17" s="60">
+      <c r="T17" s="57"/>
+      <c r="U17" s="55"/>
+      <c r="W17" s="55"/>
+      <c r="X17" s="55"/>
+      <c r="Y17" s="59">
         <v>45551</v>
       </c>
-      <c r="Z17" s="58">
+      <c r="Z17" s="57">
         <v>270000</v>
       </c>
-      <c r="AA17" s="58">
+      <c r="AA17" s="57">
         <f>SUM(Z$5:Z17)</f>
         <v>3456000</v>
       </c>
-      <c r="AB17" s="58">
+      <c r="AB17" s="57">
         <v>86611468</v>
       </c>
-      <c r="AC17" s="58">
+      <c r="AC17" s="57">
         <f>SUM(AB$5:AB17)</f>
         <v>1020520926</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="55" t="s">
         <v>169</v>
       </c>
-      <c r="T18" s="56"/>
-      <c r="U18" s="56"/>
-      <c r="V18" s="56"/>
-      <c r="W18" s="56"/>
-      <c r="X18" s="56"/>
-      <c r="Y18" s="60">
+      <c r="T18" s="57"/>
+      <c r="U18" s="55"/>
+      <c r="W18" s="55"/>
+      <c r="X18" s="55"/>
+      <c r="Y18" s="59">
         <v>45558</v>
       </c>
-      <c r="Z18" s="58">
+      <c r="Z18" s="57">
         <v>270000</v>
       </c>
-      <c r="AA18" s="58">
+      <c r="AA18" s="57">
         <f>SUM(Z$5:Z18)</f>
         <v>3726000</v>
       </c>
-      <c r="AB18" s="58">
+      <c r="AB18" s="57">
         <v>86119643</v>
       </c>
-      <c r="AC18" s="58">
+      <c r="AC18" s="57">
         <f>SUM(AB$5:AB18)</f>
         <v>1106640569</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A19" s="56" t="s">
+      <c r="A19" s="55" t="s">
         <v>170</v>
       </c>
-      <c r="T19" s="56"/>
-      <c r="U19" s="56"/>
-      <c r="V19" s="56"/>
-      <c r="W19" s="56"/>
-      <c r="X19" s="56"/>
-      <c r="Y19" s="60">
+      <c r="T19" s="57"/>
+      <c r="U19" s="55"/>
+      <c r="W19" s="55"/>
+      <c r="X19" s="55"/>
+      <c r="Y19" s="59">
         <v>45565</v>
       </c>
-      <c r="Z19" s="58">
+      <c r="Z19" s="57">
         <v>270000</v>
       </c>
-      <c r="AA19" s="58">
+      <c r="AA19" s="57">
         <f>SUM(Z$5:Z19)</f>
         <v>3996000</v>
       </c>
-      <c r="AB19" s="58">
+      <c r="AB19" s="57">
         <v>84493061</v>
       </c>
-      <c r="AC19" s="58">
+      <c r="AC19" s="57">
         <f>SUM(AB$5:AB19)</f>
         <v>1191133630</v>
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="T20" s="56"/>
-      <c r="U20" s="56"/>
-      <c r="V20" s="56"/>
-      <c r="W20" s="56"/>
-      <c r="X20" s="56"/>
-      <c r="Y20" s="60">
+      <c r="T20" s="57"/>
+      <c r="U20" s="55"/>
+      <c r="W20" s="55"/>
+      <c r="X20" s="55"/>
+      <c r="Y20" s="59">
         <v>45572</v>
       </c>
-      <c r="Z20" s="58">
+      <c r="Z20" s="57">
         <v>270000</v>
       </c>
-      <c r="AA20" s="58">
+      <c r="AA20" s="57">
         <f>SUM(Z$5:Z20)</f>
         <v>4266000</v>
       </c>
-      <c r="AB20" s="58">
+      <c r="AB20" s="57">
         <v>84288913</v>
       </c>
-      <c r="AC20" s="58">
+      <c r="AC20" s="57">
         <f>SUM(AB$5:AB20)</f>
         <v>1275422543</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A21" s="56" t="s">
+      <c r="A21" s="55" t="s">
         <v>171</v>
       </c>
-      <c r="T21" s="56"/>
-      <c r="U21" s="56"/>
-      <c r="V21" s="56"/>
-      <c r="W21" s="56"/>
-      <c r="X21" s="56"/>
-      <c r="Y21" s="60">
+      <c r="T21" s="57"/>
+      <c r="U21" s="55"/>
+      <c r="W21" s="55"/>
+      <c r="X21" s="55"/>
+      <c r="Y21" s="59">
         <v>45579</v>
       </c>
-      <c r="Z21" s="58">
+      <c r="Z21" s="57">
         <v>270000</v>
       </c>
-      <c r="AA21" s="58">
+      <c r="AA21" s="57">
         <f>SUM(Z$5:Z21)</f>
         <v>4536000</v>
       </c>
-      <c r="AB21" s="58">
+      <c r="AB21" s="57">
         <v>83821137</v>
       </c>
-      <c r="AC21" s="58">
+      <c r="AC21" s="57">
         <f>SUM(AB$5:AB21)</f>
         <v>1359243680</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y22" s="60">
+      <c r="Y22" s="59">
         <v>45586</v>
       </c>
-      <c r="Z22" s="58">
+      <c r="Z22" s="57">
         <v>270000</v>
       </c>
-      <c r="AA22" s="58">
+      <c r="AA22" s="57">
         <f>SUM(Z$5:Z22)</f>
         <v>4806000</v>
       </c>
-      <c r="AB22" s="58">
+      <c r="AB22" s="57">
         <v>84946250</v>
       </c>
-      <c r="AC22" s="58">
+      <c r="AC22" s="57">
         <f>SUM(AB$5:AB22)</f>
         <v>1444189930</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y23" s="60">
+      <c r="Y23" s="59">
         <v>45593</v>
       </c>
-      <c r="Z23" s="58">
+      <c r="Z23" s="57">
         <v>270000</v>
       </c>
-      <c r="AA23" s="58">
+      <c r="AA23" s="57">
         <f>SUM(Z$5:Z23)</f>
         <v>5076000</v>
       </c>
-      <c r="AB23" s="58">
+      <c r="AB23" s="57">
         <v>83079383</v>
       </c>
-      <c r="AC23" s="58">
+      <c r="AC23" s="57">
         <f>SUM(AB$5:AB23)</f>
         <v>1527269313</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y24" s="60">
+      <c r="Y24" s="59">
         <v>45600</v>
       </c>
-      <c r="Z24" s="58">
+      <c r="Z24" s="57">
         <v>270000</v>
       </c>
-      <c r="AA24" s="58">
+      <c r="AA24" s="57">
         <f>SUM(Z$5:Z24)</f>
         <v>5346000</v>
       </c>
-      <c r="AB24" s="58">
+      <c r="AB24" s="57">
         <v>82374273</v>
       </c>
-      <c r="AC24" s="58">
+      <c r="AC24" s="57">
         <f>SUM(AB$5:AB24)</f>
         <v>1609643586</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y25" s="60">
+      <c r="Y25" s="59">
         <v>45607</v>
       </c>
-      <c r="Z25" s="58">
+      <c r="Z25" s="57">
         <v>270000</v>
       </c>
-      <c r="AA25" s="58">
+      <c r="AA25" s="57">
         <f>SUM(Z$5:Z25)</f>
         <v>5616000</v>
       </c>
-      <c r="AB25" s="58">
+      <c r="AB25" s="57">
         <v>80715398</v>
       </c>
-      <c r="AC25" s="58">
+      <c r="AC25" s="57">
         <f>SUM(AB$5:AB25)</f>
         <v>1690358984</v>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y26" s="60">
+      <c r="Y26" s="59">
         <v>45614</v>
       </c>
-      <c r="Z26" s="58">
+      <c r="Z26" s="57">
         <v>270000</v>
       </c>
-      <c r="AA26" s="58">
+      <c r="AA26" s="57">
         <f>SUM(Z$5:Z26)</f>
         <v>5886000</v>
       </c>
-      <c r="AB26" s="58">
+      <c r="AB26" s="57">
         <v>79988175</v>
       </c>
-      <c r="AC26" s="58">
+      <c r="AC26" s="57">
         <f>SUM(AB$5:AB26)</f>
         <v>1770347159</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A27" s="55" t="s">
+      <c r="A27" s="54" t="s">
         <v>153</v>
       </c>
-      <c r="T27" s="56"/>
-      <c r="U27" s="56"/>
-      <c r="V27" s="56"/>
-      <c r="W27" s="56"/>
-      <c r="X27" s="56"/>
-      <c r="Y27" s="60">
+      <c r="T27" s="57"/>
+      <c r="U27" s="55"/>
+      <c r="W27" s="55"/>
+      <c r="X27" s="55"/>
+      <c r="Y27" s="59">
         <v>45621</v>
       </c>
-      <c r="Z27" s="58">
+      <c r="Z27" s="57">
         <v>270000</v>
       </c>
-      <c r="AA27" s="58">
+      <c r="AA27" s="57">
         <f>SUM(Z$5:Z27)</f>
         <v>6156000</v>
       </c>
-      <c r="AB27" s="58">
+      <c r="AB27" s="57">
         <v>80358809</v>
       </c>
-      <c r="AC27" s="58">
+      <c r="AC27" s="57">
         <f>SUM(AB$5:AB27)</f>
         <v>1850705968</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A28" s="56" t="s">
-        <v>208</v>
-      </c>
-      <c r="Y28" s="60">
+      <c r="A28" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="Y28" s="59">
         <v>45628</v>
       </c>
-      <c r="Z28" s="58">
+      <c r="Z28" s="57">
         <v>270000</v>
       </c>
-      <c r="AA28" s="58">
+      <c r="AA28" s="57">
         <f>SUM(Z$5:Z28)</f>
         <v>6426000</v>
       </c>
-      <c r="AB28" s="58">
+      <c r="AB28" s="57">
         <v>81613618</v>
       </c>
-      <c r="AC28" s="58">
+      <c r="AC28" s="57">
         <f>SUM(AB$5:AB28)</f>
         <v>1932319586</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A29" s="56" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y29" s="60">
+      <c r="A29" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="Y29" s="59">
         <v>45635</v>
       </c>
-      <c r="Z29" s="58">
+      <c r="Z29" s="57">
         <v>270000</v>
       </c>
-      <c r="AA29" s="58">
+      <c r="AA29" s="57">
         <f>SUM(Z$5:Z29)</f>
         <v>6696000</v>
       </c>
-      <c r="AB29" s="58">
+      <c r="AB29" s="57">
         <v>82481640</v>
       </c>
-      <c r="AC29" s="58">
+      <c r="AC29" s="57">
         <f>SUM(AB$5:AB29)</f>
         <v>2014801226</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A30" s="56" t="s">
-        <v>206</v>
-      </c>
-      <c r="T30" s="56"/>
-      <c r="U30" s="56"/>
-      <c r="V30" s="56"/>
-      <c r="W30" s="56"/>
-      <c r="X30" s="56"/>
-      <c r="Y30" s="60">
+      <c r="A30" s="55" t="s">
+        <v>213</v>
+      </c>
+      <c r="T30" s="57"/>
+      <c r="U30" s="55"/>
+      <c r="W30" s="55"/>
+      <c r="X30" s="55"/>
+      <c r="Y30" s="59">
         <v>45642</v>
       </c>
-      <c r="Z30" s="58">
+      <c r="Z30" s="57">
         <v>270000</v>
       </c>
-      <c r="AA30" s="58">
+      <c r="AA30" s="57">
         <f>SUM(Z$5:Z30)</f>
         <v>6966000</v>
       </c>
-      <c r="AB30" s="58">
+      <c r="AB30" s="57">
         <v>81340945</v>
       </c>
-      <c r="AC30" s="58">
+      <c r="AC30" s="57">
         <f>SUM(AB$5:AB30)</f>
         <v>2096142171</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A31" s="56" t="s">
-        <v>191</v>
-      </c>
-      <c r="T31" s="56"/>
-      <c r="U31" s="56"/>
-      <c r="V31" s="56"/>
-      <c r="W31" s="56"/>
-      <c r="X31" s="56"/>
-      <c r="Y31" s="60">
+      <c r="A31" s="55" t="s">
+        <v>212</v>
+      </c>
+      <c r="T31" s="57"/>
+      <c r="U31" s="55"/>
+      <c r="W31" s="55"/>
+      <c r="X31" s="55"/>
+      <c r="Y31" s="59">
         <v>45649</v>
       </c>
-      <c r="Z31" s="58">
+      <c r="Z31" s="57">
         <v>270000</v>
       </c>
-      <c r="AA31" s="58">
+      <c r="AA31" s="57">
         <f>SUM(Z$5:Z31)</f>
         <v>7236000</v>
       </c>
-      <c r="AB31" s="58">
+      <c r="AB31" s="57">
         <v>79849222</v>
       </c>
-      <c r="AC31" s="58">
+      <c r="AC31" s="57">
         <f>SUM(AB$5:AB31)</f>
         <v>2175991393</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A32" s="56" t="s">
-        <v>179</v>
-      </c>
-      <c r="T32" s="56"/>
-      <c r="U32" s="56"/>
-      <c r="V32" s="56"/>
-      <c r="W32" s="56"/>
-      <c r="X32" s="56"/>
-      <c r="Y32" s="63">
+      <c r="A32" s="55" t="s">
+        <v>211</v>
+      </c>
+      <c r="T32" s="57"/>
+      <c r="U32" s="55"/>
+      <c r="W32" s="55"/>
+      <c r="X32" s="55"/>
+      <c r="Y32" s="62">
         <v>45656</v>
       </c>
-      <c r="Z32" s="64">
+      <c r="Z32" s="63">
         <v>108000</v>
       </c>
-      <c r="AA32" s="64">
+      <c r="AA32" s="63">
         <f>SUM(Z$5:Z32)</f>
         <v>7344000</v>
       </c>
-      <c r="AB32" s="64">
+      <c r="AB32" s="63">
         <v>31795043</v>
       </c>
-      <c r="AC32" s="64">
+      <c r="AC32" s="63">
         <f>SUM(AB$5:AB32)</f>
         <v>2207786436</v>
       </c>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A33" s="56" t="s">
-        <v>193</v>
-      </c>
-      <c r="T33" s="56"/>
-      <c r="U33" s="56"/>
-      <c r="V33" s="56"/>
-      <c r="W33" s="56"/>
-      <c r="X33" s="56"/>
-      <c r="Y33" s="60">
+      <c r="A33" s="55" t="s">
+        <v>210</v>
+      </c>
+      <c r="T33" s="57"/>
+      <c r="U33" s="55"/>
+      <c r="W33" s="55"/>
+      <c r="X33" s="55"/>
+      <c r="Y33" s="59">
         <v>45663</v>
       </c>
-      <c r="Z33" s="58">
+      <c r="Z33" s="57">
         <v>162000</v>
       </c>
-      <c r="AA33" s="58">
+      <c r="AA33" s="57">
         <f>SUM(Z$5:Z33)</f>
         <v>7506000</v>
       </c>
-      <c r="AB33" s="58">
+      <c r="AB33" s="57">
         <v>48012756</v>
       </c>
-      <c r="AC33" s="58">
+      <c r="AC33" s="57">
         <f>SUM(AB$5:AB33)</f>
         <v>2255799192</v>
       </c>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A34" s="56" t="s">
-        <v>177</v>
-      </c>
-      <c r="T34" s="56"/>
-      <c r="U34" s="56"/>
-      <c r="V34" s="56"/>
-      <c r="W34" s="56"/>
-      <c r="X34" s="56"/>
-      <c r="Y34" s="60">
+      <c r="A34" s="55" t="s">
+        <v>208</v>
+      </c>
+      <c r="T34" s="57"/>
+      <c r="U34" s="55"/>
+      <c r="W34" s="55"/>
+      <c r="X34" s="55"/>
+      <c r="Y34" s="59">
         <v>45670</v>
       </c>
-      <c r="Z34" s="58">
+      <c r="Z34" s="57">
         <v>216000</v>
       </c>
-      <c r="AA34" s="58">
+      <c r="AA34" s="57">
         <f>SUM(Z$5:Z34)</f>
         <v>7722000</v>
       </c>
-      <c r="AB34" s="58">
+      <c r="AB34" s="57">
         <v>63849681</v>
       </c>
-      <c r="AC34" s="58">
+      <c r="AC34" s="57">
         <f>SUM(AB$5:AB34)</f>
         <v>2319648873</v>
       </c>
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A35" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="T35" s="56"/>
-      <c r="U35" s="56"/>
-      <c r="V35" s="56"/>
-      <c r="W35" s="56"/>
-      <c r="X35" s="56"/>
-      <c r="Y35" s="60">
+      <c r="A35" s="55" t="s">
+        <v>207</v>
+      </c>
+      <c r="T35" s="57"/>
+      <c r="U35" s="55"/>
+      <c r="W35" s="55"/>
+      <c r="X35" s="55"/>
+      <c r="Y35" s="59">
         <v>45677</v>
       </c>
-      <c r="Z35" s="58">
+      <c r="Z35" s="57">
         <v>216000</v>
       </c>
-      <c r="AA35" s="58">
+      <c r="AA35" s="57">
         <f>SUM(Z$5:Z35)</f>
         <v>7938000</v>
       </c>
-      <c r="AB35" s="58">
+      <c r="AB35" s="57">
         <v>63849681</v>
       </c>
-      <c r="AC35" s="58">
+      <c r="AC35" s="57">
         <f>SUM(AB$5:AB35)</f>
         <v>2383498554</v>
       </c>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A36" s="56" t="s">
-        <v>178</v>
-      </c>
-      <c r="T36" s="56"/>
-      <c r="U36" s="56"/>
-      <c r="V36" s="56"/>
-      <c r="W36" s="56"/>
-      <c r="X36" s="56"/>
-      <c r="Y36" s="60">
+      <c r="A36" s="55" t="s">
+        <v>206</v>
+      </c>
+      <c r="T36" s="57"/>
+      <c r="U36" s="55"/>
+      <c r="W36" s="55"/>
+      <c r="X36" s="55"/>
+      <c r="Y36" s="59">
         <v>45684</v>
       </c>
-      <c r="Z36" s="58">
+      <c r="Z36" s="57">
         <v>270000</v>
       </c>
-      <c r="AA36" s="58">
+      <c r="AA36" s="57">
         <f>SUM(Z$5:Z36)</f>
         <v>8208000</v>
       </c>
-      <c r="AB36" s="58">
+      <c r="AB36" s="57">
         <v>78829384</v>
       </c>
-      <c r="AC36" s="58">
+      <c r="AC36" s="57">
         <f>SUM(AB$5:AB36)</f>
         <v>2462327938</v>
       </c>
-      <c r="AF36" s="58"/>
+      <c r="AF36" s="57"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A37" s="56" t="s">
-        <v>175</v>
-      </c>
-      <c r="T37" s="56"/>
-      <c r="U37" s="56"/>
-      <c r="V37" s="56"/>
-      <c r="W37" s="56"/>
-      <c r="X37" s="56"/>
-      <c r="Y37" s="60">
+      <c r="A37" s="55" t="s">
+        <v>205</v>
+      </c>
+      <c r="T37" s="57"/>
+      <c r="U37" s="55"/>
+      <c r="W37" s="55"/>
+      <c r="X37" s="55"/>
+      <c r="Y37" s="59">
         <v>45691</v>
       </c>
-      <c r="Z37" s="58">
+      <c r="Z37" s="57">
         <v>270000</v>
       </c>
-      <c r="AA37" s="58">
+      <c r="AA37" s="57">
         <f>SUM(Z$5:Z37)</f>
         <v>8478000</v>
       </c>
-      <c r="AB37" s="58">
+      <c r="AB37" s="57">
         <v>76193460</v>
       </c>
-      <c r="AC37" s="58">
+      <c r="AC37" s="57">
         <f>SUM(AB$5:AB37)</f>
         <v>2538521398</v>
       </c>
-      <c r="AF37" s="58"/>
+      <c r="AF37" s="57"/>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A38" s="56" t="s">
-        <v>174</v>
-      </c>
-      <c r="T38" s="56"/>
-      <c r="U38" s="56"/>
-      <c r="V38" s="56"/>
-      <c r="W38" s="56"/>
-      <c r="X38" s="56"/>
-      <c r="Y38" s="60">
+      <c r="A38" s="55" t="s">
+        <v>209</v>
+      </c>
+      <c r="T38" s="57"/>
+      <c r="U38" s="55"/>
+      <c r="W38" s="55"/>
+      <c r="X38" s="55"/>
+      <c r="Y38" s="59">
         <v>45698</v>
       </c>
-      <c r="Z38" s="58">
+      <c r="Z38" s="57">
         <v>270000</v>
       </c>
-      <c r="AA38" s="58">
+      <c r="AA38" s="57">
         <f>SUM(Z$5:Z38)</f>
         <v>8748000</v>
       </c>
-      <c r="AB38" s="58">
+      <c r="AB38" s="57">
         <v>74747842</v>
       </c>
-      <c r="AC38" s="58">
+      <c r="AC38" s="57">
         <f>SUM(AB$5:AB38)</f>
         <v>2613269240</v>
       </c>
-      <c r="AF38" s="58"/>
+      <c r="AF38" s="57"/>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A39" s="56" t="s">
-        <v>172</v>
-      </c>
-      <c r="T39" s="56"/>
-      <c r="U39" s="56"/>
-      <c r="V39" s="56"/>
-      <c r="W39" s="56"/>
-      <c r="X39" s="56"/>
-      <c r="Y39" s="60">
+      <c r="A39" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="T39" s="57"/>
+      <c r="U39" s="55"/>
+      <c r="W39" s="55"/>
+      <c r="X39" s="55"/>
+      <c r="Y39" s="59">
         <v>45705</v>
       </c>
-      <c r="Z39" s="58">
+      <c r="Z39" s="57">
         <v>270000</v>
       </c>
-      <c r="AA39" s="58">
+      <c r="AA39" s="57">
         <f>SUM(Z$5:Z39)</f>
         <v>9018000</v>
       </c>
-      <c r="AB39" s="58">
+      <c r="AB39" s="57">
         <v>75819456</v>
       </c>
-      <c r="AC39" s="58">
+      <c r="AC39" s="57">
         <f>SUM(AB$5:AB39)</f>
         <v>2689088696</v>
       </c>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A40" s="56" t="s">
-        <v>173</v>
-      </c>
-      <c r="T40" s="56"/>
-      <c r="U40" s="56"/>
-      <c r="V40" s="56"/>
-      <c r="W40" s="56"/>
-      <c r="X40" s="56"/>
-      <c r="Y40" s="60">
+      <c r="A40" s="55" t="s">
+        <v>192</v>
+      </c>
+      <c r="T40" s="57"/>
+      <c r="U40" s="55"/>
+      <c r="W40" s="55"/>
+      <c r="X40" s="55"/>
+      <c r="Y40" s="59">
         <v>45712</v>
       </c>
-      <c r="Z40" s="58">
+      <c r="Z40" s="57">
         <v>270000</v>
       </c>
-      <c r="AA40" s="58">
+      <c r="AA40" s="57">
         <f>SUM(Z$5:Z40)</f>
         <v>9288000</v>
       </c>
-      <c r="AB40" s="58">
+      <c r="AB40" s="57">
         <v>76940674</v>
       </c>
-      <c r="AC40" s="58">
+      <c r="AC40" s="57">
         <f>SUM(AB$5:AB40)</f>
         <v>2766029370</v>
       </c>
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A41" s="56" t="s">
-        <v>154</v>
-      </c>
-      <c r="T41" s="56"/>
-      <c r="U41" s="56"/>
-      <c r="V41" s="56"/>
-      <c r="W41" s="56"/>
-      <c r="X41" s="56"/>
-      <c r="Y41" s="60">
+      <c r="A41" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="T41" s="57"/>
+      <c r="U41" s="55"/>
+      <c r="W41" s="55"/>
+      <c r="X41" s="55"/>
+      <c r="Y41" s="59">
         <v>45719</v>
       </c>
-      <c r="Z41" s="58">
+      <c r="Z41" s="57">
         <v>270000</v>
       </c>
-      <c r="AA41" s="58">
+      <c r="AA41" s="57">
         <f>SUM(Z5:Z41)</f>
         <v>9558000</v>
       </c>
-      <c r="AB41" s="58">
+      <c r="AB41" s="57">
         <v>79742497</v>
       </c>
-      <c r="AC41" s="58">
+      <c r="AC41" s="57">
         <f>SUM(AB5:AB41)</f>
         <v>2845771867</v>
       </c>
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A42" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="T42" s="56"/>
-      <c r="U42" s="56"/>
-      <c r="V42" s="56"/>
-      <c r="W42" s="56"/>
-      <c r="X42" s="56"/>
-      <c r="Y42" s="60">
+      <c r="A42" s="55" t="s">
+        <v>176</v>
+      </c>
+      <c r="T42" s="57"/>
+      <c r="U42" s="55"/>
+      <c r="W42" s="55"/>
+      <c r="X42" s="55"/>
+      <c r="Y42" s="59">
         <v>45726</v>
       </c>
-      <c r="Z42" s="58">
+      <c r="Z42" s="57">
         <v>270000</v>
       </c>
-      <c r="AA42" s="58">
+      <c r="AA42" s="57">
         <f>SUM(Z5:Z42)</f>
         <v>9828000</v>
       </c>
-      <c r="AB42" s="58">
+      <c r="AB42" s="57">
         <v>81121565</v>
       </c>
-      <c r="AC42" s="58">
+      <c r="AC42" s="57">
         <f>SUM(AB5:AB42)</f>
         <v>2926893432</v>
       </c>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A43" s="56" t="s">
-        <v>158</v>
-      </c>
-      <c r="T43" s="56"/>
-      <c r="U43" s="56"/>
-      <c r="V43" s="56"/>
-      <c r="W43" s="56"/>
-      <c r="X43" s="56"/>
-      <c r="Y43" s="61">
+      <c r="A43" s="55" t="s">
+        <v>178</v>
+      </c>
+      <c r="T43" s="57"/>
+      <c r="U43" s="55"/>
+      <c r="W43" s="55"/>
+      <c r="X43" s="55"/>
+      <c r="Y43" s="60">
         <v>45733</v>
       </c>
-      <c r="Z43" s="58">
+      <c r="Z43" s="57">
         <v>188500</v>
       </c>
-      <c r="AA43" s="58">
+      <c r="AA43" s="57">
         <f>SUM(Z5:Z43)</f>
         <v>10016500</v>
       </c>
-      <c r="AB43" s="58">
+      <c r="AB43" s="57">
         <v>57682239</v>
       </c>
-      <c r="AC43" s="58">
+      <c r="AC43" s="57">
         <f>SUM(AB5:AB43)</f>
         <v>2984575671</v>
       </c>
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A44" s="56" t="s">
-        <v>159</v>
-      </c>
-      <c r="T44" s="56"/>
-      <c r="U44" s="56"/>
-      <c r="V44" s="56"/>
-      <c r="W44" s="56"/>
-      <c r="X44" s="56"/>
-      <c r="Y44" s="62" t="s">
+      <c r="A44" s="55" t="s">
+        <v>175</v>
+      </c>
+      <c r="T44" s="57"/>
+      <c r="U44" s="55"/>
+      <c r="W44" s="55"/>
+      <c r="X44" s="55"/>
+      <c r="Y44" s="61" t="s">
         <v>186</v>
       </c>
-      <c r="Z44" s="62" t="s">
+      <c r="Z44" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="AA44" s="62" t="s">
+      <c r="AA44" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="AB44" s="62" t="s">
+      <c r="AB44" s="61" t="s">
         <v>189</v>
       </c>
-      <c r="AC44" s="62" t="s">
+      <c r="AC44" s="61" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A45" s="56" t="s">
-        <v>160</v>
-      </c>
-      <c r="T45" s="56"/>
-      <c r="U45" s="56"/>
-      <c r="V45" s="56"/>
-      <c r="W45" s="56"/>
-      <c r="X45" s="56"/>
-      <c r="Y45" s="61">
+      <c r="A45" s="55" t="s">
+        <v>174</v>
+      </c>
+      <c r="T45" s="57"/>
+      <c r="U45" s="55"/>
+      <c r="W45" s="55"/>
+      <c r="X45" s="55"/>
+      <c r="Y45" s="60">
         <v>45775</v>
       </c>
-      <c r="Z45" s="58">
+      <c r="Z45" s="57">
         <v>102990</v>
       </c>
-      <c r="AA45" s="58">
+      <c r="AA45" s="57">
         <f>Z45</f>
         <v>102990</v>
       </c>
-      <c r="AB45" s="58">
+      <c r="AB45" s="57">
         <v>28160276</v>
       </c>
-      <c r="AC45" s="58">
+      <c r="AC45" s="57">
         <f>AB45</f>
         <v>28160276</v>
       </c>
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A46" s="56" t="s">
-        <v>161</v>
-      </c>
-      <c r="T46" s="56"/>
-      <c r="U46" s="56"/>
-      <c r="V46" s="56"/>
-      <c r="W46" s="56"/>
-      <c r="X46" s="56"/>
-      <c r="Y46" s="60">
+      <c r="A46" s="55" t="s">
+        <v>172</v>
+      </c>
+      <c r="T46" s="57"/>
+      <c r="U46" s="55"/>
+      <c r="W46" s="55"/>
+      <c r="X46" s="55"/>
+      <c r="Y46" s="59">
         <v>45782</v>
       </c>
-      <c r="Z46" s="58">
+      <c r="Z46" s="57">
         <v>207209</v>
       </c>
-      <c r="AA46" s="58">
+      <c r="AA46" s="57">
         <f>SUM(Z$45:Z46)</f>
         <v>310199</v>
       </c>
-      <c r="AB46" s="58">
+      <c r="AB46" s="57">
         <v>56816910</v>
       </c>
-      <c r="AC46" s="58">
+      <c r="AC46" s="57">
         <f>SUM(AB$45:AB46)</f>
         <v>84977186</v>
       </c>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A47" s="56" t="s">
-        <v>162</v>
-      </c>
-      <c r="T47" s="56"/>
-      <c r="U47" s="56"/>
-      <c r="V47" s="56"/>
-      <c r="W47" s="56"/>
-      <c r="X47" s="56"/>
-      <c r="Y47" s="60">
+      <c r="A47" s="55" t="s">
+        <v>173</v>
+      </c>
+      <c r="T47" s="57"/>
+      <c r="U47" s="55"/>
+      <c r="W47" s="55"/>
+      <c r="X47" s="55"/>
+      <c r="Y47" s="59">
         <v>45789</v>
       </c>
-      <c r="Z47" s="58">
+      <c r="Z47" s="57">
         <v>259857</v>
       </c>
-      <c r="AA47" s="58">
+      <c r="AA47" s="57">
         <f>SUM(Z$45:Z47)</f>
         <v>570056</v>
       </c>
-      <c r="AB47" s="58">
+      <c r="AB47" s="57">
         <v>71686947</v>
       </c>
-      <c r="AC47" s="58">
+      <c r="AC47" s="57">
         <f>SUM(AB$45:AB47)</f>
         <v>156664133</v>
       </c>
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A48" s="56" t="s">
-        <v>163</v>
-      </c>
-      <c r="T48" s="56"/>
-      <c r="U48" s="56"/>
-      <c r="V48" s="56"/>
-      <c r="W48" s="56"/>
-      <c r="X48" s="56"/>
-      <c r="Y48" s="60">
+      <c r="A48" s="55" t="s">
+        <v>154</v>
+      </c>
+      <c r="T48" s="57"/>
+      <c r="U48" s="55"/>
+      <c r="W48" s="55"/>
+      <c r="X48" s="55"/>
+      <c r="Y48" s="59">
         <v>45796</v>
       </c>
-      <c r="Z48" s="58">
+      <c r="Z48" s="57">
         <v>268866</v>
       </c>
-      <c r="AA48" s="58">
+      <c r="AA48" s="57">
         <f>SUM(Z$45:Z48)</f>
         <v>838922</v>
       </c>
-      <c r="AB48" s="58">
+      <c r="AB48" s="57">
         <v>73709071</v>
       </c>
-      <c r="AC48" s="58">
+      <c r="AC48" s="57">
         <f>SUM(AB$45:AB48)</f>
         <v>230373204</v>
       </c>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A49" s="56" t="s">
-        <v>164</v>
-      </c>
-      <c r="T49" s="56"/>
-      <c r="U49" s="56"/>
-      <c r="V49" s="56"/>
-      <c r="W49" s="56"/>
-      <c r="X49" s="56"/>
-      <c r="Y49" s="60">
+      <c r="A49" s="55" t="s">
+        <v>155</v>
+      </c>
+      <c r="T49" s="57"/>
+      <c r="U49" s="55"/>
+      <c r="W49" s="55"/>
+      <c r="X49" s="55"/>
+      <c r="Y49" s="59">
         <v>45803</v>
       </c>
-      <c r="Z49" s="58">
+      <c r="Z49" s="57">
         <v>251715</v>
       </c>
-      <c r="AA49" s="58">
+      <c r="AA49" s="57">
         <f>SUM(Z$45:Z49)</f>
         <v>1090637</v>
       </c>
-      <c r="AB49" s="58">
+      <c r="AB49" s="57">
         <v>70641359</v>
       </c>
-      <c r="AC49" s="58">
+      <c r="AC49" s="57">
         <f>SUM(AB$45:AB49)</f>
         <v>301014563</v>
       </c>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A50" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="T50" s="56"/>
-      <c r="U50" s="56"/>
-      <c r="V50" s="56"/>
-      <c r="W50" s="56"/>
-      <c r="X50" s="56"/>
-      <c r="Y50" s="60">
+      <c r="A50" s="55" t="s">
+        <v>158</v>
+      </c>
+      <c r="T50" s="57"/>
+      <c r="U50" s="55"/>
+      <c r="W50" s="55"/>
+      <c r="X50" s="55"/>
+      <c r="Y50" s="59">
         <v>45810</v>
       </c>
-      <c r="Z50" s="58">
+      <c r="Z50" s="57">
         <v>197115</v>
       </c>
-      <c r="AA50" s="58">
+      <c r="AA50" s="57">
         <f>SUM(Z$45:Z50)</f>
         <v>1287752</v>
       </c>
-      <c r="AB50" s="58">
+      <c r="AB50" s="57">
         <v>55813358</v>
       </c>
-      <c r="AC50" s="58">
+      <c r="AC50" s="57">
         <f>SUM(AB$45:AB50)</f>
         <v>356827921</v>
       </c>
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A51" s="56" t="s">
-        <v>205</v>
-      </c>
-      <c r="T51" s="56"/>
-      <c r="U51" s="56"/>
-      <c r="V51" s="56"/>
-      <c r="W51" s="56"/>
-      <c r="X51" s="56"/>
-      <c r="Y51" s="60">
+      <c r="A51" s="55" t="s">
+        <v>159</v>
+      </c>
+      <c r="T51" s="57"/>
+      <c r="U51" s="55"/>
+      <c r="W51" s="55"/>
+      <c r="X51" s="55"/>
+      <c r="Y51" s="59">
         <v>45817</v>
       </c>
-      <c r="Z51" s="58">
+      <c r="Z51" s="57">
         <v>204612</v>
       </c>
-      <c r="AA51" s="58">
+      <c r="AA51" s="57">
         <f>SUM(Z$45:Z51)</f>
         <v>1492364</v>
       </c>
-      <c r="AB51" s="58">
+      <c r="AB51" s="57">
         <v>56483154</v>
       </c>
-      <c r="AC51" s="58">
+      <c r="AC51" s="57">
         <f>SUM(AB$45:AB51)</f>
         <v>413311075</v>
       </c>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A52" s="56" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y52" s="60">
+      <c r="A52" s="55" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y52" s="59">
         <v>45824</v>
       </c>
-      <c r="Z52" s="58">
+      <c r="Z52" s="57">
         <v>316007</v>
       </c>
-      <c r="AA52" s="58">
+      <c r="AA52" s="57">
         <f>SUM(Z$45:Z52)</f>
         <v>1808371</v>
       </c>
-      <c r="AB52" s="58">
+      <c r="AB52" s="57">
         <v>85301407</v>
       </c>
-      <c r="AC52" s="58">
+      <c r="AC52" s="57">
         <f>SUM(AB$45:AB52)</f>
         <v>498612482</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A53" s="56" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y53" s="60">
+      <c r="A53" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y53" s="59">
         <v>45831</v>
       </c>
-      <c r="Z53" s="58">
+      <c r="Z53" s="57">
         <v>279202</v>
       </c>
-      <c r="AA53" s="58">
+      <c r="AA53" s="57">
         <f>SUM(Z$45:Z53)</f>
         <v>2087573</v>
       </c>
-      <c r="AB53" s="58">
+      <c r="AB53" s="57">
         <v>73119443</v>
       </c>
-      <c r="AC53" s="58">
+      <c r="AC53" s="57">
         <f>SUM(AB$45:AB53)</f>
         <v>571731925</v>
       </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A54" s="56" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y54" s="60">
+      <c r="A54" s="55" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y54" s="59">
         <v>45838</v>
       </c>
-      <c r="Z54" s="58">
+      <c r="Z54" s="57">
         <v>352192</v>
       </c>
-      <c r="AA54" s="58">
+      <c r="AA54" s="57">
         <f>SUM(Z$45:Z54)</f>
         <v>2439765</v>
       </c>
-      <c r="AB54" s="58">
+      <c r="AB54" s="57">
         <v>91369669</v>
       </c>
-      <c r="AC54" s="58">
+      <c r="AC54" s="57">
         <f>SUM(AB$45:AB54)</f>
         <v>663101594</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A55" s="56" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y55" s="60">
+      <c r="A55" s="55" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y55" s="59">
         <v>45845</v>
       </c>
-      <c r="Z55" s="58">
+      <c r="Z55" s="57">
         <v>313752</v>
       </c>
-      <c r="AA55" s="58">
+      <c r="AA55" s="57">
         <f>SUM(Z$45:Z55)</f>
         <v>2753517</v>
       </c>
-      <c r="AB55" s="58">
+      <c r="AB55" s="57">
         <v>83251888</v>
       </c>
-      <c r="AC55" s="58">
+      <c r="AC55" s="57">
         <f>SUM(AB$45:AB55)</f>
         <v>746353482</v>
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A56" s="56" t="s">
-        <v>195</v>
-      </c>
-      <c r="Y56" s="60">
+      <c r="A56" s="55" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y56" s="59">
         <v>45852</v>
       </c>
-      <c r="Z56" s="58">
+      <c r="Z56" s="57">
         <v>345581</v>
       </c>
-      <c r="AA56" s="58">
+      <c r="AA56" s="57">
         <f>SUM(Z$45:Z56)</f>
         <v>3099098</v>
       </c>
-      <c r="AB56" s="58">
+      <c r="AB56" s="57">
         <v>91413515</v>
       </c>
-      <c r="AC56" s="58">
+      <c r="AC56" s="57">
         <f>SUM(AB$45:AB56)</f>
         <v>837766997</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A57" s="56" t="s">
-        <v>196</v>
-      </c>
-      <c r="Y57" s="60">
+      <c r="A57" s="55" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y57" s="59">
         <v>45859</v>
       </c>
-      <c r="Z57" s="58">
+      <c r="Z57" s="57">
         <v>362255</v>
       </c>
-      <c r="AA57" s="58">
+      <c r="AA57" s="57">
         <f>SUM(Z$45:Z57)</f>
         <v>3461353</v>
       </c>
-      <c r="AB57" s="58">
+      <c r="AB57" s="57">
         <v>92733079</v>
       </c>
-      <c r="AC57" s="58">
+      <c r="AC57" s="57">
         <f>SUM(AB$45:AB57)</f>
         <v>930500076</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A58" s="56" t="s">
-        <v>197</v>
-      </c>
-      <c r="Y58" s="60">
+      <c r="A58" s="55" t="s">
+        <v>204</v>
+      </c>
+      <c r="Y58" s="59">
         <v>45866</v>
       </c>
-      <c r="Z58" s="58">
+      <c r="Z58" s="57">
         <v>375672</v>
       </c>
-      <c r="AA58" s="58">
+      <c r="AA58" s="57">
         <f>SUM(Z$45:Z58)</f>
         <v>3837025</v>
       </c>
-      <c r="AB58" s="58">
+      <c r="AB58" s="57">
         <v>92409563</v>
       </c>
-      <c r="AC58" s="58">
+      <c r="AC58" s="57">
         <f>SUM(AB$45:AB58)</f>
         <v>1022909639</v>
       </c>
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A59" s="56" t="s">
-        <v>198</v>
-      </c>
-      <c r="Y59" s="60">
+      <c r="A59" s="55" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y59" s="59">
         <v>45873</v>
       </c>
-      <c r="Z59" s="58">
+      <c r="Z59" s="57">
         <v>365756</v>
       </c>
-      <c r="AA59" s="58">
+      <c r="AA59" s="57">
         <f>SUM(Z$45:Z59)</f>
         <v>4202781</v>
       </c>
-      <c r="AB59" s="58">
+      <c r="AB59" s="57">
         <v>89076060</v>
       </c>
-      <c r="AC59" s="58">
+      <c r="AC59" s="57">
         <f>SUM(AB$45:AB59)</f>
         <v>1111985699</v>
       </c>
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A60" s="56" t="s">
-        <v>199</v>
-      </c>
-      <c r="Y60" s="60">
+      <c r="A60" s="55" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y60" s="59">
         <v>45880</v>
       </c>
-      <c r="Z60" s="58">
+      <c r="Z60" s="57">
         <v>380062</v>
       </c>
-      <c r="AA60" s="58">
+      <c r="AA60" s="57">
         <f>SUM(Z$45:Z60)</f>
         <v>4582843</v>
       </c>
-      <c r="AB60" s="58">
+      <c r="AB60" s="57">
         <v>92397701</v>
       </c>
-      <c r="AC60" s="58">
+      <c r="AC60" s="57">
         <f>SUM(AB$45:AB60)</f>
         <v>1204383400</v>
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A61" s="56" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y61" s="60">
+      <c r="A61" s="55" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y61" s="59">
         <v>45887</v>
       </c>
-      <c r="Z61" s="58">
+      <c r="Z61" s="57">
         <v>376116</v>
       </c>
-      <c r="AA61" s="58">
+      <c r="AA61" s="57">
         <f>SUM(Z$45:Z61)</f>
         <v>4958959</v>
       </c>
-      <c r="AB61" s="58">
+      <c r="AB61" s="57">
         <v>92464404</v>
       </c>
-      <c r="AC61" s="58">
+      <c r="AC61" s="57">
         <f>SUM(AB$45:AB61)</f>
         <v>1296847804</v>
       </c>
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A62" s="56" t="s">
-        <v>201</v>
-      </c>
-      <c r="Y62" s="60">
+      <c r="A62" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y62" s="59">
         <v>45894</v>
       </c>
-      <c r="Z62" s="58">
+      <c r="Z62" s="57">
         <v>390489</v>
       </c>
-      <c r="AA62" s="58">
+      <c r="AA62" s="57">
         <f>SUM(Z$45:Z62)</f>
         <v>5349448</v>
       </c>
-      <c r="AB62" s="58">
+      <c r="AB62" s="57">
         <v>98831454</v>
       </c>
-      <c r="AC62" s="58">
+      <c r="AC62" s="57">
         <f>SUM(AB$45:AB62)</f>
         <v>1395679258</v>
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A63" s="56" t="s">
-        <v>204</v>
-      </c>
-      <c r="Y63" s="60">
+      <c r="A63" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y63" s="59">
         <v>45901</v>
       </c>
-      <c r="Z63" s="58">
+      <c r="Z63" s="57">
         <v>416394</v>
       </c>
-      <c r="AA63" s="58">
+      <c r="AA63" s="57">
         <f>SUM(Z$45:Z63)</f>
         <v>5765842</v>
       </c>
-      <c r="AB63" s="58">
+      <c r="AB63" s="57">
         <v>106686368</v>
       </c>
-      <c r="AC63" s="58">
+      <c r="AC63" s="57">
         <f>SUM(AB$45:AB63)</f>
         <v>1502365626</v>
       </c>
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A64" s="56" t="s">
-        <v>203</v>
-      </c>
-      <c r="Y64" s="60">
+      <c r="A64" s="55" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y64" s="59">
         <v>45908</v>
       </c>
-      <c r="Z64" s="58">
+      <c r="Z64" s="57">
         <v>387564</v>
       </c>
-      <c r="AA64" s="58">
+      <c r="AA64" s="57">
         <f>SUM(Z$45:Z64)</f>
         <v>6153406</v>
       </c>
-      <c r="AB64" s="58">
+      <c r="AB64" s="57">
         <v>98866394</v>
       </c>
-      <c r="AC64" s="58">
+      <c r="AC64" s="57">
         <f>SUM(AB$45:AB64)</f>
         <v>1601232020</v>
       </c>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A65" s="56" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y65" s="60">
+      <c r="A65" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y65" s="59">
         <v>45915</v>
       </c>
-      <c r="Z65" s="58">
+      <c r="Z65" s="57">
         <v>243717</v>
       </c>
-      <c r="AA65" s="58">
+      <c r="AA65" s="57">
         <f>SUM(Z$45:Z65)</f>
         <v>6397123</v>
       </c>
-      <c r="AB65" s="58">
+      <c r="AB65" s="57">
         <v>62346848</v>
       </c>
-      <c r="AC65" s="58">
+      <c r="AC65" s="57">
         <f>SUM(AB$45:AB65)</f>
         <v>1663578868</v>
       </c>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y66" s="60">
+      <c r="A66" s="55" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y66" s="59">
         <v>45922</v>
       </c>
-      <c r="Z66" s="58">
+      <c r="Z66" s="57">
         <v>271160</v>
       </c>
-      <c r="AA66" s="58">
+      <c r="AA66" s="57">
         <f>SUM(Z$45:Z66)</f>
         <v>6668283</v>
       </c>
-      <c r="AB66" s="58">
+      <c r="AB66" s="57">
         <v>66970032</v>
       </c>
-      <c r="AC66" s="58">
+      <c r="AC66" s="57">
         <f>SUM(AB$45:AB66)</f>
         <v>1730548900</v>
       </c>
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y67" s="60">
+      <c r="A67" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y67" s="59">
         <v>45929</v>
       </c>
-      <c r="Z67" s="58">
+      <c r="Z67" s="57">
         <v>293620</v>
       </c>
-      <c r="AA67" s="58">
+      <c r="AA67" s="57">
         <f>SUM(Z$45:Z67)</f>
         <v>6961903</v>
       </c>
-      <c r="AB67" s="58">
+      <c r="AB67" s="57">
         <v>70784809</v>
       </c>
-      <c r="AC67" s="58">
+      <c r="AC67" s="57">
         <f>SUM(AB$45:AB67)</f>
         <v>1801333709</v>
       </c>
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y68" s="60">
+      <c r="A68" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y68" s="59">
         <v>45936</v>
       </c>
-      <c r="Z68" s="58">
+      <c r="Z68" s="57">
         <v>266241</v>
       </c>
-      <c r="AA68" s="58">
+      <c r="AA68" s="57">
         <f>SUM(Z$45:Z68)</f>
         <v>7228144</v>
       </c>
-      <c r="AB68" s="58">
+      <c r="AB68" s="57">
         <v>65407817</v>
       </c>
-      <c r="AC68" s="58">
+      <c r="AC68" s="57">
         <f>SUM(AB$45:AB68)</f>
         <v>1866741526</v>
       </c>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y69" s="60">
+      <c r="A69" s="55" t="s">
+        <v>200</v>
+      </c>
+      <c r="Y69" s="59">
         <v>45943</v>
       </c>
-      <c r="Z69" s="58">
+      <c r="Z69" s="57">
         <v>274102</v>
       </c>
-      <c r="AA69" s="58">
+      <c r="AA69" s="57">
         <f>SUM(Z$45:Z69)</f>
         <v>7502246</v>
       </c>
-      <c r="AB69" s="58">
+      <c r="AB69" s="57">
         <v>68242334</v>
       </c>
-      <c r="AC69" s="58">
+      <c r="AC69" s="57">
         <f>SUM(AB$45:AB69)</f>
         <v>1934983860</v>
       </c>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y70" s="60">
+      <c r="A70" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="Y70" s="59">
         <v>45950</v>
       </c>
-      <c r="Z70" s="58">
+      <c r="Z70" s="57">
         <v>249659</v>
       </c>
-      <c r="AA70" s="58">
+      <c r="AA70" s="57">
         <f>SUM(Z$45:Z70)</f>
         <v>7751905</v>
       </c>
-      <c r="AB70" s="58">
+      <c r="AB70" s="57">
         <v>63722172</v>
       </c>
-      <c r="AC70" s="58">
+      <c r="AC70" s="57">
         <f>SUM(AB$45:AB70)</f>
         <v>1998706032</v>
       </c>
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y71" s="60">
+      <c r="A71" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y71" s="59">
         <v>45957</v>
       </c>
-      <c r="Z71" s="58">
+      <c r="Z71" s="57">
         <v>86370</v>
       </c>
-      <c r="AA71" s="58">
+      <c r="AA71" s="57">
         <f>SUM(Z$45:Z71)</f>
         <v>7838275</v>
       </c>
-      <c r="AB71" s="58">
+      <c r="AB71" s="57">
         <v>22848513</v>
       </c>
-      <c r="AC71" s="58">
+      <c r="AC71" s="57">
         <f>SUM(AB$45:AB71)</f>
         <v>2021554545</v>
       </c>
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y72" s="60">
+      <c r="A72" s="55" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y72" s="59">
         <v>45964</v>
       </c>
-      <c r="Z72" s="58">
+      <c r="Z72" s="57">
         <v>162610</v>
       </c>
-      <c r="AA72" s="58">
+      <c r="AA72" s="57">
         <f>SUM(Z$45:Z72)</f>
         <v>8000885</v>
       </c>
-      <c r="AB72" s="58">
+      <c r="AB72" s="57">
         <v>42752249</v>
       </c>
-      <c r="AC72" s="58">
+      <c r="AC72" s="57">
         <f>SUM(AB$45:AB72)</f>
         <v>2064306794</v>
       </c>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y73" s="60">
+      <c r="Y73" s="59">
         <v>45971</v>
       </c>
-      <c r="Z73" s="58">
+      <c r="Z73" s="57">
         <v>215029</v>
       </c>
-      <c r="AA73" s="58">
+      <c r="AA73" s="57">
         <f>SUM(Z$45:Z73)</f>
         <v>8215914</v>
       </c>
-      <c r="AB73" s="58">
+      <c r="AB73" s="57">
         <v>56294477</v>
       </c>
-      <c r="AC73" s="58">
+      <c r="AC73" s="57">
         <f>SUM(AB$45:AB73)</f>
         <v>2120601271</v>
       </c>
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y74" s="60">
+      <c r="Y74" s="59">
         <v>45978</v>
       </c>
-      <c r="Z74" s="58">
+      <c r="Z74" s="57">
         <v>141656</v>
       </c>
-      <c r="AA74" s="58">
+      <c r="AA74" s="57">
         <f>SUM(Z$45:Z74)</f>
         <v>8357570</v>
       </c>
-      <c r="AB74" s="58">
+      <c r="AB74" s="57">
         <v>37472121</v>
       </c>
-      <c r="AC74" s="58">
+      <c r="AC74" s="57">
         <f>SUM(AB$45:AB74)</f>
         <v>2158073392</v>
       </c>
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y75" s="60">
+      <c r="Y75" s="59">
         <v>45985</v>
       </c>
-      <c r="Z75" s="58">
+      <c r="Z75" s="57">
         <v>200723</v>
       </c>
-      <c r="AA75" s="58">
+      <c r="AA75" s="57">
         <f>SUM(Z$45:Z75)</f>
         <v>8558293</v>
       </c>
-      <c r="AB75" s="58">
+      <c r="AB75" s="57">
         <v>51875958</v>
       </c>
-      <c r="AC75" s="58">
+      <c r="AC75" s="57">
         <f>SUM(AB$45:AB75)</f>
         <v>2209949350</v>
       </c>
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y76" s="60">
+      <c r="Y76" s="59">
         <v>45992</v>
       </c>
-      <c r="Z76" s="58">
+      <c r="Z76" s="57">
         <v>186672</v>
       </c>
-      <c r="AA76" s="58">
+      <c r="AA76" s="57">
         <f>SUM(Z$45:Z76)</f>
         <v>8744965</v>
       </c>
-      <c r="AB76" s="58">
+      <c r="AB76" s="57">
         <v>48812636</v>
       </c>
-      <c r="AC76" s="58">
+      <c r="AC76" s="57">
         <f>SUM(AB$45:AB76)</f>
         <v>2258761986</v>
       </c>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y77" s="60">
+      <c r="Y77" s="59">
         <v>45999</v>
       </c>
-      <c r="Z77" s="58">
+      <c r="Z77" s="57">
         <v>190572</v>
       </c>
-      <c r="AA77" s="58">
+      <c r="AA77" s="57">
         <f>SUM(Z$45:Z77)</f>
         <v>8935537</v>
       </c>
-      <c r="AB77" s="58">
+      <c r="AB77" s="57">
         <v>49903186</v>
       </c>
-      <c r="AC77" s="58">
+      <c r="AC77" s="57">
         <f>SUM(AB$45:AB77)</f>
         <v>2308665172</v>
       </c>
     </row>
     <row r="78" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y78" s="60">
+      <c r="Y78" s="59">
         <v>46006</v>
       </c>
-      <c r="Z78" s="58">
+      <c r="Z78" s="57">
         <v>156888</v>
       </c>
-      <c r="AA78" s="58">
+      <c r="AA78" s="57">
         <f>SUM(Z$45:Z78)</f>
         <v>9092425</v>
       </c>
-      <c r="AB78" s="58">
+      <c r="AB78" s="57">
         <v>40538342</v>
       </c>
-      <c r="AC78" s="58">
+      <c r="AC78" s="57">
         <f>SUM(AB$45:AB78)</f>
         <v>2349203514</v>
       </c>
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y79" s="60">
+      <c r="Y79" s="59">
         <v>46013</v>
       </c>
-      <c r="Z79" s="58">
+      <c r="Z79" s="57">
         <v>73113</v>
       </c>
-      <c r="AA79" s="58">
+      <c r="AA79" s="57">
         <f>SUM(Z$45:Z79)</f>
         <v>9165538</v>
       </c>
-      <c r="AB79" s="58">
+      <c r="AB79" s="57">
         <v>19398960</v>
       </c>
-      <c r="AC79" s="58">
+      <c r="AC79" s="57">
         <f>SUM(AB$45:AB79)</f>
         <v>2368602474</v>
       </c>
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Y80" s="63">
+      <c r="Y80" s="62">
         <v>46020</v>
       </c>
-      <c r="Z80" s="64">
+      <c r="Z80" s="63">
         <v>29421</v>
       </c>
-      <c r="AA80" s="64">
+      <c r="AA80" s="63">
         <f>SUM(Z$45:Z80)</f>
         <v>9194959</v>
       </c>
-      <c r="AB80" s="64">
+      <c r="AB80" s="63">
         <v>7736120</v>
       </c>
-      <c r="AC80" s="64">
+      <c r="AC80" s="63">
         <f>SUM(AB$45:AB80)</f>
         <v>2376338594</v>
       </c>
     </row>
     <row r="81" spans="25:29" x14ac:dyDescent="0.35">
-      <c r="Y81" s="60">
+      <c r="Y81" s="59">
         <v>46027</v>
       </c>
-      <c r="Z81" s="58">
+      <c r="Z81" s="57">
         <v>42073</v>
       </c>
-      <c r="AA81" s="58">
+      <c r="AA81" s="57">
         <f>SUM(Z$45:Z81)</f>
         <v>9237032</v>
       </c>
-      <c r="AB81" s="58">
+      <c r="AB81" s="57">
         <v>11093439</v>
       </c>
-      <c r="AC81" s="58">
+      <c r="AC81" s="57">
         <f>SUM(AB$45:AB81)</f>
         <v>2387432033</v>
       </c>
     </row>
     <row r="82" spans="25:29" x14ac:dyDescent="0.35">
-      <c r="Y82" s="60">
+      <c r="Y82" s="59">
         <v>46034</v>
       </c>
-      <c r="Z82" s="58">
+      <c r="Z82" s="57">
         <v>57798</v>
       </c>
-      <c r="AA82" s="58">
+      <c r="AA82" s="57">
         <f>SUM(Z$45:Z82)</f>
         <v>9294830</v>
       </c>
-      <c r="AB82" s="58">
+      <c r="AB82" s="57">
         <v>15093539</v>
       </c>
-      <c r="AC82" s="58">
+      <c r="AC82" s="57">
         <f>SUM(AB$45:AB82)</f>
         <v>2402525572</v>
       </c>
     </row>
     <row r="83" spans="25:29" x14ac:dyDescent="0.35">
-      <c r="Y83" s="60">
+      <c r="Y83" s="59">
         <v>46041</v>
       </c>
-      <c r="Z83" s="58">
+      <c r="Z83" s="57">
         <v>66186</v>
       </c>
-      <c r="AA83" s="58">
+      <c r="AA83" s="57">
         <f>SUM(Z$45:Z83)</f>
         <v>9361016</v>
       </c>
-      <c r="AB83" s="58">
+      <c r="AB83" s="57">
         <v>17691908</v>
       </c>
-      <c r="AC83" s="58">
+      <c r="AC83" s="57">
         <f>SUM(AB$45:AB83)</f>
         <v>2420217480</v>
       </c>
     </row>
     <row r="84" spans="25:29" x14ac:dyDescent="0.35">
-      <c r="Y84" s="60">
+      <c r="Y84" s="59">
         <v>46048</v>
       </c>
-      <c r="Z84" s="58">
+      <c r="Z84" s="57">
         <v>725349</v>
       </c>
-      <c r="AA84" s="58">
+      <c r="AA84" s="57">
         <f>SUM(Z$45:Z84)</f>
         <v>10086365</v>
       </c>
-      <c r="AB84" s="58">
+      <c r="AB84" s="57">
         <v>184559740</v>
       </c>
-      <c r="AC84" s="58">
+      <c r="AC84" s="57">
         <f>SUM(AB$45:AB84)</f>
         <v>2604777220</v>
       </c>
     </row>
     <row r="85" spans="25:29" x14ac:dyDescent="0.35">
-      <c r="Y85" s="60">
+      <c r="Y85" s="59">
         <v>46055</v>
       </c>
-      <c r="Z85" s="58">
+      <c r="Z85" s="57">
         <v>170916</v>
       </c>
-      <c r="AA85" s="58">
+      <c r="AA85" s="57">
         <f>SUM(Z$45:Z85)</f>
         <v>10257281</v>
       </c>
-      <c r="AB85" s="58">
+      <c r="AB85" s="57">
         <v>43824616</v>
       </c>
-      <c r="AC85" s="58">
+      <c r="AC85" s="57">
         <f>SUM(AB$45:AB85)</f>
         <v>2648601836</v>
       </c>
     </row>
     <row r="86" spans="25:29" x14ac:dyDescent="0.35">
-      <c r="Y86" s="60">
+      <c r="Y86" s="59">
         <v>46062</v>
       </c>
-      <c r="Z86" s="58">
+      <c r="Z86" s="57">
         <v>69537</v>
       </c>
-      <c r="AA86" s="58">
+      <c r="AA86" s="57">
         <f>SUM(Z$45:Z86)</f>
         <v>10326818</v>
       </c>
-      <c r="AB86" s="58">
+      <c r="AB86" s="57">
         <v>18760501</v>
       </c>
-      <c r="AC86" s="58">
+      <c r="AC86" s="57">
         <f>SUM(AB$45:AB86)</f>
         <v>2667362337</v>
       </c>
     </row>
     <row r="87" spans="25:29" x14ac:dyDescent="0.35">
-      <c r="Y87" s="60">
+      <c r="Y87" s="59">
         <v>46069</v>
       </c>
-      <c r="Z87" s="58">
+      <c r="Z87" s="57">
         <v>65565</v>
       </c>
-      <c r="AA87" s="58">
+      <c r="AA87" s="57">
         <f>SUM(Z$45:Z87)</f>
         <v>10392383</v>
       </c>
-      <c r="AB87" s="58">
+      <c r="AB87" s="57">
         <v>18321521</v>
       </c>
-      <c r="AC87" s="58">
+      <c r="AC87" s="57">
         <f>SUM(AB$45:AB87)</f>
         <v>2685683858</v>
       </c>
     </row>
     <row r="88" spans="25:29" x14ac:dyDescent="0.35">
-      <c r="Y88" s="60">
+      <c r="Y88" s="59">
         <v>46076</v>
       </c>
-      <c r="Z88" s="58">
+      <c r="Z88" s="57">
         <v>63292</v>
       </c>
-      <c r="AA88" s="58">
+      <c r="AA88" s="57">
         <f>SUM(Z$45:Z88)</f>
         <v>10455675</v>
       </c>
-      <c r="AB88" s="58">
+      <c r="AB88" s="57">
         <v>17961487</v>
       </c>
-      <c r="AC88" s="58">
+      <c r="AC88" s="57">
         <f>SUM(AB$45:AB88)</f>
         <v>2703645345</v>
       </c>
     </row>
     <row r="89" spans="25:29" x14ac:dyDescent="0.35">
-      <c r="Y89" s="60">
+      <c r="Y89" s="59">
         <v>46083</v>
       </c>
-      <c r="Z89" s="58">
+      <c r="Z89" s="57">
         <v>212306</v>
       </c>
-      <c r="AA89" s="58">
+      <c r="AA89" s="57">
         <f>SUM(Z$45:Z89)</f>
         <v>10667981</v>
       </c>
-      <c r="AB89" s="58">
+      <c r="AB89" s="57">
         <v>61108346</v>
       </c>
-      <c r="AC89" s="58">
+      <c r="AC89" s="57">
         <f>SUM(AB$45:AB89)</f>
         <v>2764753691</v>
       </c>
     </row>
     <row r="90" spans="25:29" x14ac:dyDescent="0.35">
-      <c r="Y90" s="60">
+      <c r="Y90" s="59">
         <v>46090</v>
       </c>
-      <c r="Z90" s="58">
+      <c r="Z90" s="57">
         <v>241501</v>
       </c>
-      <c r="AA90" s="58">
+      <c r="AA90" s="57">
         <f>SUM(Z$45:Z90)</f>
         <v>10909482</v>
       </c>
-      <c r="AB90" s="58">
+      <c r="AB90" s="57">
         <v>65148807</v>
       </c>
-      <c r="AC90" s="58">
+      <c r="AC90" s="57">
         <f>SUM(AB$45:AB90)</f>
         <v>2829902498</v>
       </c>
     </row>
     <row r="91" spans="25:29" x14ac:dyDescent="0.35">
-      <c r="Y91" s="60">
+      <c r="Y91" s="59">
         <v>46097</v>
       </c>
-      <c r="Z91" s="58">
+      <c r="Z91" s="57">
         <v>251239</v>
       </c>
-      <c r="AA91" s="58">
+      <c r="AA91" s="57">
         <f>SUM(Z$45:Z91)</f>
         <v>11160721</v>
       </c>
-      <c r="AB91" s="58">
+      <c r="AB91" s="57">
         <v>65750677</v>
       </c>
-      <c r="AC91" s="58">
+      <c r="AC91" s="57">
         <f>SUM(AB$45:AB91)</f>
         <v>2895653175</v>
       </c>
     </row>
     <row r="92" spans="25:29" x14ac:dyDescent="0.35">
-      <c r="Y92" s="61">
+      <c r="Y92" s="60">
         <v>46104</v>
       </c>
-      <c r="Z92" s="58">
+      <c r="Z92" s="57">
         <v>406220</v>
       </c>
-      <c r="AA92" s="58">
+      <c r="AA92" s="57">
         <f>SUM(Z$45:Z92)</f>
         <v>11566941</v>
       </c>
-      <c r="AB92" s="58">
+      <c r="AB92" s="57">
         <v>104347579</v>
       </c>
-      <c r="AC92" s="58">
+      <c r="AC92" s="57">
         <f>SUM(AB$45:AB92)</f>
         <v>3000000754</v>
       </c>
@@ -4523,7 +4623,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>51</v>
@@ -4579,7 +4679,9 @@
       <c r="T4" s="9">
         <v>33177</v>
       </c>
-      <c r="U4" s="9"/>
+      <c r="U4" s="9">
+        <v>35061</v>
+      </c>
       <c r="V4" s="9"/>
       <c r="W4" s="9"/>
       <c r="X4" s="10"/>
@@ -4618,44 +4720,44 @@
         <v>138494</v>
       </c>
       <c r="AK4" s="11">
-        <f>AJ4*1.03</f>
-        <v>142648.82</v>
+        <f>AJ4*1</f>
+        <v>138494</v>
       </c>
       <c r="AL4" s="9">
         <f>AK4*1.05</f>
-        <v>149781.26100000003</v>
+        <v>145418.70000000001</v>
       </c>
       <c r="AM4" s="9">
         <f t="shared" ref="AM4:AT4" si="0">AL4*1.05</f>
-        <v>157270.32405000002</v>
+        <v>152689.63500000001</v>
       </c>
       <c r="AN4" s="9">
         <f t="shared" si="0"/>
-        <v>165133.84025250003</v>
+        <v>160324.11675000002</v>
       </c>
       <c r="AO4" s="9">
         <f t="shared" si="0"/>
-        <v>173390.53226512505</v>
+        <v>168340.32258750004</v>
       </c>
       <c r="AP4" s="9">
         <f t="shared" si="0"/>
-        <v>182060.0588783813</v>
+        <v>176757.33871687503</v>
       </c>
       <c r="AQ4" s="9">
         <f t="shared" si="0"/>
-        <v>191163.06182230037</v>
+        <v>185595.20565271878</v>
       </c>
       <c r="AR4" s="9">
         <f t="shared" si="0"/>
-        <v>200721.2149134154</v>
+        <v>194874.96593535473</v>
       </c>
       <c r="AS4" s="9">
         <f t="shared" si="0"/>
-        <v>210757.27565908618</v>
+        <v>204618.71423212247</v>
       </c>
       <c r="AT4" s="9">
         <f t="shared" si="0"/>
-        <v>221295.1394420405</v>
+        <v>214849.64994372861</v>
       </c>
     </row>
     <row r="5" spans="1:300" x14ac:dyDescent="0.25">
@@ -4663,7 +4765,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3">
-        <v>683.9</v>
+        <v>681.9</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>52</v>
@@ -4719,7 +4821,9 @@
       <c r="T5" s="10">
         <v>-22092</v>
       </c>
-      <c r="U5" s="10"/>
+      <c r="U5" s="10">
+        <v>-23616</v>
+      </c>
       <c r="V5" s="10"/>
       <c r="W5" s="10"/>
       <c r="X5" s="10"/>
@@ -4767,43 +4871,43 @@
       </c>
       <c r="AK5" s="12">
         <f>AK4*-0.67</f>
-        <v>-95574.709400000007</v>
+        <v>-92790.98000000001</v>
       </c>
       <c r="AL5" s="10">
         <f t="shared" ref="AL5:AT5" si="1">AL4*-0.67</f>
-        <v>-100353.44487000002</v>
+        <v>-97430.52900000001</v>
       </c>
       <c r="AM5" s="10">
         <f t="shared" si="1"/>
-        <v>-105371.11711350002</v>
+        <v>-102302.05545000001</v>
       </c>
       <c r="AN5" s="10">
         <f t="shared" si="1"/>
-        <v>-110639.67296917502</v>
+        <v>-107417.15822250002</v>
       </c>
       <c r="AO5" s="10">
         <f t="shared" si="1"/>
-        <v>-116171.65661763379</v>
+        <v>-112788.01613362503</v>
       </c>
       <c r="AP5" s="10">
         <f t="shared" si="1"/>
-        <v>-121980.23944851548</v>
+        <v>-118427.41694030628</v>
       </c>
       <c r="AQ5" s="10">
         <f t="shared" si="1"/>
-        <v>-128079.25142094126</v>
+        <v>-124348.78778732159</v>
       </c>
       <c r="AR5" s="10">
         <f t="shared" si="1"/>
-        <v>-134483.21399198833</v>
+        <v>-130566.22717668768</v>
       </c>
       <c r="AS5" s="10">
         <f t="shared" si="1"/>
-        <v>-141207.37469158776</v>
+        <v>-137094.53853552206</v>
       </c>
       <c r="AT5" s="10">
         <f t="shared" si="1"/>
-        <v>-148267.74342616714</v>
+        <v>-143949.26546229818</v>
       </c>
     </row>
     <row r="6" spans="1:300" x14ac:dyDescent="0.25">
@@ -4812,7 +4916,7 @@
       </c>
       <c r="B6" s="18">
         <f>B4*B5</f>
-        <v>169607.19999999998</v>
+        <v>186158.69999999998</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>53</v>
@@ -4882,10 +4986,13 @@
         <v>11695</v>
       </c>
       <c r="T6" s="10">
-        <f t="shared" ref="T6" si="4">SUM(T4:T5)</f>
+        <f t="shared" ref="T6:U6" si="4">SUM(T4:T5)</f>
         <v>11085</v>
       </c>
-      <c r="U6" s="10"/>
+      <c r="U6" s="10">
+        <f t="shared" si="4"/>
+        <v>11445</v>
+      </c>
       <c r="V6" s="10"/>
       <c r="W6" s="10"/>
       <c r="X6" s="10"/>
@@ -4936,43 +5043,43 @@
       </c>
       <c r="AK6" s="12">
         <f t="shared" si="6"/>
-        <v>47074.1106</v>
+        <v>45703.01999999999</v>
       </c>
       <c r="AL6" s="10">
         <f t="shared" si="6"/>
-        <v>49427.816130000007</v>
+        <v>47988.171000000002</v>
       </c>
       <c r="AM6" s="10">
         <f t="shared" si="6"/>
-        <v>51899.206936500006</v>
+        <v>50387.579549999995</v>
       </c>
       <c r="AN6" s="10">
         <f t="shared" si="6"/>
-        <v>54494.167283325005</v>
+        <v>52906.958527499999</v>
       </c>
       <c r="AO6" s="10">
         <f t="shared" si="6"/>
-        <v>57218.875647491252</v>
+        <v>55552.306453875004</v>
       </c>
       <c r="AP6" s="10">
         <f t="shared" si="6"/>
-        <v>60079.81942986582</v>
+        <v>58329.92177656875</v>
       </c>
       <c r="AQ6" s="10">
         <f t="shared" si="6"/>
-        <v>63083.810401359107</v>
+        <v>61246.41786539719</v>
       </c>
       <c r="AR6" s="10">
         <f t="shared" si="6"/>
-        <v>66238.000921427069</v>
+        <v>64308.738758667052</v>
       </c>
       <c r="AS6" s="10">
         <f t="shared" si="6"/>
-        <v>69549.900967498426</v>
+        <v>67524.175696600403</v>
       </c>
       <c r="AT6" s="10">
         <f t="shared" si="6"/>
-        <v>73027.396015873353</v>
+        <v>70900.384481430432</v>
       </c>
     </row>
     <row r="7" spans="1:300" x14ac:dyDescent="0.25">
@@ -5037,7 +5144,9 @@
       <c r="T7" s="10">
         <v>-6482</v>
       </c>
-      <c r="U7" s="10"/>
+      <c r="U7" s="10">
+        <v>-6760</v>
+      </c>
       <c r="V7" s="10"/>
       <c r="W7" s="10"/>
       <c r="X7" s="10"/>
@@ -5084,44 +5193,44 @@
         <v>-26571</v>
       </c>
       <c r="AK7" s="12">
-        <f>AJ7*1.03</f>
-        <v>-27368.13</v>
+        <f>AJ7*1.04</f>
+        <v>-27633.84</v>
       </c>
       <c r="AL7" s="10">
         <f>AK7*1.05</f>
-        <v>-28736.536500000002</v>
+        <v>-29015.532000000003</v>
       </c>
       <c r="AM7" s="10">
         <f t="shared" ref="AM7:AT7" si="7">AL7*1.05</f>
-        <v>-30173.363325000002</v>
+        <v>-30466.308600000004</v>
       </c>
       <c r="AN7" s="10">
         <f t="shared" si="7"/>
-        <v>-31682.031491250003</v>
+        <v>-31989.624030000006</v>
       </c>
       <c r="AO7" s="10">
         <f t="shared" si="7"/>
-        <v>-33266.133065812508</v>
+        <v>-33589.105231500005</v>
       </c>
       <c r="AP7" s="10">
         <f t="shared" si="7"/>
-        <v>-34929.439719103138</v>
+        <v>-35268.560493075005</v>
       </c>
       <c r="AQ7" s="10">
         <f t="shared" si="7"/>
-        <v>-36675.911705058294</v>
+        <v>-37031.988517728758</v>
       </c>
       <c r="AR7" s="10">
         <f t="shared" si="7"/>
-        <v>-38509.707290311213</v>
+        <v>-38883.587943615195</v>
       </c>
       <c r="AS7" s="10">
         <f t="shared" si="7"/>
-        <v>-40435.192654826773</v>
+        <v>-40827.767340795959</v>
       </c>
       <c r="AT7" s="10">
         <f t="shared" si="7"/>
-        <v>-42456.952287568114</v>
+        <v>-42869.155707835758</v>
       </c>
     </row>
     <row r="8" spans="1:300" x14ac:dyDescent="0.25">
@@ -5186,7 +5295,9 @@
       <c r="T8" s="10">
         <v>-179</v>
       </c>
-      <c r="U8" s="10"/>
+      <c r="U8" s="10">
+        <v>-581</v>
+      </c>
       <c r="V8" s="10"/>
       <c r="W8" s="10"/>
       <c r="X8" s="10"/>
@@ -5262,7 +5373,7 @@
       </c>
       <c r="B9" s="27">
         <f>B6-B7+B8</f>
-        <v>201177.19999999998</v>
+        <v>217728.69999999998</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>56</v>
@@ -5332,13 +5443,16 @@
         <v>5117</v>
       </c>
       <c r="T9" s="9">
-        <f t="shared" ref="T9" si="10">SUM(T6:T8)</f>
+        <f t="shared" ref="T9:U9" si="10">SUM(T6:T8)</f>
         <v>4424</v>
       </c>
-      <c r="U9" s="9"/>
+      <c r="U9" s="9">
+        <f t="shared" si="10"/>
+        <v>4104</v>
+      </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
+      <c r="X9" s="10"/>
       <c r="Y9" s="10"/>
       <c r="Z9" s="9">
         <f t="shared" ref="Z9:AI9" si="11">SUM(Z6:Z8)</f>
@@ -5386,43 +5500,43 @@
       </c>
       <c r="AK9" s="11">
         <f t="shared" si="12"/>
-        <v>19705.980599999999</v>
+        <v>18069.179999999989</v>
       </c>
       <c r="AL9" s="9">
         <f t="shared" si="12"/>
-        <v>20691.279630000005</v>
+        <v>18972.638999999999</v>
       </c>
       <c r="AM9" s="9">
         <f t="shared" si="12"/>
-        <v>21725.843611500004</v>
+        <v>19921.270949999991</v>
       </c>
       <c r="AN9" s="9">
         <f t="shared" si="12"/>
-        <v>22812.135792075002</v>
+        <v>20917.334497499993</v>
       </c>
       <c r="AO9" s="9">
         <f t="shared" si="12"/>
-        <v>23952.742581678744</v>
+        <v>21963.201222374999</v>
       </c>
       <c r="AP9" s="9">
         <f t="shared" si="12"/>
-        <v>25150.379710762681</v>
+        <v>23061.361283493745</v>
       </c>
       <c r="AQ9" s="9">
         <f t="shared" si="12"/>
-        <v>26407.898696300814</v>
+        <v>24214.429347668432</v>
       </c>
       <c r="AR9" s="9">
         <f t="shared" si="12"/>
-        <v>27728.293631115856</v>
+        <v>25425.150815051857</v>
       </c>
       <c r="AS9" s="9">
         <f t="shared" si="12"/>
-        <v>29114.708312671653</v>
+        <v>26696.408355804444</v>
       </c>
       <c r="AT9" s="9">
         <f t="shared" si="12"/>
-        <v>30570.443728305239</v>
+        <v>28031.228773594674</v>
       </c>
     </row>
     <row r="10" spans="1:300" x14ac:dyDescent="0.25">
@@ -5480,7 +5594,9 @@
       <c r="T10" s="10">
         <v>-245</v>
       </c>
-      <c r="U10" s="10"/>
+      <c r="U10" s="10">
+        <v>-259</v>
+      </c>
       <c r="V10" s="10"/>
       <c r="W10" s="10"/>
       <c r="X10" s="10"/>
@@ -5631,10 +5747,13 @@
         <v>4885</v>
       </c>
       <c r="T11" s="9">
-        <f t="shared" ref="T11" si="16">SUM(T9:T10)</f>
+        <f t="shared" ref="T11:U11" si="16">SUM(T9:T10)</f>
         <v>4179</v>
       </c>
-      <c r="U11" s="9"/>
+      <c r="U11" s="9">
+        <f t="shared" si="16"/>
+        <v>3845</v>
+      </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
       <c r="X11" s="9"/>
@@ -5685,46 +5804,53 @@
       </c>
       <c r="AK11" s="11">
         <f t="shared" si="18"/>
-        <v>18724.260599999998</v>
+        <v>17087.459999999988</v>
       </c>
       <c r="AL11" s="9">
         <f t="shared" si="18"/>
-        <v>19699.742430000006</v>
+        <v>17981.1018</v>
       </c>
       <c r="AM11" s="9">
         <f t="shared" si="18"/>
-        <v>20724.391039500006</v>
+        <v>18919.818377999993</v>
       </c>
       <c r="AN11" s="9">
         <f t="shared" si="18"/>
-        <v>21800.668694355001</v>
+        <v>19905.867399779992</v>
       </c>
       <c r="AO11" s="9">
         <f t="shared" si="18"/>
-        <v>22931.160812981543</v>
+        <v>20941.619453677798</v>
       </c>
       <c r="AP11" s="9">
         <f t="shared" si="18"/>
-        <v>24118.58212437851</v>
+        <v>22029.563697109574</v>
       </c>
       <c r="AQ11" s="9">
         <f t="shared" si="18"/>
-        <v>25365.783134052799</v>
+        <v>23172.313785420418</v>
       </c>
       <c r="AR11" s="9">
         <f t="shared" si="18"/>
-        <v>26675.756913245361</v>
+        <v>24372.614097181362</v>
       </c>
       <c r="AS11" s="9">
         <f t="shared" si="18"/>
-        <v>28051.646227622456</v>
+        <v>25633.346270755246</v>
       </c>
       <c r="AT11" s="9">
         <f t="shared" si="18"/>
-        <v>29496.751022405548</v>
+        <v>26957.536067694982</v>
       </c>
     </row>
     <row r="12" spans="1:300" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B12" s="67">
+        <f>(B8-B7)/AK9</f>
+        <v>1.7471739171340381</v>
+      </c>
       <c r="C12" s="2" t="s">
         <v>59</v>
       </c>
@@ -5779,7 +5905,9 @@
       <c r="T12" s="10">
         <v>-4</v>
       </c>
-      <c r="U12" s="10"/>
+      <c r="U12" s="10">
+        <v>37</v>
+      </c>
       <c r="V12" s="10"/>
       <c r="W12" s="10"/>
       <c r="X12" s="10"/>
@@ -5903,7 +6031,9 @@
       <c r="T13" s="10">
         <v>-250</v>
       </c>
-      <c r="U13" s="10"/>
+      <c r="U13" s="10">
+        <v>-307</v>
+      </c>
       <c r="V13" s="10"/>
       <c r="W13" s="10"/>
       <c r="X13" s="10"/>
@@ -6049,10 +6179,13 @@
         <v>4581</v>
       </c>
       <c r="T14" s="10">
-        <f t="shared" ref="T14" si="21">SUM(T11:T13)</f>
+        <f t="shared" ref="T14:U14" si="21">SUM(T11:T13)</f>
         <v>3925</v>
       </c>
-      <c r="U14" s="10"/>
+      <c r="U14" s="10">
+        <f t="shared" si="21"/>
+        <v>3575</v>
+      </c>
       <c r="V14" s="10"/>
       <c r="W14" s="10"/>
       <c r="X14" s="10"/>
@@ -6103,43 +6236,43 @@
       </c>
       <c r="AK14" s="12">
         <f t="shared" si="23"/>
-        <v>18724.260599999998</v>
+        <v>17087.459999999988</v>
       </c>
       <c r="AL14" s="10">
         <f t="shared" si="23"/>
-        <v>19699.742430000006</v>
+        <v>17981.1018</v>
       </c>
       <c r="AM14" s="10">
         <f t="shared" si="23"/>
-        <v>20724.391039500006</v>
+        <v>18919.818377999993</v>
       </c>
       <c r="AN14" s="10">
         <f t="shared" si="23"/>
-        <v>21800.668694355001</v>
+        <v>19905.867399779992</v>
       </c>
       <c r="AO14" s="10">
         <f t="shared" si="23"/>
-        <v>22931.160812981543</v>
+        <v>20941.619453677798</v>
       </c>
       <c r="AP14" s="10">
         <f t="shared" si="23"/>
-        <v>24118.58212437851</v>
+        <v>22029.563697109574</v>
       </c>
       <c r="AQ14" s="10">
         <f t="shared" si="23"/>
-        <v>25365.783134052799</v>
+        <v>23172.313785420418</v>
       </c>
       <c r="AR14" s="10">
         <f t="shared" si="23"/>
-        <v>26675.756913245361</v>
+        <v>24372.614097181362</v>
       </c>
       <c r="AS14" s="10">
         <f t="shared" si="23"/>
-        <v>28051.646227622456</v>
+        <v>25633.346270755246</v>
       </c>
       <c r="AT14" s="10">
         <f t="shared" si="23"/>
-        <v>29496.751022405548</v>
+        <v>26957.536067694982</v>
       </c>
     </row>
     <row r="15" spans="1:300" x14ac:dyDescent="0.25">
@@ -6197,7 +6330,9 @@
       <c r="T15" s="10">
         <v>-1041</v>
       </c>
-      <c r="U15" s="10"/>
+      <c r="U15" s="10">
+        <v>-883</v>
+      </c>
       <c r="V15" s="10"/>
       <c r="W15" s="10"/>
       <c r="X15" s="10"/>
@@ -6237,43 +6372,43 @@
       </c>
       <c r="AK15" s="12">
         <f>AK14*-0.2</f>
-        <v>-3744.8521199999996</v>
+        <v>-3417.4919999999979</v>
       </c>
       <c r="AL15" s="10">
         <f t="shared" ref="AL15:AT15" si="24">AL14*-0.2</f>
-        <v>-3939.9484860000011</v>
+        <v>-3596.2203600000003</v>
       </c>
       <c r="AM15" s="10">
         <f t="shared" si="24"/>
-        <v>-4144.8782079000011</v>
+        <v>-3783.9636755999986</v>
       </c>
       <c r="AN15" s="10">
         <f t="shared" si="24"/>
-        <v>-4360.1337388710008</v>
+        <v>-3981.1734799559986</v>
       </c>
       <c r="AO15" s="10">
         <f t="shared" si="24"/>
-        <v>-4586.2321625963086</v>
+        <v>-4188.3238907355599</v>
       </c>
       <c r="AP15" s="10">
         <f t="shared" si="24"/>
-        <v>-4823.7164248757026</v>
+        <v>-4405.9127394219149</v>
       </c>
       <c r="AQ15" s="10">
         <f t="shared" si="24"/>
-        <v>-5073.1566268105598</v>
+        <v>-4634.4627570840839</v>
       </c>
       <c r="AR15" s="10">
         <f t="shared" si="24"/>
-        <v>-5335.1513826490727</v>
+        <v>-4874.5228194362726</v>
       </c>
       <c r="AS15" s="10">
         <f t="shared" si="24"/>
-        <v>-5610.3292455244919</v>
+        <v>-5126.6692541510492</v>
       </c>
       <c r="AT15" s="10">
         <f t="shared" si="24"/>
-        <v>-5899.3502044811103</v>
+        <v>-5391.5072135389964</v>
       </c>
     </row>
     <row r="16" spans="1:300" x14ac:dyDescent="0.25">
@@ -6345,10 +6480,13 @@
         <v>3355</v>
       </c>
       <c r="T16" s="9">
-        <f t="shared" ref="T16" si="27">SUM(T14:T15)</f>
+        <f t="shared" ref="T16:U16" si="27">SUM(T14:T15)</f>
         <v>2884</v>
       </c>
-      <c r="U16" s="9"/>
+      <c r="U16" s="9">
+        <f t="shared" si="27"/>
+        <v>2692</v>
+      </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
       <c r="X16" s="9"/>
@@ -6399,1062 +6537,1062 @@
       </c>
       <c r="AK16" s="11">
         <f t="shared" si="29"/>
-        <v>14979.408479999998</v>
+        <v>13669.96799999999</v>
       </c>
       <c r="AL16" s="9">
         <f t="shared" si="29"/>
-        <v>15759.793944000005</v>
+        <v>14384.881440000001</v>
       </c>
       <c r="AM16" s="9">
         <f t="shared" si="29"/>
-        <v>16579.512831600005</v>
+        <v>15135.854702399994</v>
       </c>
       <c r="AN16" s="9">
         <f t="shared" si="29"/>
-        <v>17440.534955484</v>
+        <v>15924.693919823994</v>
       </c>
       <c r="AO16" s="9">
         <f t="shared" si="29"/>
-        <v>18344.928650385235</v>
+        <v>16753.295562942239</v>
       </c>
       <c r="AP16" s="9">
         <f t="shared" si="29"/>
-        <v>19294.865699502807</v>
+        <v>17623.65095768766</v>
       </c>
       <c r="AQ16" s="9">
         <f t="shared" si="29"/>
-        <v>20292.626507242239</v>
+        <v>18537.851028336336</v>
       </c>
       <c r="AR16" s="9">
         <f t="shared" si="29"/>
-        <v>21340.605530596287</v>
+        <v>19498.09127774509</v>
       </c>
       <c r="AS16" s="9">
         <f t="shared" si="29"/>
-        <v>22441.316982097964</v>
+        <v>20506.677016604197</v>
       </c>
       <c r="AT16" s="9">
         <f t="shared" si="29"/>
-        <v>23597.400817924437</v>
+        <v>21566.028854155986</v>
       </c>
       <c r="AU16" s="9">
         <f>AT16*(1+$AW$20)</f>
-        <v>23361.426809745193</v>
+        <v>21350.368565614426</v>
       </c>
       <c r="AV16" s="9">
         <f t="shared" ref="AV16:DG16" si="30">AU16*(1+$AW$20)</f>
-        <v>23127.812541647741</v>
+        <v>21136.864879958281</v>
       </c>
       <c r="AW16" s="9">
         <f t="shared" si="30"/>
-        <v>22896.534416231265</v>
+        <v>20925.496231158697</v>
       </c>
       <c r="AX16" s="9">
         <f t="shared" si="30"/>
-        <v>22667.569072068953</v>
+        <v>20716.241268847109</v>
       </c>
       <c r="AY16" s="9">
         <f t="shared" si="30"/>
-        <v>22440.893381348262</v>
+        <v>20509.078856158638</v>
       </c>
       <c r="AZ16" s="9">
         <f t="shared" si="30"/>
-        <v>22216.484447534778</v>
+        <v>20303.988067597053</v>
       </c>
       <c r="BA16" s="9">
         <f t="shared" si="30"/>
-        <v>21994.31960305943</v>
+        <v>20100.948186921083</v>
       </c>
       <c r="BB16" s="9">
         <f t="shared" si="30"/>
-        <v>21774.376407028834</v>
+        <v>19899.938705051871</v>
       </c>
       <c r="BC16" s="9">
         <f t="shared" si="30"/>
-        <v>21556.632642958546</v>
+        <v>19700.93931800135</v>
       </c>
       <c r="BD16" s="9">
         <f t="shared" si="30"/>
-        <v>21341.066316528959</v>
+        <v>19503.929924821336</v>
       </c>
       <c r="BE16" s="9">
         <f t="shared" si="30"/>
-        <v>21127.655653363669</v>
+        <v>19308.890625573124</v>
       </c>
       <c r="BF16" s="9">
         <f t="shared" si="30"/>
-        <v>20916.379096830031</v>
+        <v>19115.801719317391</v>
       </c>
       <c r="BG16" s="9">
         <f t="shared" si="30"/>
-        <v>20707.21530586173</v>
+        <v>18924.643702124216</v>
       </c>
       <c r="BH16" s="9">
         <f t="shared" si="30"/>
-        <v>20500.143152803113</v>
+        <v>18735.397265102973</v>
       </c>
       <c r="BI16" s="9">
         <f t="shared" si="30"/>
-        <v>20295.141721275082</v>
+        <v>18548.043292451941</v>
       </c>
       <c r="BJ16" s="9">
         <f t="shared" si="30"/>
-        <v>20092.190304062333</v>
+        <v>18362.562859527421</v>
       </c>
       <c r="BK16" s="9">
         <f t="shared" si="30"/>
-        <v>19891.268401021709</v>
+        <v>18178.937230932148</v>
       </c>
       <c r="BL16" s="9">
         <f t="shared" si="30"/>
-        <v>19692.355717011491</v>
+        <v>17997.147858622826</v>
       </c>
       <c r="BM16" s="9">
         <f t="shared" si="30"/>
-        <v>19495.432159841377</v>
+        <v>17817.176380036599</v>
       </c>
       <c r="BN16" s="9">
         <f t="shared" si="30"/>
-        <v>19300.477838242965</v>
+        <v>17639.004616236234</v>
       </c>
       <c r="BO16" s="9">
         <f t="shared" si="30"/>
-        <v>19107.473059860535</v>
+        <v>17462.614570073871</v>
       </c>
       <c r="BP16" s="9">
         <f t="shared" si="30"/>
-        <v>18916.39832926193</v>
+        <v>17287.988424373132</v>
       </c>
       <c r="BQ16" s="9">
         <f t="shared" si="30"/>
-        <v>18727.234345969311</v>
+        <v>17115.1085401294</v>
       </c>
       <c r="BR16" s="9">
         <f t="shared" si="30"/>
-        <v>18539.962002509619</v>
+        <v>16943.957454728104</v>
       </c>
       <c r="BS16" s="9">
         <f t="shared" si="30"/>
-        <v>18354.562382484524</v>
+        <v>16774.517880180822</v>
       </c>
       <c r="BT16" s="9">
         <f t="shared" si="30"/>
-        <v>18171.01675865968</v>
+        <v>16606.772701379014</v>
       </c>
       <c r="BU16" s="9">
         <f t="shared" si="30"/>
-        <v>17989.306591073084</v>
+        <v>16440.704974365224</v>
       </c>
       <c r="BV16" s="9">
         <f t="shared" si="30"/>
-        <v>17809.413525162352</v>
+        <v>16276.297924621571</v>
       </c>
       <c r="BW16" s="9">
         <f t="shared" si="30"/>
-        <v>17631.319389910728</v>
+        <v>16113.534945375355</v>
       </c>
       <c r="BX16" s="9">
         <f t="shared" si="30"/>
-        <v>17455.006196011622</v>
+        <v>15952.399595921601</v>
       </c>
       <c r="BY16" s="9">
         <f t="shared" si="30"/>
-        <v>17280.456134051507</v>
+        <v>15792.875599962385</v>
       </c>
       <c r="BZ16" s="9">
         <f t="shared" si="30"/>
-        <v>17107.651572710991</v>
+        <v>15634.94684396276</v>
       </c>
       <c r="CA16" s="9">
         <f t="shared" si="30"/>
-        <v>16936.575056983882</v>
+        <v>15478.597375523132</v>
       </c>
       <c r="CB16" s="9">
         <f t="shared" si="30"/>
-        <v>16767.209306414043</v>
+        <v>15323.8114017679</v>
       </c>
       <c r="CC16" s="9">
         <f t="shared" si="30"/>
-        <v>16599.5372133499</v>
+        <v>15170.573287750221</v>
       </c>
       <c r="CD16" s="9">
         <f t="shared" si="30"/>
-        <v>16433.5418412164</v>
+        <v>15018.867554872719</v>
       </c>
       <c r="CE16" s="9">
         <f t="shared" si="30"/>
-        <v>16269.206422804236</v>
+        <v>14868.678879323992</v>
       </c>
       <c r="CF16" s="9">
         <f t="shared" si="30"/>
-        <v>16106.514358576194</v>
+        <v>14719.992090530752</v>
       </c>
       <c r="CG16" s="9">
         <f t="shared" si="30"/>
-        <v>15945.449214990433</v>
+        <v>14572.792169625443</v>
       </c>
       <c r="CH16" s="9">
         <f t="shared" si="30"/>
-        <v>15785.994722840529</v>
+        <v>14427.064247929189</v>
       </c>
       <c r="CI16" s="9">
         <f t="shared" si="30"/>
-        <v>15628.134775612123</v>
+        <v>14282.793605449897</v>
       </c>
       <c r="CJ16" s="9">
         <f t="shared" si="30"/>
-        <v>15471.853427856002</v>
+        <v>14139.965669395398</v>
       </c>
       <c r="CK16" s="9">
         <f t="shared" si="30"/>
-        <v>15317.134893577442</v>
+        <v>13998.566012701443</v>
       </c>
       <c r="CL16" s="9">
         <f t="shared" si="30"/>
-        <v>15163.963544641667</v>
+        <v>13858.580352574429</v>
       </c>
       <c r="CM16" s="9">
         <f t="shared" si="30"/>
-        <v>15012.323909195251</v>
+        <v>13719.994549048684</v>
       </c>
       <c r="CN16" s="9">
         <f t="shared" si="30"/>
-        <v>14862.200670103299</v>
+        <v>13582.794603558197</v>
       </c>
       <c r="CO16" s="9">
         <f t="shared" si="30"/>
-        <v>14713.578663402266</v>
+        <v>13446.966657522615</v>
       </c>
       <c r="CP16" s="9">
         <f t="shared" si="30"/>
-        <v>14566.442876768244</v>
+        <v>13312.496990947388</v>
       </c>
       <c r="CQ16" s="9">
         <f t="shared" si="30"/>
-        <v>14420.778448000561</v>
+        <v>13179.372021037914</v>
       </c>
       <c r="CR16" s="9">
         <f t="shared" si="30"/>
-        <v>14276.570663520555</v>
+        <v>13047.578300827536</v>
       </c>
       <c r="CS16" s="9">
         <f t="shared" si="30"/>
-        <v>14133.804956885349</v>
+        <v>12917.102517819259</v>
       </c>
       <c r="CT16" s="9">
         <f t="shared" si="30"/>
-        <v>13992.466907316495</v>
+        <v>12787.931492641066</v>
       </c>
       <c r="CU16" s="9">
         <f t="shared" si="30"/>
-        <v>13852.54223824333</v>
+        <v>12660.052177714655</v>
       </c>
       <c r="CV16" s="9">
         <f t="shared" si="30"/>
-        <v>13714.016815860896</v>
+        <v>12533.451655937508</v>
       </c>
       <c r="CW16" s="9">
         <f t="shared" si="30"/>
-        <v>13576.876647702287</v>
+        <v>12408.117139378133</v>
       </c>
       <c r="CX16" s="9">
         <f t="shared" si="30"/>
-        <v>13441.107881225264</v>
+        <v>12284.035967984351</v>
       </c>
       <c r="CY16" s="9">
         <f t="shared" si="30"/>
-        <v>13306.696802413011</v>
+        <v>12161.195608304508</v>
       </c>
       <c r="CZ16" s="9">
         <f t="shared" si="30"/>
-        <v>13173.629834388881</v>
+        <v>12039.583652221463</v>
       </c>
       <c r="DA16" s="9">
         <f t="shared" si="30"/>
-        <v>13041.893536044992</v>
+        <v>11919.187815699248</v>
       </c>
       <c r="DB16" s="9">
         <f t="shared" si="30"/>
-        <v>12911.474600684542</v>
+        <v>11799.995937542255</v>
       </c>
       <c r="DC16" s="9">
         <f t="shared" si="30"/>
-        <v>12782.359854677696</v>
+        <v>11681.995978166833</v>
       </c>
       <c r="DD16" s="9">
         <f t="shared" si="30"/>
-        <v>12654.536256130919</v>
+        <v>11565.176018385164</v>
       </c>
       <c r="DE16" s="9">
         <f t="shared" si="30"/>
-        <v>12527.990893569609</v>
+        <v>11449.524258201312</v>
       </c>
       <c r="DF16" s="9">
         <f t="shared" si="30"/>
-        <v>12402.710984633914</v>
+        <v>11335.029015619299</v>
       </c>
       <c r="DG16" s="9">
         <f t="shared" si="30"/>
-        <v>12278.683874787574</v>
+        <v>11221.678725463105</v>
       </c>
       <c r="DH16" s="9">
         <f t="shared" ref="DH16:FS16" si="31">DG16*(1+$AW$20)</f>
-        <v>12155.897036039698</v>
+        <v>11109.461938208475</v>
       </c>
       <c r="DI16" s="9">
         <f t="shared" si="31"/>
-        <v>12034.338065679302</v>
+        <v>10998.367318826389</v>
       </c>
       <c r="DJ16" s="9">
         <f t="shared" si="31"/>
-        <v>11913.994685022508</v>
+        <v>10888.383645638125</v>
       </c>
       <c r="DK16" s="9">
         <f t="shared" si="31"/>
-        <v>11794.854738172282</v>
+        <v>10779.499809181743</v>
       </c>
       <c r="DL16" s="9">
         <f t="shared" si="31"/>
-        <v>11676.90619079056</v>
+        <v>10671.704811089925</v>
       </c>
       <c r="DM16" s="9">
         <f t="shared" si="31"/>
-        <v>11560.137128882654</v>
+        <v>10564.987762979026</v>
       </c>
       <c r="DN16" s="9">
         <f t="shared" si="31"/>
-        <v>11444.535757593827</v>
+        <v>10459.337885349236</v>
       </c>
       <c r="DO16" s="9">
         <f t="shared" si="31"/>
-        <v>11330.090400017889</v>
+        <v>10354.744506495743</v>
       </c>
       <c r="DP16" s="9">
         <f t="shared" si="31"/>
-        <v>11216.789496017709</v>
+        <v>10251.197061430785</v>
       </c>
       <c r="DQ16" s="9">
         <f t="shared" si="31"/>
-        <v>11104.621601057532</v>
+        <v>10148.685090816476</v>
       </c>
       <c r="DR16" s="9">
         <f t="shared" si="31"/>
-        <v>10993.575385046955</v>
+        <v>10047.198239908312</v>
       </c>
       <c r="DS16" s="9">
         <f t="shared" si="31"/>
-        <v>10883.639631196485</v>
+        <v>9946.7262575092282</v>
       </c>
       <c r="DT16" s="9">
         <f t="shared" si="31"/>
-        <v>10774.803234884521</v>
+        <v>9847.2589949341364</v>
       </c>
       <c r="DU16" s="9">
         <f t="shared" si="31"/>
-        <v>10667.055202535676</v>
+        <v>9748.7864049847958</v>
       </c>
       <c r="DV16" s="9">
         <f t="shared" si="31"/>
-        <v>10560.384650510319</v>
+        <v>9651.2985409349476</v>
       </c>
       <c r="DW16" s="9">
         <f t="shared" si="31"/>
-        <v>10454.780804005217</v>
+        <v>9554.7855555255974</v>
       </c>
       <c r="DX16" s="9">
         <f t="shared" si="31"/>
-        <v>10350.232995965165</v>
+        <v>9459.2376999703411</v>
       </c>
       <c r="DY16" s="9">
         <f t="shared" si="31"/>
-        <v>10246.730666005513</v>
+        <v>9364.6453229706367</v>
       </c>
       <c r="DZ16" s="9">
         <f t="shared" si="31"/>
-        <v>10144.263359345458</v>
+        <v>9270.9988697409299</v>
       </c>
       <c r="EA16" s="9">
         <f t="shared" si="31"/>
-        <v>10042.820725752003</v>
+        <v>9178.2888810435197</v>
       </c>
       <c r="EB16" s="9">
         <f t="shared" si="31"/>
-        <v>9942.3925184944819</v>
+        <v>9086.5059922330838</v>
       </c>
       <c r="EC16" s="9">
         <f t="shared" si="31"/>
-        <v>9842.968593309537</v>
+        <v>8995.6409323107528</v>
       </c>
       <c r="ED16" s="9">
         <f t="shared" si="31"/>
-        <v>9744.5389073764418</v>
+        <v>8905.6845229876453</v>
       </c>
       <c r="EE16" s="9">
         <f t="shared" si="31"/>
-        <v>9647.0935183026777</v>
+        <v>8816.6276777577696</v>
       </c>
       <c r="EF16" s="9">
         <f t="shared" si="31"/>
-        <v>9550.6225831196516</v>
+        <v>8728.4614009801917</v>
       </c>
       <c r="EG16" s="9">
         <f t="shared" si="31"/>
-        <v>9455.1163572884543</v>
+        <v>8641.176786970389</v>
       </c>
       <c r="EH16" s="9">
         <f t="shared" si="31"/>
-        <v>9360.565193715569</v>
+        <v>8554.7650191006851</v>
       </c>
       <c r="EI16" s="9">
         <f t="shared" si="31"/>
-        <v>9266.959541778413</v>
+        <v>8469.217368909678</v>
       </c>
       <c r="EJ16" s="9">
         <f t="shared" si="31"/>
-        <v>9174.2899463606282</v>
+        <v>8384.5251952205817</v>
       </c>
       <c r="EK16" s="9">
         <f t="shared" si="31"/>
-        <v>9082.5470468970216</v>
+        <v>8300.6799432683765</v>
       </c>
       <c r="EL16" s="9">
         <f t="shared" si="31"/>
-        <v>8991.7215764280518</v>
+        <v>8217.6731438356928</v>
       </c>
       <c r="EM16" s="9">
         <f t="shared" si="31"/>
-        <v>8901.8043606637711</v>
+        <v>8135.4964123973359</v>
       </c>
       <c r="EN16" s="9">
         <f t="shared" si="31"/>
-        <v>8812.7863170571327</v>
+        <v>8054.1414482733626</v>
       </c>
       <c r="EO16" s="9">
         <f t="shared" si="31"/>
-        <v>8724.6584538865609</v>
+        <v>7973.6000337906289</v>
       </c>
       <c r="EP16" s="9">
         <f t="shared" si="31"/>
-        <v>8637.4118693476958</v>
+        <v>7893.8640334527227</v>
       </c>
       <c r="EQ16" s="9">
         <f t="shared" si="31"/>
-        <v>8551.0377506542191</v>
+        <v>7814.9253931181956</v>
       </c>
       <c r="ER16" s="9">
         <f t="shared" si="31"/>
-        <v>8465.5273731476773</v>
+        <v>7736.7761391870135</v>
       </c>
       <c r="ES16" s="9">
         <f t="shared" si="31"/>
-        <v>8380.8720994162013</v>
+        <v>7659.4083777951437</v>
       </c>
       <c r="ET16" s="9">
         <f t="shared" si="31"/>
-        <v>8297.063378422039</v>
+        <v>7582.814294017192</v>
       </c>
       <c r="EU16" s="9">
         <f t="shared" si="31"/>
-        <v>8214.0927446378191</v>
+        <v>7506.9861510770197</v>
       </c>
       <c r="EV16" s="9">
         <f t="shared" si="31"/>
-        <v>8131.9518171914406</v>
+        <v>7431.9162895662494</v>
       </c>
       <c r="EW16" s="9">
         <f t="shared" si="31"/>
-        <v>8050.6322990195258</v>
+        <v>7357.5971266705865</v>
       </c>
       <c r="EX16" s="9">
         <f t="shared" si="31"/>
-        <v>7970.1259760293306</v>
+        <v>7284.0211554038806</v>
       </c>
       <c r="EY16" s="9">
         <f t="shared" si="31"/>
-        <v>7890.4247162690372</v>
+        <v>7211.1809438498422</v>
       </c>
       <c r="EZ16" s="9">
         <f t="shared" si="31"/>
-        <v>7811.5204691063464</v>
+        <v>7139.0691344113438</v>
       </c>
       <c r="FA16" s="9">
         <f t="shared" si="31"/>
-        <v>7733.4052644152825</v>
+        <v>7067.6784430672305</v>
       </c>
       <c r="FB16" s="9">
         <f t="shared" si="31"/>
-        <v>7656.07121177113</v>
+        <v>6997.0016586365582</v>
       </c>
       <c r="FC16" s="9">
         <f t="shared" si="31"/>
-        <v>7579.5104996534183</v>
+        <v>6927.0316420501922</v>
       </c>
       <c r="FD16" s="9">
         <f t="shared" si="31"/>
-        <v>7503.7153946568842</v>
+        <v>6857.76132562969</v>
       </c>
       <c r="FE16" s="9">
         <f t="shared" si="31"/>
-        <v>7428.6782407103155</v>
+        <v>6789.1837123733931</v>
       </c>
       <c r="FF16" s="9">
         <f t="shared" si="31"/>
-        <v>7354.3914583032119</v>
+        <v>6721.2918752496589</v>
       </c>
       <c r="FG16" s="9">
         <f t="shared" si="31"/>
-        <v>7280.8475437201796</v>
+        <v>6654.0789564971619</v>
       </c>
       <c r="FH16" s="9">
         <f t="shared" si="31"/>
-        <v>7208.0390682829775</v>
+        <v>6587.5381669321905</v>
       </c>
       <c r="FI16" s="9">
         <f t="shared" si="31"/>
-        <v>7135.9586776001479</v>
+        <v>6521.662785262869</v>
       </c>
       <c r="FJ16" s="9">
         <f t="shared" si="31"/>
-        <v>7064.5990908241465</v>
+        <v>6456.4461574102406</v>
       </c>
       <c r="FK16" s="9">
         <f t="shared" si="31"/>
-        <v>6993.9530999159051</v>
+        <v>6391.8816958361385</v>
       </c>
       <c r="FL16" s="9">
         <f t="shared" si="31"/>
-        <v>6924.0135689167464</v>
+        <v>6327.9628788777773</v>
       </c>
       <c r="FM16" s="9">
         <f t="shared" si="31"/>
-        <v>6854.7734332275786</v>
+        <v>6264.6832500889996</v>
       </c>
       <c r="FN16" s="9">
         <f t="shared" si="31"/>
-        <v>6786.2256988953031</v>
+        <v>6202.0364175881095</v>
       </c>
       <c r="FO16" s="9">
         <f t="shared" si="31"/>
-        <v>6718.3634419063501</v>
+        <v>6140.0160534122288</v>
       </c>
       <c r="FP16" s="9">
         <f t="shared" si="31"/>
-        <v>6651.1798074872868</v>
+        <v>6078.615892878106</v>
       </c>
       <c r="FQ16" s="9">
         <f t="shared" si="31"/>
-        <v>6584.668009412414</v>
+        <v>6017.8297339493247</v>
       </c>
       <c r="FR16" s="9">
         <f t="shared" si="31"/>
-        <v>6518.8213293182898</v>
+        <v>5957.6514366098318</v>
       </c>
       <c r="FS16" s="9">
         <f t="shared" si="31"/>
-        <v>6453.6331160251066</v>
+        <v>5898.0749222437335</v>
       </c>
       <c r="FT16" s="9">
         <f t="shared" ref="FT16:IE16" si="32">FS16*(1+$AW$20)</f>
-        <v>6389.0967848648552</v>
+        <v>5839.0941730212962</v>
       </c>
       <c r="FU16" s="9">
         <f t="shared" si="32"/>
-        <v>6325.2058170162063</v>
+        <v>5780.7032312910833</v>
       </c>
       <c r="FV16" s="9">
         <f t="shared" si="32"/>
-        <v>6261.9537588460444</v>
+        <v>5722.8961989781728</v>
       </c>
       <c r="FW16" s="9">
         <f t="shared" si="32"/>
-        <v>6199.3342212575835</v>
+        <v>5665.6672369883909</v>
       </c>
       <c r="FX16" s="9">
         <f t="shared" si="32"/>
-        <v>6137.3408790450076</v>
+        <v>5609.0105646185066</v>
       </c>
       <c r="FY16" s="9">
         <f t="shared" si="32"/>
-        <v>6075.9674702545572</v>
+        <v>5552.9204589723213</v>
       </c>
       <c r="FZ16" s="9">
         <f t="shared" si="32"/>
-        <v>6015.2077955520117</v>
+        <v>5497.3912543825982</v>
       </c>
       <c r="GA16" s="9">
         <f t="shared" si="32"/>
-        <v>5955.0557175964914</v>
+        <v>5442.4173418387718</v>
       </c>
       <c r="GB16" s="9">
         <f t="shared" si="32"/>
-        <v>5895.5051604205264</v>
+        <v>5387.9931684203839</v>
       </c>
       <c r="GC16" s="9">
         <f t="shared" si="32"/>
-        <v>5836.550108816321</v>
+        <v>5334.1132367361797</v>
       </c>
       <c r="GD16" s="9">
         <f t="shared" si="32"/>
-        <v>5778.184607728158</v>
+        <v>5280.772104368818</v>
       </c>
       <c r="GE16" s="9">
         <f t="shared" si="32"/>
-        <v>5720.4027616508765</v>
+        <v>5227.9643833251293</v>
       </c>
       <c r="GF16" s="9">
         <f t="shared" si="32"/>
-        <v>5663.1987340343676</v>
+        <v>5175.6847394918777</v>
       </c>
       <c r="GG16" s="9">
         <f t="shared" si="32"/>
-        <v>5606.566746694024</v>
+        <v>5123.9278920969591</v>
       </c>
       <c r="GH16" s="9">
         <f t="shared" si="32"/>
-        <v>5550.5010792270841</v>
+        <v>5072.6886131759893</v>
       </c>
       <c r="GI16" s="9">
         <f t="shared" si="32"/>
-        <v>5494.9960684348134</v>
+        <v>5021.9617270442295</v>
       </c>
       <c r="GJ16" s="9">
         <f t="shared" si="32"/>
-        <v>5440.0461077504651</v>
+        <v>4971.742109773787</v>
       </c>
       <c r="GK16" s="9">
         <f t="shared" si="32"/>
-        <v>5385.6456466729605</v>
+        <v>4922.0246886760488</v>
       </c>
       <c r="GL16" s="9">
         <f t="shared" si="32"/>
-        <v>5331.7891902062311</v>
+        <v>4872.8044417892879</v>
       </c>
       <c r="GM16" s="9">
         <f t="shared" si="32"/>
-        <v>5278.4712983041691</v>
+        <v>4824.0763973713947</v>
       </c>
       <c r="GN16" s="9">
         <f t="shared" si="32"/>
-        <v>5225.6865853211275</v>
+        <v>4775.8356333976808</v>
       </c>
       <c r="GO16" s="9">
         <f t="shared" si="32"/>
-        <v>5173.4297194679166</v>
+        <v>4728.0772770637041</v>
       </c>
       <c r="GP16" s="9">
         <f t="shared" si="32"/>
-        <v>5121.6954222732375</v>
+        <v>4680.7965042930673</v>
       </c>
       <c r="GQ16" s="9">
         <f t="shared" si="32"/>
-        <v>5070.4784680505054</v>
+        <v>4633.9885392501365</v>
       </c>
       <c r="GR16" s="9">
         <f t="shared" si="32"/>
-        <v>5019.7736833700001</v>
+        <v>4587.6486538576346</v>
       </c>
       <c r="GS16" s="9">
         <f t="shared" si="32"/>
-        <v>4969.5759465362999</v>
+        <v>4541.7721673190581</v>
       </c>
       <c r="GT16" s="9">
         <f t="shared" si="32"/>
-        <v>4919.8801870709367</v>
+        <v>4496.3544456458676</v>
       </c>
       <c r="GU16" s="9">
         <f t="shared" si="32"/>
-        <v>4870.6813852002269</v>
+        <v>4451.3909011894093</v>
       </c>
       <c r="GV16" s="9">
         <f t="shared" si="32"/>
-        <v>4821.9745713482243</v>
+        <v>4406.8769921775156</v>
       </c>
       <c r="GW16" s="9">
         <f t="shared" si="32"/>
-        <v>4773.7548256347418</v>
+        <v>4362.8082222557405</v>
       </c>
       <c r="GX16" s="9">
         <f t="shared" si="32"/>
-        <v>4726.0172773783943</v>
+        <v>4319.1801400331833</v>
       </c>
       <c r="GY16" s="9">
         <f t="shared" si="32"/>
-        <v>4678.7571046046105</v>
+        <v>4275.9883386328511</v>
       </c>
       <c r="GZ16" s="9">
         <f t="shared" si="32"/>
-        <v>4631.9695335585648</v>
+        <v>4233.2284552465226</v>
       </c>
       <c r="HA16" s="9">
         <f t="shared" si="32"/>
-        <v>4585.6498382229793</v>
+        <v>4190.8961706940572</v>
       </c>
       <c r="HB16" s="9">
         <f t="shared" si="32"/>
-        <v>4539.7933398407495</v>
+        <v>4148.9872089871169</v>
       </c>
       <c r="HC16" s="9">
         <f t="shared" si="32"/>
-        <v>4494.3954064423415</v>
+        <v>4107.497336897246</v>
       </c>
       <c r="HD16" s="9">
         <f t="shared" si="32"/>
-        <v>4449.451452377918</v>
+        <v>4066.4223635282733</v>
       </c>
       <c r="HE16" s="9">
         <f t="shared" si="32"/>
-        <v>4404.9569378541391</v>
+        <v>4025.7581398929906</v>
       </c>
       <c r="HF16" s="9">
         <f t="shared" si="32"/>
-        <v>4360.9073684755977</v>
+        <v>3985.5005584940604</v>
       </c>
       <c r="HG16" s="9">
         <f t="shared" si="32"/>
-        <v>4317.2982947908413</v>
+        <v>3945.6455529091199</v>
       </c>
       <c r="HH16" s="9">
         <f t="shared" si="32"/>
-        <v>4274.1253118429331</v>
+        <v>3906.1890973800287</v>
       </c>
       <c r="HI16" s="9">
         <f t="shared" si="32"/>
-        <v>4231.384058724504</v>
+        <v>3867.1272064062282</v>
       </c>
       <c r="HJ16" s="9">
         <f t="shared" si="32"/>
-        <v>4189.070218137259</v>
+        <v>3828.4559343421661</v>
       </c>
       <c r="HK16" s="9">
         <f t="shared" si="32"/>
-        <v>4147.179515955886</v>
+        <v>3790.1713749987443</v>
       </c>
       <c r="HL16" s="9">
         <f t="shared" si="32"/>
-        <v>4105.7077207963275</v>
+        <v>3752.2696612487571</v>
       </c>
       <c r="HM16" s="9">
         <f t="shared" si="32"/>
-        <v>4064.6506435883643</v>
+        <v>3714.7469646362697</v>
       </c>
       <c r="HN16" s="9">
         <f t="shared" si="32"/>
-        <v>4024.0041371524808</v>
+        <v>3677.5994949899068</v>
       </c>
       <c r="HO16" s="9">
         <f t="shared" si="32"/>
-        <v>3983.7640957809558</v>
+        <v>3640.8235000400077</v>
       </c>
       <c r="HP16" s="9">
         <f t="shared" si="32"/>
-        <v>3943.9264548231463</v>
+        <v>3604.4152650396077</v>
       </c>
       <c r="HQ16" s="9">
         <f t="shared" si="32"/>
-        <v>3904.4871902749146</v>
+        <v>3568.3711123892117</v>
       </c>
       <c r="HR16" s="9">
         <f t="shared" si="32"/>
-        <v>3865.4423183721656</v>
+        <v>3532.6874012653197</v>
       </c>
       <c r="HS16" s="9">
         <f t="shared" si="32"/>
-        <v>3826.7878951884441</v>
+        <v>3497.3605272526665</v>
       </c>
       <c r="HT16" s="9">
         <f t="shared" si="32"/>
-        <v>3788.5200162365595</v>
+        <v>3462.38692198014</v>
       </c>
       <c r="HU16" s="9">
         <f t="shared" si="32"/>
-        <v>3750.6348160741941</v>
+        <v>3427.7630527603387</v>
       </c>
       <c r="HV16" s="9">
         <f t="shared" si="32"/>
-        <v>3713.1284679134519</v>
+        <v>3393.4854222327353</v>
       </c>
       <c r="HW16" s="9">
         <f t="shared" si="32"/>
-        <v>3675.9971832343172</v>
+        <v>3359.5505680104079</v>
       </c>
       <c r="HX16" s="9">
         <f t="shared" si="32"/>
-        <v>3639.237211401974</v>
+        <v>3325.9550623303039</v>
       </c>
       <c r="HY16" s="9">
         <f t="shared" si="32"/>
-        <v>3602.8448392879541</v>
+        <v>3292.6955117070011</v>
       </c>
       <c r="HZ16" s="9">
         <f t="shared" si="32"/>
-        <v>3566.8163908950746</v>
+        <v>3259.768556589931</v>
       </c>
       <c r="IA16" s="9">
         <f t="shared" si="32"/>
-        <v>3531.148226986124</v>
+        <v>3227.1708710240318</v>
       </c>
       <c r="IB16" s="9">
         <f t="shared" si="32"/>
-        <v>3495.8367447162627</v>
+        <v>3194.8991623137913</v>
       </c>
       <c r="IC16" s="9">
         <f t="shared" si="32"/>
-        <v>3460.8783772690999</v>
+        <v>3162.9501706906535</v>
       </c>
       <c r="ID16" s="9">
         <f t="shared" si="32"/>
-        <v>3426.269593496409</v>
+        <v>3131.3206689837471</v>
       </c>
       <c r="IE16" s="9">
         <f t="shared" si="32"/>
-        <v>3392.0068975614449</v>
+        <v>3100.0074622939096</v>
       </c>
       <c r="IF16" s="9">
         <f t="shared" ref="IF16:KN16" si="33">IE16*(1+$AW$20)</f>
-        <v>3358.0868285858305</v>
+        <v>3069.0073876709703</v>
       </c>
       <c r="IG16" s="9">
         <f t="shared" si="33"/>
-        <v>3324.5059602999722</v>
+        <v>3038.3173137942604</v>
       </c>
       <c r="IH16" s="9">
         <f t="shared" si="33"/>
-        <v>3291.2609006969724</v>
+        <v>3007.9341406563176</v>
       </c>
       <c r="II16" s="9">
         <f t="shared" si="33"/>
-        <v>3258.3482916900025</v>
+        <v>2977.8547992497543</v>
       </c>
       <c r="IJ16" s="9">
         <f t="shared" si="33"/>
-        <v>3225.7648087731022</v>
+        <v>2948.0762512572569</v>
       </c>
       <c r="IK16" s="9">
         <f t="shared" si="33"/>
-        <v>3193.5071606853712</v>
+        <v>2918.5954887446842</v>
       </c>
       <c r="IL16" s="9">
         <f t="shared" si="33"/>
-        <v>3161.5720890785174</v>
+        <v>2889.4095338572374</v>
       </c>
       <c r="IM16" s="9">
         <f t="shared" si="33"/>
-        <v>3129.9563681877321</v>
+        <v>2860.5154385186652</v>
       </c>
       <c r="IN16" s="9">
         <f t="shared" si="33"/>
-        <v>3098.6568045058548</v>
+        <v>2831.9102841334784</v>
       </c>
       <c r="IO16" s="9">
         <f t="shared" si="33"/>
-        <v>3067.6702364607963</v>
+        <v>2803.5911812921436</v>
       </c>
       <c r="IP16" s="9">
         <f t="shared" si="33"/>
-        <v>3036.9935340961883</v>
+        <v>2775.5552694792223</v>
       </c>
       <c r="IQ16" s="9">
         <f t="shared" si="33"/>
-        <v>3006.6235987552263</v>
+        <v>2747.7997167844301</v>
       </c>
       <c r="IR16" s="9">
         <f t="shared" si="33"/>
-        <v>2976.557362767674</v>
+        <v>2720.3217196165856</v>
       </c>
       <c r="IS16" s="9">
         <f t="shared" si="33"/>
-        <v>2946.791789139997</v>
+        <v>2693.1185024204196</v>
       </c>
       <c r="IT16" s="9">
         <f t="shared" si="33"/>
-        <v>2917.3238712485972</v>
+        <v>2666.1873173962153</v>
       </c>
       <c r="IU16" s="9">
         <f t="shared" si="33"/>
-        <v>2888.1506325361111</v>
+        <v>2639.5254442222531</v>
       </c>
       <c r="IV16" s="9">
         <f t="shared" si="33"/>
-        <v>2859.2691262107501</v>
+        <v>2613.1301897800304</v>
       </c>
       <c r="IW16" s="9">
         <f t="shared" si="33"/>
-        <v>2830.6764349486425</v>
+        <v>2586.9988878822301</v>
       </c>
       <c r="IX16" s="9">
         <f t="shared" si="33"/>
-        <v>2802.3696705991561</v>
+        <v>2561.1288990034077</v>
       </c>
       <c r="IY16" s="9">
         <f t="shared" si="33"/>
-        <v>2774.3459738931647</v>
+        <v>2535.5176100133735</v>
       </c>
       <c r="IZ16" s="9">
         <f t="shared" si="33"/>
-        <v>2746.6025141542332</v>
+        <v>2510.16243391324</v>
       </c>
       <c r="JA16" s="9">
         <f t="shared" si="33"/>
-        <v>2719.1364890126906</v>
+        <v>2485.0608095741077</v>
       </c>
       <c r="JB16" s="9">
         <f t="shared" si="33"/>
-        <v>2691.9451241225638</v>
+        <v>2460.2102014783668</v>
       </c>
       <c r="JC16" s="9">
         <f t="shared" si="33"/>
-        <v>2665.0256728813383</v>
+        <v>2435.6080994635831</v>
       </c>
       <c r="JD16" s="9">
         <f t="shared" si="33"/>
-        <v>2638.3754161525248</v>
+        <v>2411.2520184689474</v>
       </c>
       <c r="JE16" s="9">
         <f t="shared" si="33"/>
-        <v>2611.9916619909995</v>
+        <v>2387.139498284258</v>
       </c>
       <c r="JF16" s="9">
         <f t="shared" si="33"/>
-        <v>2585.8717453710897</v>
+        <v>2363.2681033014155</v>
       </c>
       <c r="JG16" s="9">
         <f t="shared" si="33"/>
-        <v>2560.0130279173786</v>
+        <v>2339.6354222684013</v>
       </c>
       <c r="JH16" s="9">
         <f t="shared" si="33"/>
-        <v>2534.4128976382049</v>
+        <v>2316.2390680457174</v>
       </c>
       <c r="JI16" s="9">
         <f t="shared" si="33"/>
-        <v>2509.068768661823</v>
+        <v>2293.0766773652604</v>
       </c>
       <c r="JJ16" s="9">
         <f t="shared" si="33"/>
-        <v>2483.9780809752046</v>
+        <v>2270.1459105916078</v>
       </c>
       <c r="JK16" s="9">
         <f t="shared" si="33"/>
-        <v>2459.1383001654526</v>
+        <v>2247.4444514856918</v>
       </c>
       <c r="JL16" s="9">
         <f t="shared" si="33"/>
-        <v>2434.5469171637983</v>
+        <v>2224.9700069708351</v>
       </c>
       <c r="JM16" s="9">
         <f t="shared" si="33"/>
-        <v>2410.2014479921604</v>
+        <v>2202.7203069011266</v>
       </c>
       <c r="JN16" s="9">
         <f t="shared" si="33"/>
-        <v>2386.0994335122386</v>
+        <v>2180.6931038321154</v>
       </c>
       <c r="JO16" s="9">
         <f t="shared" si="33"/>
-        <v>2362.2384391771161</v>
+        <v>2158.8861727937942</v>
       </c>
       <c r="JP16" s="9">
         <f t="shared" si="33"/>
-        <v>2338.6160547853451</v>
+        <v>2137.2973110658563</v>
       </c>
       <c r="JQ16" s="9">
         <f t="shared" si="33"/>
-        <v>2315.2298942374919</v>
+        <v>2115.9243379551976</v>
       </c>
       <c r="JR16" s="9">
         <f t="shared" si="33"/>
-        <v>2292.0775952951171</v>
+        <v>2094.7650945756454</v>
       </c>
       <c r="JS16" s="9">
         <f t="shared" si="33"/>
-        <v>2269.1568193421658</v>
+        <v>2073.8174436298891</v>
       </c>
       <c r="JT16" s="9">
         <f t="shared" si="33"/>
-        <v>2246.4652511487443</v>
+        <v>2053.0792691935903</v>
       </c>
       <c r="JU16" s="9">
         <f t="shared" si="33"/>
-        <v>2224.0005986372566</v>
+        <v>2032.5484765016545</v>
       </c>
       <c r="JV16" s="9">
         <f t="shared" si="33"/>
-        <v>2201.7605926508841</v>
+        <v>2012.2229917366378</v>
       </c>
       <c r="JW16" s="9">
         <f t="shared" si="33"/>
-        <v>2179.742986724375</v>
+        <v>1992.1007618192714</v>
       </c>
       <c r="JX16" s="9">
         <f t="shared" si="33"/>
-        <v>2157.9455568571311</v>
+        <v>1972.1797542010786</v>
       </c>
       <c r="JY16" s="9">
         <f t="shared" si="33"/>
-        <v>2136.36610128856</v>
+        <v>1952.4579566590678</v>
       </c>
       <c r="JZ16" s="9">
         <f t="shared" si="33"/>
-        <v>2115.0024402756744</v>
+        <v>1932.933377092477</v>
       </c>
       <c r="KA16" s="9">
         <f t="shared" si="33"/>
-        <v>2093.8524158729178</v>
+        <v>1913.6040433215524</v>
       </c>
       <c r="KB16" s="9">
         <f t="shared" si="33"/>
-        <v>2072.9138917141886</v>
+        <v>1894.4680028883367</v>
       </c>
       <c r="KC16" s="9">
         <f t="shared" si="33"/>
-        <v>2052.1847527970467</v>
+        <v>1875.5233228594534</v>
       </c>
       <c r="KD16" s="9">
         <f t="shared" si="33"/>
-        <v>2031.6629052690762</v>
+        <v>1856.7680896308589</v>
       </c>
       <c r="KE16" s="9">
         <f t="shared" si="33"/>
-        <v>2011.3462762163854</v>
+        <v>1838.2004087345504</v>
       </c>
       <c r="KF16" s="9">
         <f t="shared" si="33"/>
-        <v>1991.2328134542215</v>
+        <v>1819.8184046472049</v>
       </c>
       <c r="KG16" s="9">
         <f t="shared" si="33"/>
-        <v>1971.3204853196794</v>
+        <v>1801.6202206007329</v>
       </c>
       <c r="KH16" s="9">
         <f t="shared" si="33"/>
-        <v>1951.6072804664825</v>
+        <v>1783.6040183947255</v>
       </c>
       <c r="KI16" s="9">
         <f t="shared" si="33"/>
-        <v>1932.0912076618176</v>
+        <v>1765.7679782107782</v>
       </c>
       <c r="KJ16" s="9">
         <f t="shared" si="33"/>
-        <v>1912.7702955851994</v>
+        <v>1748.1102984286704</v>
       </c>
       <c r="KK16" s="9">
         <f t="shared" si="33"/>
-        <v>1893.6425926293473</v>
+        <v>1730.6291954443836</v>
       </c>
       <c r="KL16" s="9">
         <f t="shared" si="33"/>
-        <v>1874.7061667030539</v>
+        <v>1713.3229034899398</v>
       </c>
       <c r="KM16" s="9">
         <f t="shared" si="33"/>
-        <v>1855.9591050360234</v>
+        <v>1696.1896744550404</v>
       </c>
       <c r="KN16" s="9">
         <f t="shared" si="33"/>
-        <v>1837.3995139856631</v>
-      </c>
-    </row>
-    <row r="17" spans="3:49" x14ac:dyDescent="0.25">
+        <v>1679.22777771049</v>
+      </c>
+    </row>
+    <row r="17" spans="2:49" x14ac:dyDescent="0.25">
       <c r="C17" s="2" t="s">
         <v>64</v>
       </c>
@@ -7509,6 +7647,9 @@
       <c r="T17" s="2">
         <v>681.9</v>
       </c>
+      <c r="U17" s="14">
+        <v>678.587806</v>
+      </c>
       <c r="Z17" s="2">
         <v>702.3</v>
       </c>
@@ -7573,7 +7714,7 @@
         <v>681.9</v>
       </c>
     </row>
-    <row r="18" spans="3:49" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:49" x14ac:dyDescent="0.25">
       <c r="C18" s="2" t="s">
         <v>65</v>
       </c>
@@ -7642,10 +7783,13 @@
         <v>4.9056879660769122</v>
       </c>
       <c r="T18" s="13">
-        <f t="shared" ref="T18" si="37">T16/T17</f>
+        <f t="shared" ref="T18:U18" si="37">T16/T17</f>
         <v>4.2293591435694387</v>
       </c>
-      <c r="U18" s="13"/>
+      <c r="U18" s="13">
+        <f t="shared" si="37"/>
+        <v>3.9670621490654963</v>
+      </c>
       <c r="V18" s="13"/>
       <c r="W18" s="13"/>
       <c r="Z18" s="13">
@@ -7694,46 +7838,46 @@
       </c>
       <c r="AK18" s="8">
         <f t="shared" ref="AK18:AT18" si="39">AK16/AK17</f>
-        <v>21.967163044434667</v>
+        <v>20.04688077430707</v>
       </c>
       <c r="AL18" s="13">
         <f t="shared" si="39"/>
-        <v>23.111591060272776</v>
+        <v>21.095294676638805</v>
       </c>
       <c r="AM18" s="13">
         <f t="shared" si="39"/>
-        <v>24.313701175538942</v>
+        <v>22.196589972723267</v>
       </c>
       <c r="AN18" s="13">
         <f t="shared" si="39"/>
-        <v>25.576382102190937</v>
+        <v>23.353415339234484</v>
       </c>
       <c r="AO18" s="13">
         <f t="shared" si="39"/>
-        <v>26.902667033854282</v>
+        <v>24.568551932750022</v>
       </c>
       <c r="AP18" s="13">
         <f t="shared" si="39"/>
-        <v>28.295740870366341</v>
+        <v>25.844920014206863</v>
       </c>
       <c r="AQ18" s="13">
         <f t="shared" si="39"/>
-        <v>29.758947803552193</v>
+        <v>27.185585904584745</v>
       </c>
       <c r="AR18" s="13">
         <f t="shared" si="39"/>
-        <v>31.295799282294013</v>
+        <v>28.593769288378194</v>
       </c>
       <c r="AS18" s="13">
         <f t="shared" si="39"/>
-        <v>32.909982375858576</v>
+        <v>30.072850882246954</v>
       </c>
       <c r="AT18" s="13">
         <f t="shared" si="39"/>
-        <v>34.605368555395863</v>
-      </c>
-    </row>
-    <row r="19" spans="3:49" x14ac:dyDescent="0.25">
+        <v>31.62638048710366</v>
+      </c>
+    </row>
+    <row r="19" spans="2:49" x14ac:dyDescent="0.25">
       <c r="AV19" s="2" t="s">
         <v>147</v>
       </c>
@@ -7741,823 +7885,805 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="3:49" x14ac:dyDescent="0.25">
-      <c r="C20" s="1" t="s">
+    <row r="20" spans="2:49" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="68"/>
+      <c r="C20" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16">
+      <c r="H20" s="69">
         <f t="shared" ref="H20:R20" si="40">(H4-D4)/D4</f>
         <v>0.25145039503221478</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="69">
         <f t="shared" si="40"/>
         <v>0.15821666798491918</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="69">
         <f t="shared" si="40"/>
         <v>8.4943528883791669E-2</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="69">
         <f t="shared" si="40"/>
         <v>-1.0920309044745967E-4</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="69">
         <f t="shared" si="40"/>
         <v>-0.18813772538787682</v>
       </c>
-      <c r="M20" s="16">
+      <c r="M20" s="69">
         <f t="shared" si="40"/>
         <v>-0.16646938310949239</v>
       </c>
-      <c r="N20" s="16">
+      <c r="N20" s="69">
         <f t="shared" si="40"/>
         <v>-0.16642154609798696</v>
       </c>
-      <c r="O20" s="16">
+      <c r="O20" s="69">
         <f t="shared" si="40"/>
         <v>3.2218430034129691E-2</v>
       </c>
-      <c r="P20" s="16">
+      <c r="P20" s="69">
         <f t="shared" si="40"/>
         <v>3.6154949784791965E-3</v>
       </c>
-      <c r="Q20" s="16">
+      <c r="Q20" s="69">
         <f t="shared" si="40"/>
         <v>-6.6417237894966813E-2</v>
       </c>
-      <c r="R20" s="16">
+      <c r="R20" s="69">
         <f t="shared" si="40"/>
         <v>-4.5101174394883391E-2</v>
       </c>
-      <c r="S20" s="16">
+      <c r="S20" s="69">
         <f>(S4-O4)/O4</f>
         <v>-8.2264250760481411E-2</v>
       </c>
-      <c r="T20" s="16">
+      <c r="T20" s="69">
         <f>(T4-P4)/P4</f>
         <v>-5.1435269899359558E-2</v>
       </c>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
-      <c r="Y20" s="16"/>
-      <c r="Z20" s="16"/>
-      <c r="AA20" s="16">
+      <c r="U20" s="69">
+        <f>(U4-Q4)/Q4</f>
+        <v>2.5625274243089073E-2</v>
+      </c>
+      <c r="V20" s="69"/>
+      <c r="W20" s="69"/>
+      <c r="X20" s="69"/>
+      <c r="Y20" s="69"/>
+      <c r="Z20" s="69"/>
+      <c r="AA20" s="69">
         <f t="shared" ref="AA20:AG20" si="41">(AA4-Z4)/Z4</f>
         <v>2.7598737299404177E-2</v>
       </c>
-      <c r="AB20" s="16">
+      <c r="AB20" s="69">
         <f t="shared" si="41"/>
         <v>7.9288409490507514E-2</v>
       </c>
-      <c r="AC20" s="16">
+      <c r="AC20" s="69">
         <f t="shared" si="41"/>
         <v>8.4519287969615151E-2</v>
       </c>
-      <c r="AD20" s="16">
+      <c r="AD20" s="69">
         <f t="shared" si="41"/>
         <v>8.8396624472573834E-2</v>
       </c>
-      <c r="AE20" s="16">
+      <c r="AE20" s="69">
         <f t="shared" si="41"/>
         <v>-5.6003101376235702E-2</v>
       </c>
-      <c r="AF20" s="16">
+      <c r="AF20" s="69">
         <f t="shared" si="41"/>
         <v>9.4454300545370915E-4</v>
       </c>
-      <c r="AG20" s="16">
+      <c r="AG20" s="69">
         <f t="shared" si="41"/>
         <v>0.28150360639057331</v>
       </c>
-      <c r="AH20" s="16">
+      <c r="AH20" s="69">
         <f>(AH4-AG4)/AG4</f>
         <v>-5.7794881317513272E-2</v>
       </c>
-      <c r="AI20" s="16">
+      <c r="AI20" s="69">
         <f>(AI4-AH4)/AH4</f>
         <v>-1.0880276186398636E-2</v>
       </c>
-      <c r="AJ20" s="16">
+      <c r="AJ20" s="69">
         <f t="shared" ref="AJ20:AT20" si="42">(AJ4-AI4)/AI4</f>
         <v>-4.8452035782501755E-2</v>
       </c>
-      <c r="AK20" s="41">
+      <c r="AK20" s="71">
         <f t="shared" si="42"/>
-        <v>3.0000000000000051E-2</v>
-      </c>
-      <c r="AL20" s="16">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="69">
         <f t="shared" si="42"/>
-        <v>5.0000000000000142E-2</v>
-      </c>
-      <c r="AM20" s="16">
+        <v>5.0000000000000086E-2</v>
+      </c>
+      <c r="AM20" s="69">
         <f t="shared" si="42"/>
-        <v>4.9999999999999968E-2</v>
-      </c>
-      <c r="AN20" s="16">
+        <v>4.9999999999999982E-2</v>
+      </c>
+      <c r="AN20" s="69">
         <f t="shared" si="42"/>
-        <v>5.000000000000001E-2</v>
-      </c>
-      <c r="AO20" s="16">
+        <v>5.0000000000000037E-2</v>
+      </c>
+      <c r="AO20" s="69">
         <f t="shared" si="42"/>
-        <v>5.0000000000000107E-2</v>
-      </c>
-      <c r="AP20" s="16">
+        <v>5.0000000000000121E-2</v>
+      </c>
+      <c r="AP20" s="69">
         <f t="shared" si="42"/>
-        <v>5.000000000000001E-2</v>
-      </c>
-      <c r="AQ20" s="16">
+        <v>4.9999999999999982E-2</v>
+      </c>
+      <c r="AQ20" s="69">
         <f t="shared" si="42"/>
-        <v>5.0000000000000024E-2</v>
-      </c>
-      <c r="AR20" s="16">
+        <v>4.9999999999999975E-2</v>
+      </c>
+      <c r="AR20" s="69">
         <f t="shared" si="42"/>
-        <v>5.0000000000000079E-2</v>
-      </c>
-      <c r="AS20" s="16">
+        <v>5.0000000000000065E-2</v>
+      </c>
+      <c r="AS20" s="69">
         <f t="shared" si="42"/>
-        <v>5.0000000000000051E-2</v>
-      </c>
-      <c r="AT20" s="16">
+        <v>4.9999999999999996E-2</v>
+      </c>
+      <c r="AT20" s="69">
         <f t="shared" si="42"/>
-        <v>5.0000000000000031E-2</v>
-      </c>
-      <c r="AV20" s="2" t="s">
+        <v>5.00000000000001E-2</v>
+      </c>
+      <c r="AV20" s="70" t="s">
         <v>148</v>
       </c>
       <c r="AW20" s="39">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="21" spans="3:49" x14ac:dyDescent="0.25">
-      <c r="C21" s="1" t="s">
+    <row r="21" spans="2:49" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="68"/>
+      <c r="C21" s="69" t="s">
         <v>130</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16">
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69">
         <v>0.17699999999999999</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="69">
         <v>0.17199999999999999</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="69">
         <v>0.128</v>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="69">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="69">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="69">
         <v>-0.04</v>
       </c>
-      <c r="M21" s="16">
+      <c r="M21" s="69">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="N21" s="16">
+      <c r="N21" s="69">
         <v>1.9E-2</v>
       </c>
-      <c r="O21" s="16">
+      <c r="O21" s="69">
         <v>3.9E-2</v>
       </c>
-      <c r="P21" s="16">
+      <c r="P21" s="69">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="Q21" s="16">
+      <c r="Q21" s="69">
         <v>1.9E-2</v>
       </c>
-      <c r="R21" s="16">
+      <c r="R21" s="69">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="S21" s="16">
+      <c r="S21" s="69">
         <v>-1.0999999999999999E-2</v>
       </c>
-      <c r="T21" s="16">
+      <c r="T21" s="69">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="16"/>
-      <c r="Y21" s="16"/>
-      <c r="Z21" s="16"/>
-      <c r="AA21" s="16"/>
-      <c r="AB21" s="16">
+      <c r="U21" s="69">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="V21" s="69"/>
+      <c r="W21" s="69"/>
+      <c r="X21" s="69"/>
+      <c r="Y21" s="69"/>
+      <c r="Z21" s="69"/>
+      <c r="AA21" s="69"/>
+      <c r="AB21" s="69">
         <v>0.1</v>
       </c>
-      <c r="AC21" s="16">
+      <c r="AC21" s="69">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="AD21" s="16">
+      <c r="AD21" s="69">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="AE21" s="16">
+      <c r="AE21" s="69">
         <v>-1.9E-2</v>
       </c>
-      <c r="AF21" s="16">
+      <c r="AF21" s="69">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="AG21" s="16">
+      <c r="AG21" s="69">
         <v>0.157</v>
       </c>
-      <c r="AH21" s="16">
+      <c r="AH21" s="69">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="AI21" s="16">
+      <c r="AI21" s="69">
         <v>2E-3</v>
       </c>
-      <c r="AJ21" s="16"/>
-      <c r="AK21" s="41"/>
-      <c r="AL21" s="16"/>
-      <c r="AM21" s="16"/>
-      <c r="AN21" s="16"/>
-      <c r="AO21" s="16"/>
-      <c r="AP21" s="16"/>
-      <c r="AQ21" s="16"/>
-      <c r="AR21" s="16"/>
-      <c r="AS21" s="16"/>
-      <c r="AT21" s="16"/>
-      <c r="AV21" s="38" t="s">
+      <c r="AJ21" s="69"/>
+      <c r="AK21" s="71"/>
+      <c r="AL21" s="69"/>
+      <c r="AM21" s="69"/>
+      <c r="AN21" s="69"/>
+      <c r="AO21" s="69"/>
+      <c r="AP21" s="69"/>
+      <c r="AQ21" s="69"/>
+      <c r="AR21" s="69"/>
+      <c r="AS21" s="69"/>
+      <c r="AT21" s="69"/>
+      <c r="AV21" s="72" t="s">
         <v>149</v>
       </c>
-      <c r="AW21" s="40">
+      <c r="AW21" s="74">
         <f>NPV(AW19,AK16:KN16)</f>
-        <v>243764.67214313347</v>
-      </c>
-    </row>
-    <row r="22" spans="3:49" x14ac:dyDescent="0.25">
-      <c r="C22" s="2" t="s">
+        <v>222698.69451763167</v>
+      </c>
+    </row>
+    <row r="22" spans="2:49" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="68"/>
+      <c r="C22" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="70">
         <f t="shared" ref="D22:S22" si="43">D6/D4</f>
         <v>0.22206349669105857</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="70">
         <f t="shared" si="43"/>
         <v>0.24321759076168631</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="70">
         <f t="shared" si="43"/>
         <v>0.23318955845321498</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="70">
         <f t="shared" si="43"/>
         <v>0.27947800922766114</v>
       </c>
-      <c r="H22" s="15">
+      <c r="H22" s="70">
         <f t="shared" si="43"/>
         <v>0.26990635046358852</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="70">
         <f t="shared" si="43"/>
         <v>0.26687912588208512</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="70">
         <f t="shared" si="43"/>
         <v>0.2759215001378803</v>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="70">
         <f t="shared" si="43"/>
         <v>0.32</v>
       </c>
-      <c r="L22" s="15">
+      <c r="L22" s="70">
         <f t="shared" si="43"/>
         <v>0.33190817790530847</v>
       </c>
-      <c r="M22" s="15">
+      <c r="M22" s="70">
         <f t="shared" si="43"/>
         <v>0.33181309227954231</v>
       </c>
-      <c r="N22" s="15">
+      <c r="N22" s="70">
         <f t="shared" si="43"/>
         <v>0.32601863593758618</v>
       </c>
-      <c r="O22" s="15">
+      <c r="O22" s="70">
         <f t="shared" si="43"/>
         <v>0.31937574394921309</v>
       </c>
-      <c r="P22" s="15">
+      <c r="P22" s="70">
         <f t="shared" si="43"/>
         <v>0.32805352241537056</v>
       </c>
-      <c r="Q22" s="15">
+      <c r="Q22" s="70">
         <f t="shared" si="43"/>
         <v>0.33350884891034077</v>
       </c>
-      <c r="R22" s="15">
+      <c r="R22" s="70">
         <f t="shared" si="43"/>
         <v>0.33411282406605464</v>
       </c>
-      <c r="S22" s="15">
+      <c r="S22" s="70">
         <f t="shared" si="43"/>
         <v>0.337080270932411</v>
       </c>
-      <c r="T22" s="15">
-        <f t="shared" ref="T22" si="44">T6/T4</f>
+      <c r="T22" s="70">
+        <f t="shared" ref="T22:U22" si="44">T6/T4</f>
         <v>0.33411700877113665</v>
       </c>
-      <c r="U22" s="15"/>
-      <c r="V22" s="15"/>
-      <c r="W22" s="15"/>
-      <c r="X22" s="15"/>
-      <c r="Y22" s="15"/>
-      <c r="Z22" s="15">
+      <c r="U22" s="70">
+        <f t="shared" si="44"/>
+        <v>0.32643107726533754</v>
+      </c>
+      <c r="Z22" s="70">
         <f t="shared" ref="Z22:AT22" si="45">Z6/Z4</f>
         <v>0.26687237994701529</v>
       </c>
-      <c r="AA22" s="15">
+      <c r="AA22" s="70">
         <f t="shared" si="45"/>
         <v>0.27884786345048301</v>
       </c>
-      <c r="AB22" s="15">
+      <c r="AB22" s="70">
         <f t="shared" si="45"/>
         <v>0.29155722326454031</v>
       </c>
-      <c r="AC22" s="15">
+      <c r="AC22" s="70">
         <f t="shared" si="45"/>
         <v>0.270084388185654</v>
       </c>
-      <c r="AD22" s="15">
+      <c r="AD22" s="70">
         <f t="shared" si="45"/>
         <v>0.29351424694708278</v>
       </c>
-      <c r="AE22" s="15">
+      <c r="AE22" s="70">
         <f t="shared" si="45"/>
         <v>0.32392897036598989</v>
       </c>
-      <c r="AF22" s="15">
+      <c r="AF22" s="70">
         <f t="shared" si="45"/>
         <v>0.28796146618854979</v>
       </c>
-      <c r="AG22" s="15">
+      <c r="AG22" s="70">
         <f t="shared" si="45"/>
         <v>0.23837667202397342</v>
       </c>
-      <c r="AH22" s="15">
+      <c r="AH22" s="70">
         <f t="shared" si="45"/>
         <v>0.30255458826887399</v>
       </c>
-      <c r="AI22" s="15">
+      <c r="AI22" s="70">
         <f t="shared" si="45"/>
         <v>0.32716117241284542</v>
       </c>
-      <c r="AJ22" s="15">
+      <c r="AJ22" s="70">
         <f t="shared" si="45"/>
         <v>0.33317688852946697</v>
       </c>
-      <c r="AK22" s="37">
+      <c r="AK22" s="68">
+        <f t="shared" si="45"/>
+        <v>0.3299999999999999</v>
+      </c>
+      <c r="AL22" s="70">
+        <f t="shared" si="45"/>
+        <v>0.33</v>
+      </c>
+      <c r="AM22" s="70">
         <f t="shared" si="45"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="AL22" s="15">
+      <c r="AN22" s="70">
         <f t="shared" si="45"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="AM22" s="15">
+      <c r="AO22" s="70">
         <f t="shared" si="45"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="AN22" s="15">
+      <c r="AP22" s="70">
         <f t="shared" si="45"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="AO22" s="15">
-        <f t="shared" si="45"/>
-        <v>0.3299999999999999</v>
-      </c>
-      <c r="AP22" s="15">
+      <c r="AQ22" s="70">
         <f t="shared" si="45"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="AQ22" s="15">
-        <f t="shared" si="45"/>
-        <v>0.3299999999999999</v>
-      </c>
-      <c r="AR22" s="15">
-        <f t="shared" si="45"/>
-        <v>0.3299999999999999</v>
-      </c>
-      <c r="AS22" s="15">
+      <c r="AR22" s="70">
         <f t="shared" si="45"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="AT22" s="15">
+      <c r="AS22" s="70">
         <f t="shared" si="45"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="AV22" s="2" t="s">
+      <c r="AT22" s="70">
+        <f t="shared" si="45"/>
+        <v>0.32999999999999996</v>
+      </c>
+      <c r="AV22" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="AW22" s="2">
+      <c r="AW22" s="73">
         <v>681.9</v>
       </c>
     </row>
-    <row r="23" spans="3:49" x14ac:dyDescent="0.25">
-      <c r="C23" s="2" t="s">
+    <row r="23" spans="2:49" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="68"/>
+      <c r="C23" s="70" t="s">
         <v>131</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="70">
         <f t="shared" ref="D23:R23" si="46">D9/D4</f>
         <v>4.8482551529109935E-2</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="70">
         <f t="shared" si="46"/>
         <v>6.9867383796039975E-2</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="70">
         <f t="shared" si="46"/>
         <v>6.9410855418983272E-2</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="70">
         <f t="shared" si="46"/>
         <v>0.11226077697998853</v>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="70">
         <f t="shared" si="46"/>
         <v>0.10355029585798817</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="70">
         <f t="shared" si="46"/>
         <v>9.5948099248804916E-2</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="70">
         <f t="shared" si="46"/>
         <v>8.417593528816987E-2</v>
       </c>
-      <c r="K23" s="15">
+      <c r="K23" s="70">
         <f t="shared" si="46"/>
         <v>0.1325051194539249</v>
       </c>
-      <c r="L23" s="15">
+      <c r="L23" s="70">
         <f t="shared" si="46"/>
         <v>0.14002869440459109</v>
       </c>
-      <c r="M23" s="15">
+      <c r="M23" s="70">
         <f t="shared" si="46"/>
         <v>0.147417866018516</v>
       </c>
-      <c r="N23" s="15">
+      <c r="N23" s="70">
         <f t="shared" si="46"/>
         <v>0.14034845895131498</v>
       </c>
-      <c r="O23" s="15">
+      <c r="O23" s="70">
         <f t="shared" si="46"/>
         <v>0.13143764052374024</v>
       </c>
-      <c r="P23" s="15">
+      <c r="P23" s="70">
         <f t="shared" si="46"/>
         <v>0.1345494053064959</v>
       </c>
-      <c r="Q23" s="15">
+      <c r="Q23" s="70">
         <f t="shared" si="46"/>
         <v>0.13728243381600116</v>
       </c>
-      <c r="R23" s="15">
+      <c r="R23" s="70">
         <f t="shared" si="46"/>
         <v>0.14596685720884578</v>
       </c>
-      <c r="S23" s="15">
+      <c r="S23" s="70">
         <f>S9/S4</f>
         <v>0.14748522841908057</v>
       </c>
-      <c r="T23" s="15">
+      <c r="T23" s="70">
         <f>T9/T4</f>
         <v>0.13334538987853031</v>
       </c>
-      <c r="U23" s="15"/>
-      <c r="V23" s="15"/>
-      <c r="W23" s="15"/>
-      <c r="X23" s="15"/>
-      <c r="Y23" s="15"/>
-      <c r="Z23" s="15">
+      <c r="U23" s="70">
+        <f>U9/U4</f>
+        <v>0.11705313596303585</v>
+      </c>
+      <c r="Z23" s="70">
         <f t="shared" ref="Z23:AT23" si="47">Z9/Z4</f>
         <v>9.8295760208690713E-2</v>
       </c>
-      <c r="AA23" s="15">
+      <c r="AA23" s="70">
         <f t="shared" si="47"/>
         <v>8.897844682826607E-2</v>
       </c>
-      <c r="AB23" s="15">
+      <c r="AB23" s="70">
         <f t="shared" si="47"/>
         <v>0.11485837184825883</v>
       </c>
-      <c r="AC23" s="15">
+      <c r="AC23" s="70">
         <f t="shared" si="47"/>
         <v>9.755274261603375E-2</v>
       </c>
-      <c r="AD23" s="15">
+      <c r="AD23" s="70">
         <f t="shared" si="47"/>
         <v>0.11728629579375847</v>
       </c>
-      <c r="AE23" s="15">
+      <c r="AE23" s="70">
         <f t="shared" si="47"/>
         <v>0.14428510414613313</v>
       </c>
-      <c r="AF23" s="15">
+      <c r="AF23" s="70">
         <f t="shared" si="47"/>
         <v>0.11529782467772244</v>
       </c>
-      <c r="AG23" s="15">
+      <c r="AG23" s="70">
         <f t="shared" si="47"/>
         <v>6.9711153656521932E-2</v>
       </c>
-      <c r="AH23" s="15">
+      <c r="AH23" s="70">
         <f t="shared" si="47"/>
         <v>0.12842939373551618</v>
       </c>
-      <c r="AI23" s="15">
+      <c r="AI23" s="70">
         <f t="shared" si="47"/>
         <v>0.13977711513885643</v>
       </c>
-      <c r="AJ23" s="15">
+      <c r="AJ23" s="70">
         <f t="shared" si="47"/>
         <v>0.14132020159718112</v>
       </c>
-      <c r="AK23" s="37">
+      <c r="AK23" s="68">
         <f t="shared" si="47"/>
-        <v>0.1381433130677141</v>
-      </c>
-      <c r="AL23" s="15">
+        <v>0.13046904559042261</v>
+      </c>
+      <c r="AL23" s="70">
         <f t="shared" si="47"/>
-        <v>0.13814331306771413</v>
-      </c>
-      <c r="AM23" s="15">
+        <v>0.13046904559042266</v>
+      </c>
+      <c r="AM23" s="70">
         <f t="shared" si="47"/>
-        <v>0.13814331306771413</v>
-      </c>
-      <c r="AN23" s="15">
+        <v>0.13046904559042263</v>
+      </c>
+      <c r="AN23" s="70">
         <f t="shared" si="47"/>
-        <v>0.1381433130677141</v>
-      </c>
-      <c r="AO23" s="15">
+        <v>0.13046904559042263</v>
+      </c>
+      <c r="AO23" s="70">
         <f t="shared" si="47"/>
-        <v>0.13814331306771405</v>
-      </c>
-      <c r="AP23" s="15">
+        <v>0.13046904559042266</v>
+      </c>
+      <c r="AP23" s="70">
         <f t="shared" si="47"/>
-        <v>0.13814331306771405</v>
-      </c>
-      <c r="AQ23" s="15">
+        <v>0.13046904559042263</v>
+      </c>
+      <c r="AQ23" s="70">
         <f t="shared" si="47"/>
-        <v>0.13814331306771405</v>
-      </c>
-      <c r="AR23" s="15">
+        <v>0.13046904559042263</v>
+      </c>
+      <c r="AR23" s="70">
         <f t="shared" si="47"/>
-        <v>0.13814331306771405</v>
-      </c>
-      <c r="AS23" s="15">
+        <v>0.13046904559042263</v>
+      </c>
+      <c r="AS23" s="70">
         <f t="shared" si="47"/>
-        <v>0.13814331306771405</v>
-      </c>
-      <c r="AT23" s="15">
+        <v>0.13046904559042263</v>
+      </c>
+      <c r="AT23" s="70">
         <f t="shared" si="47"/>
-        <v>0.13814331306771407</v>
-      </c>
-      <c r="AV23" s="2" t="s">
+        <v>0.13046904559042263</v>
+      </c>
+      <c r="AV23" s="70" t="s">
         <v>150</v>
       </c>
-      <c r="AW23" s="44">
+      <c r="AW23" s="14">
         <f>AW21/AW22</f>
-        <v>357.47862170865739</v>
-      </c>
-    </row>
-    <row r="24" spans="3:49" x14ac:dyDescent="0.25">
-      <c r="C24" s="2" t="s">
+        <v>326.58556169179013</v>
+      </c>
+    </row>
+    <row r="24" spans="2:49" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="68"/>
+      <c r="C24" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="70">
         <f t="shared" ref="D24:S24" si="48">D11/D4</f>
         <v>3.3526719337628644E-2</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="70">
         <f t="shared" si="48"/>
         <v>6.2406074507632685E-2</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="70">
         <f t="shared" si="48"/>
         <v>6.2105761799097457E-2</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="70">
         <f t="shared" si="48"/>
         <v>0.10439815446777144</v>
       </c>
-      <c r="H24" s="15">
+      <c r="H24" s="70">
         <f t="shared" si="48"/>
         <v>9.6887667148115364E-2</v>
       </c>
-      <c r="I24" s="15">
+      <c r="I24" s="70">
         <f t="shared" si="48"/>
         <v>8.8800364215797858E-2</v>
       </c>
-      <c r="J24" s="15">
+      <c r="J24" s="70">
         <f t="shared" si="48"/>
         <v>7.0479823513190556E-2</v>
       </c>
-      <c r="K24" s="15">
+      <c r="K24" s="70">
         <f t="shared" si="48"/>
         <v>0.12513310580204778</v>
       </c>
-      <c r="L24" s="15">
+      <c r="L24" s="70">
         <f t="shared" si="48"/>
         <v>0.1308464849354376</v>
       </c>
-      <c r="M24" s="15">
+      <c r="M24" s="70">
         <f t="shared" si="48"/>
         <v>0.14037195837998745</v>
       </c>
-      <c r="N24" s="15">
+      <c r="N24" s="70">
         <f t="shared" si="48"/>
         <v>0.13312565473893145</v>
       </c>
-      <c r="O24" s="15">
+      <c r="O24" s="70">
         <f t="shared" si="48"/>
         <v>0.12429572807829652</v>
       </c>
-      <c r="P24" s="15">
+      <c r="P24" s="70">
         <f t="shared" si="48"/>
         <v>0.12723010064043916</v>
       </c>
-      <c r="Q24" s="15">
+      <c r="Q24" s="70">
         <f t="shared" si="48"/>
         <v>0.13023255813953488</v>
       </c>
-      <c r="R24" s="15">
+      <c r="R24" s="70">
         <f t="shared" si="48"/>
         <v>0.13895144061435419</v>
       </c>
-      <c r="S24" s="15">
+      <c r="S24" s="70">
         <f t="shared" si="48"/>
         <v>0.1407983859345727</v>
       </c>
-      <c r="T24" s="15">
-        <f t="shared" ref="T24" si="49">T11/T4</f>
+      <c r="T24" s="70">
+        <f t="shared" ref="T24:U24" si="49">T11/T4</f>
         <v>0.12596075594538386</v>
       </c>
-      <c r="U24" s="15"/>
-      <c r="V24" s="15"/>
-      <c r="W24" s="15"/>
-      <c r="X24" s="15"/>
-      <c r="Y24" s="15"/>
-      <c r="Z24" s="15">
+      <c r="U24" s="70">
+        <f t="shared" si="49"/>
+        <v>0.10966601066712302</v>
+      </c>
+      <c r="Z24" s="70">
         <f t="shared" ref="Z24:AT24" si="50">Z11/Z4</f>
         <v>9.8295760208690713E-2</v>
       </c>
-      <c r="AA24" s="15">
+      <c r="AA24" s="70">
         <f t="shared" si="50"/>
         <v>8.897844682826607E-2</v>
       </c>
-      <c r="AB24" s="15">
+      <c r="AB24" s="70">
         <f t="shared" si="50"/>
         <v>0.10895529217956344</v>
       </c>
-      <c r="AC24" s="15">
+      <c r="AC24" s="70">
         <f t="shared" si="50"/>
         <v>9.0793248945147675E-2</v>
       </c>
-      <c r="AD24" s="15">
+      <c r="AD24" s="70">
         <f t="shared" si="50"/>
         <v>0.11125411901531304</v>
       </c>
-      <c r="AE24" s="15">
+      <c r="AE24" s="70">
         <f t="shared" si="50"/>
         <v>0.13764044943820225</v>
       </c>
-      <c r="AF24" s="15">
+      <c r="AF24" s="70">
         <f t="shared" si="50"/>
         <v>0.10830659653556746</v>
       </c>
-      <c r="AG24" s="15">
+      <c r="AG24" s="70">
         <f t="shared" si="50"/>
         <v>6.0695510747696461E-2</v>
       </c>
-      <c r="AH24" s="15">
+      <c r="AH24" s="70">
         <f t="shared" si="50"/>
         <v>0.12089271272944742</v>
       </c>
-      <c r="AI24" s="15">
+      <c r="AI24" s="70">
         <f t="shared" si="50"/>
         <v>0.13215066027235375</v>
       </c>
-      <c r="AJ24" s="15">
+      <c r="AJ24" s="70">
         <f t="shared" si="50"/>
         <v>0.13430184701142286</v>
       </c>
-      <c r="AK24" s="37">
+      <c r="AK24" s="68">
         <f t="shared" si="50"/>
-        <v>0.13126123721177643</v>
-      </c>
-      <c r="AL24" s="15">
+        <v>0.1233805074588068</v>
+      </c>
+      <c r="AL24" s="70">
         <f t="shared" si="50"/>
-        <v>0.13152341153009789</v>
-      </c>
-      <c r="AM24" s="15">
+        <v>0.12365054700667795</v>
+      </c>
+      <c r="AM24" s="70">
         <f t="shared" si="50"/>
-        <v>0.13177559825534041</v>
-      </c>
-      <c r="AN24" s="15">
+        <v>0.1239102993336777</v>
+      </c>
+      <c r="AN24" s="70">
         <f t="shared" si="50"/>
-        <v>0.13201817786724035</v>
-      </c>
-      <c r="AO24" s="15">
+        <v>0.12416015633393465</v>
+      </c>
+      <c r="AO24" s="70">
         <f t="shared" si="50"/>
-        <v>0.13225151635106785</v>
-      </c>
-      <c r="AP24" s="15">
+        <v>0.12440049497227706</v>
+      </c>
+      <c r="AP24" s="70">
         <f t="shared" si="50"/>
-        <v>0.13247596574979725</v>
-      </c>
-      <c r="AQ24" s="15">
+        <v>0.12463167785296832</v>
+      </c>
+      <c r="AQ24" s="70">
         <f t="shared" si="50"/>
-        <v>0.13269186469524166</v>
-      </c>
-      <c r="AR24" s="15">
+        <v>0.12485405376677609</v>
+      </c>
+      <c r="AR24" s="70">
         <f t="shared" si="50"/>
-        <v>0.1328995389189549</v>
-      </c>
-      <c r="AS24" s="15">
+        <v>0.12506795821720074</v>
+      </c>
+      <c r="AS24" s="70">
         <f t="shared" si="50"/>
-        <v>0.13309930174366957</v>
-      </c>
-      <c r="AT24" s="15">
+        <v>0.12527371392665679</v>
+      </c>
+      <c r="AT24" s="70">
         <f t="shared" si="50"/>
-        <v>0.13329145455601413</v>
-      </c>
-      <c r="AV24" s="1" t="s">
+        <v>0.12547163132337169</v>
+      </c>
+      <c r="AV24" s="69" t="s">
         <v>151</v>
       </c>
-      <c r="AW24" s="16">
+      <c r="AW24" s="69">
         <f>(AW23-B4)/B4</f>
-        <v>0.44144605527684427</v>
-      </c>
-    </row>
-    <row r="25" spans="3:49" x14ac:dyDescent="0.25">
-      <c r="C25" s="15" t="s">
+        <v>0.19628410876113603</v>
+      </c>
+    </row>
+    <row r="25" spans="2:49" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="68"/>
+      <c r="C25" s="70" t="s">
         <v>146</v>
       </c>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="15">
+      <c r="Z25" s="70">
         <v>0.29199999999999998</v>
       </c>
-      <c r="AA25" s="15">
+      <c r="AA25" s="70">
         <v>0.128</v>
       </c>
-      <c r="AB25" s="15">
+      <c r="AB25" s="70">
         <v>0.13900000000000001</v>
       </c>
-      <c r="AC25" s="15">
+      <c r="AC25" s="70">
         <v>0.153</v>
       </c>
-      <c r="AD25" s="15">
+      <c r="AD25" s="70">
         <v>0.152</v>
       </c>
-      <c r="AE25" s="15">
+      <c r="AE25" s="70">
         <v>0.16400000000000001</v>
       </c>
-      <c r="AF25" s="15">
+      <c r="AF25" s="70">
         <v>0.16300000000000001</v>
       </c>
-      <c r="AG25" s="15">
+      <c r="AG25" s="70">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="AH25" s="15">
+      <c r="AH25" s="70">
         <v>0.14399999999999999</v>
       </c>
-      <c r="AI25" s="15">
+      <c r="AI25" s="70">
         <v>0.16900000000000001</v>
       </c>
-      <c r="AJ25" s="15"/>
-    </row>
-    <row r="27" spans="3:49" x14ac:dyDescent="0.25">
+      <c r="AK25" s="68"/>
+    </row>
+    <row r="27" spans="2:49" x14ac:dyDescent="0.25">
       <c r="C27" s="1" t="s">
         <v>66</v>
       </c>
@@ -8594,7 +8720,7 @@
       <c r="AH27" s="1"/>
       <c r="AI27" s="1"/>
     </row>
-    <row r="28" spans="3:49" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:49" x14ac:dyDescent="0.25">
       <c r="C28" s="2" t="s">
         <v>67</v>
       </c>
@@ -8649,7 +8775,9 @@
       <c r="T28" s="10">
         <v>38804</v>
       </c>
-      <c r="U28" s="10"/>
+      <c r="U28" s="10">
+        <v>39324</v>
+      </c>
       <c r="V28" s="10"/>
       <c r="W28" s="10"/>
       <c r="X28" s="10"/>
@@ -8687,7 +8815,7 @@
         <v>36861</v>
       </c>
     </row>
-    <row r="29" spans="3:49" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:49" x14ac:dyDescent="0.25">
       <c r="C29" s="2" t="s">
         <v>68</v>
       </c>
@@ -8742,7 +8870,9 @@
       <c r="T29" s="10">
         <v>19478</v>
       </c>
-      <c r="U29" s="10"/>
+      <c r="U29" s="10">
+        <v>19105</v>
+      </c>
       <c r="V29" s="10"/>
       <c r="W29" s="10"/>
       <c r="X29" s="10"/>
@@ -8780,7 +8910,7 @@
         <v>18273</v>
       </c>
     </row>
-    <row r="30" spans="3:49" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:49" x14ac:dyDescent="0.25">
       <c r="C30" s="2" t="s">
         <v>69</v>
       </c>
@@ -8835,7 +8965,9 @@
       <c r="T30" s="10">
         <v>48054</v>
       </c>
-      <c r="U30" s="10"/>
+      <c r="U30" s="10">
+        <v>49188</v>
+      </c>
       <c r="V30" s="10"/>
       <c r="X30" s="10"/>
       <c r="Z30" s="10">
@@ -8872,7 +9004,7 @@
         <v>46308</v>
       </c>
     </row>
-    <row r="31" spans="3:49" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:49" x14ac:dyDescent="0.25">
       <c r="C31" s="2" t="s">
         <v>70</v>
       </c>
@@ -8927,7 +9059,9 @@
       <c r="T31" s="10">
         <v>3823</v>
       </c>
-      <c r="U31" s="10"/>
+      <c r="U31" s="10">
+        <v>3834</v>
+      </c>
       <c r="V31" s="10"/>
       <c r="W31" s="10"/>
       <c r="X31" s="10"/>
@@ -8965,7 +9099,7 @@
         <v>3752</v>
       </c>
     </row>
-    <row r="32" spans="3:49" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:49" x14ac:dyDescent="0.25">
       <c r="C32" s="2" t="s">
         <v>71</v>
       </c>
@@ -9020,7 +9154,9 @@
       <c r="T32" s="10">
         <v>307</v>
       </c>
-      <c r="U32" s="10"/>
+      <c r="U32" s="10">
+        <v>332</v>
+      </c>
       <c r="V32" s="10"/>
       <c r="W32" s="10"/>
       <c r="X32" s="10"/>
@@ -9113,7 +9249,9 @@
       <c r="T33" s="10">
         <v>8</v>
       </c>
-      <c r="U33" s="10"/>
+      <c r="U33" s="10">
+        <v>8</v>
+      </c>
       <c r="V33" s="10"/>
       <c r="W33" s="10"/>
       <c r="X33" s="10"/>
@@ -9206,7 +9344,9 @@
       <c r="T34" s="10">
         <v>7811</v>
       </c>
-      <c r="U34" s="10"/>
+      <c r="U34" s="10">
+        <v>9453</v>
+      </c>
       <c r="V34" s="10"/>
       <c r="W34" s="10"/>
       <c r="X34" s="10"/>
@@ -9299,7 +9439,9 @@
       <c r="T35" s="10">
         <v>124</v>
       </c>
-      <c r="U35" s="10"/>
+      <c r="U35" s="10">
+        <v>129</v>
+      </c>
       <c r="V35" s="10"/>
       <c r="W35" s="10"/>
       <c r="X35" s="10"/>
@@ -9392,7 +9534,9 @@
       <c r="T36" s="10">
         <v>2067</v>
       </c>
-      <c r="U36" s="10"/>
+      <c r="U36" s="10">
+        <v>2185</v>
+      </c>
       <c r="V36" s="10"/>
       <c r="W36" s="10"/>
       <c r="X36" s="10"/>
@@ -9485,7 +9629,9 @@
       <c r="T37" s="10">
         <v>898</v>
       </c>
-      <c r="U37" s="10"/>
+      <c r="U37" s="10">
+        <v>860</v>
+      </c>
       <c r="V37" s="10"/>
       <c r="W37" s="10"/>
       <c r="X37" s="10"/>
@@ -9578,7 +9724,9 @@
       <c r="T38" s="10">
         <v>19395</v>
       </c>
-      <c r="U38" s="10"/>
+      <c r="U38" s="10">
+        <v>20339</v>
+      </c>
       <c r="V38" s="10"/>
       <c r="W38" s="10"/>
       <c r="X38" s="10"/>
@@ -9671,7 +9819,9 @@
       <c r="T39" s="10">
         <v>22689</v>
       </c>
-      <c r="U39" s="10"/>
+      <c r="U39" s="10">
+        <v>23993</v>
+      </c>
       <c r="V39" s="10"/>
       <c r="W39" s="10"/>
       <c r="X39" s="10"/>
@@ -9764,7 +9914,9 @@
       <c r="T40" s="10">
         <v>1497</v>
       </c>
-      <c r="U40" s="10"/>
+      <c r="U40" s="10">
+        <v>1531</v>
+      </c>
       <c r="V40" s="10"/>
       <c r="W40" s="10"/>
       <c r="X40" s="10"/>
@@ -9857,7 +10009,9 @@
       <c r="T41" s="10">
         <v>3780</v>
       </c>
-      <c r="U41" s="10"/>
+      <c r="U41" s="10">
+        <v>4381</v>
+      </c>
       <c r="V41" s="10"/>
       <c r="W41" s="10"/>
       <c r="X41" s="10"/>
@@ -9950,7 +10104,9 @@
       <c r="T42" s="10">
         <v>1381</v>
       </c>
-      <c r="U42" s="10"/>
+      <c r="U42" s="10">
+        <v>1378</v>
+      </c>
       <c r="V42" s="10"/>
       <c r="W42" s="10"/>
       <c r="X42" s="10"/>
@@ -10043,7 +10199,9 @@
       <c r="T43" s="10">
         <v>10741</v>
       </c>
-      <c r="U43" s="10"/>
+      <c r="U43" s="10">
+        <v>5495</v>
+      </c>
       <c r="V43" s="10"/>
       <c r="W43" s="10"/>
       <c r="X43" s="10"/>
@@ -10153,7 +10311,10 @@
         <f>SUM(T28:T43)</f>
         <v>180857</v>
       </c>
-      <c r="U44" s="9"/>
+      <c r="U44" s="9">
+        <f>SUM(U28:U43)</f>
+        <v>181535</v>
+      </c>
       <c r="V44" s="9"/>
       <c r="W44" s="9"/>
       <c r="X44" s="9"/>
@@ -10257,7 +10418,9 @@
       <c r="T45" s="10">
         <v>2350</v>
       </c>
-      <c r="U45" s="10"/>
+      <c r="U45" s="10">
+        <v>2350</v>
+      </c>
       <c r="V45" s="10"/>
       <c r="W45" s="10"/>
       <c r="X45" s="10"/>
@@ -10350,7 +10513,9 @@
       <c r="T46" s="10">
         <v>7490</v>
       </c>
-      <c r="U46" s="10"/>
+      <c r="U46" s="10">
+        <v>9128</v>
+      </c>
       <c r="V46" s="10"/>
       <c r="W46" s="10"/>
       <c r="X46" s="10"/>
@@ -10443,7 +10608,9 @@
       <c r="T47" s="10">
         <v>77875</v>
       </c>
-      <c r="U47" s="10"/>
+      <c r="U47" s="10">
+        <v>81284</v>
+      </c>
       <c r="V47" s="10"/>
       <c r="W47" s="10"/>
       <c r="X47" s="10"/>
@@ -10536,7 +10703,9 @@
       <c r="T48" s="10">
         <v>446</v>
       </c>
-      <c r="U48" s="10"/>
+      <c r="U48" s="10">
+        <v>418</v>
+      </c>
       <c r="V48" s="10"/>
       <c r="W48" s="10"/>
       <c r="X48" s="10"/>
@@ -10646,7 +10815,10 @@
         <f>SUM(T45:T48)</f>
         <v>88161</v>
       </c>
-      <c r="U49" s="17"/>
+      <c r="U49" s="17">
+        <f>SUM(U45:U48)</f>
+        <v>93180</v>
+      </c>
       <c r="V49" s="17"/>
       <c r="W49" s="17"/>
       <c r="X49" s="17"/>
@@ -10751,7 +10923,9 @@
       <c r="T50" s="10">
         <v>26331</v>
       </c>
-      <c r="U50" s="10"/>
+      <c r="U50" s="10">
+        <v>25551</v>
+      </c>
       <c r="V50" s="10"/>
       <c r="W50" s="10"/>
       <c r="X50" s="10"/>
@@ -10844,7 +11018,9 @@
       <c r="T51" s="10">
         <v>2284</v>
       </c>
-      <c r="U51" s="10"/>
+      <c r="U51" s="10">
+        <v>2308</v>
+      </c>
       <c r="V51" s="10"/>
       <c r="W51" s="10"/>
       <c r="X51" s="10"/>
@@ -10937,7 +11113,9 @@
       <c r="T52" s="10">
         <v>7194</v>
       </c>
-      <c r="U52" s="10"/>
+      <c r="U52" s="10">
+        <v>7606</v>
+      </c>
       <c r="V52" s="10"/>
       <c r="W52" s="10"/>
       <c r="X52" s="10"/>
@@ -11030,7 +11208,9 @@
       <c r="T53" s="10">
         <v>304</v>
       </c>
-      <c r="U53" s="10"/>
+      <c r="U53" s="10">
+        <v>358</v>
+      </c>
       <c r="V53" s="10"/>
       <c r="W53" s="10"/>
       <c r="X53" s="10"/>
@@ -11123,7 +11303,9 @@
       <c r="T54" s="10">
         <v>58</v>
       </c>
-      <c r="U54" s="10"/>
+      <c r="U54" s="10">
+        <v>47</v>
+      </c>
       <c r="V54" s="10"/>
       <c r="W54" s="10"/>
       <c r="X54" s="10"/>
@@ -11216,7 +11398,9 @@
       <c r="T55" s="10">
         <v>15980</v>
       </c>
-      <c r="U55" s="10"/>
+      <c r="U55" s="10">
+        <v>17058</v>
+      </c>
       <c r="V55" s="10"/>
       <c r="W55" s="10"/>
       <c r="X55" s="10"/>
@@ -11309,7 +11493,9 @@
       <c r="T56" s="10">
         <v>15127</v>
       </c>
-      <c r="U56" s="10"/>
+      <c r="U56" s="10">
+        <v>15734</v>
+      </c>
       <c r="V56" s="10"/>
       <c r="W56" s="10"/>
       <c r="X56" s="10"/>
@@ -11402,7 +11588,9 @@
       <c r="T57" s="10">
         <v>1671</v>
       </c>
-      <c r="U57" s="10"/>
+      <c r="U57" s="10">
+        <v>1444</v>
+      </c>
       <c r="V57" s="10"/>
       <c r="W57" s="10"/>
       <c r="X57" s="10"/>
@@ -11495,7 +11683,9 @@
       <c r="T58" s="10">
         <v>1016</v>
       </c>
-      <c r="U58" s="10"/>
+      <c r="U58" s="10">
+        <v>1254</v>
+      </c>
       <c r="V58" s="10"/>
       <c r="W58" s="10"/>
       <c r="X58" s="10"/>
@@ -11588,7 +11778,9 @@
       <c r="T59" s="10">
         <v>22731</v>
       </c>
-      <c r="U59" s="10"/>
+      <c r="U59" s="10">
+        <v>16995</v>
+      </c>
       <c r="V59" s="10"/>
       <c r="W59" s="10"/>
       <c r="X59" s="10"/>
@@ -11698,7 +11890,10 @@
         <f>SUM(T50:T59)</f>
         <v>92696</v>
       </c>
-      <c r="U60" s="17"/>
+      <c r="U60" s="17">
+        <f>SUM(U50:U59)</f>
+        <v>88355</v>
+      </c>
       <c r="V60" s="17"/>
       <c r="W60" s="17"/>
       <c r="X60" s="17"/>
@@ -11819,7 +12014,10 @@
         <f>T49+T60</f>
         <v>180857</v>
       </c>
-      <c r="U61" s="9"/>
+      <c r="U61" s="9">
+        <f>U49+U60</f>
+        <v>181535</v>
+      </c>
       <c r="V61" s="9"/>
       <c r="W61" s="9"/>
       <c r="X61" s="9"/>
@@ -11960,7 +12158,10 @@
         <f>T11</f>
         <v>4179</v>
       </c>
-      <c r="U64" s="10"/>
+      <c r="U64" s="10">
+        <f>U11</f>
+        <v>3845</v>
+      </c>
       <c r="V64" s="10"/>
       <c r="W64" s="10"/>
       <c r="X64" s="1"/>
@@ -12072,7 +12273,10 @@
       <c r="T65" s="10">
         <v>4196</v>
       </c>
-      <c r="U65" s="10"/>
+      <c r="U65" s="10">
+        <f>8042-T65</f>
+        <v>3846</v>
+      </c>
       <c r="V65" s="10"/>
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
@@ -12170,7 +12374,10 @@
       <c r="T66" s="10">
         <v>1999</v>
       </c>
-      <c r="U66" s="9"/>
+      <c r="U66" s="10">
+        <f>4584-T66</f>
+        <v>2585</v>
+      </c>
       <c r="V66" s="10"/>
       <c r="W66" s="1"/>
       <c r="X66" s="1"/>
@@ -12269,7 +12476,10 @@
       <c r="T67" s="10">
         <v>-165</v>
       </c>
-      <c r="U67" s="9"/>
+      <c r="U67" s="10">
+        <f>-298-T67</f>
+        <v>-133</v>
+      </c>
       <c r="V67" s="10"/>
       <c r="W67" s="1"/>
       <c r="X67" s="1"/>
@@ -12368,7 +12578,10 @@
       <c r="T68" s="10">
         <v>-271</v>
       </c>
-      <c r="U68" s="9"/>
+      <c r="U68" s="10">
+        <f>-439-T68</f>
+        <v>-168</v>
+      </c>
       <c r="V68" s="10"/>
       <c r="W68" s="1"/>
       <c r="X68" s="1"/>
@@ -12468,7 +12681,10 @@
       <c r="T69" s="10">
         <v>24</v>
       </c>
-      <c r="U69" s="10"/>
+      <c r="U69" s="10">
+        <f>(-729-1993+1061)-T69</f>
+        <v>-1685</v>
+      </c>
       <c r="V69" s="10"/>
       <c r="Z69" s="10"/>
       <c r="AA69" s="10">
@@ -12573,7 +12789,10 @@
       <c r="T70" s="10">
         <v>-448</v>
       </c>
-      <c r="U70" s="10"/>
+      <c r="U70" s="10">
+        <f>-626-T70</f>
+        <v>-178</v>
+      </c>
       <c r="V70" s="10"/>
       <c r="Z70" s="10"/>
       <c r="AA70" s="10">
@@ -12669,7 +12888,10 @@
       <c r="T71" s="10">
         <v>57</v>
       </c>
-      <c r="U71" s="10"/>
+      <c r="U71" s="10">
+        <f>110-T71</f>
+        <v>53</v>
+      </c>
       <c r="V71" s="10"/>
       <c r="Z71" s="10"/>
       <c r="AA71" s="10">
@@ -12765,7 +12987,10 @@
       <c r="T72" s="10">
         <v>-44</v>
       </c>
-      <c r="U72" s="10"/>
+      <c r="U72" s="10">
+        <f>-76-T72</f>
+        <v>-32</v>
+      </c>
       <c r="V72" s="10"/>
       <c r="Z72" s="10"/>
       <c r="AA72" s="10">
@@ -12861,7 +13086,10 @@
       <c r="T73" s="10">
         <v>-1109</v>
       </c>
-      <c r="U73" s="10"/>
+      <c r="U73" s="10">
+        <f>-2324-T73</f>
+        <v>-1215</v>
+      </c>
       <c r="V73" s="10"/>
       <c r="Z73" s="10"/>
       <c r="AA73" s="10">
@@ -12971,7 +13199,10 @@
         <f>SUM(T65:T73)</f>
         <v>4239</v>
       </c>
-      <c r="U74" s="9"/>
+      <c r="U74" s="9">
+        <f>SUM(U65:U73)</f>
+        <v>3073</v>
+      </c>
       <c r="V74" s="10"/>
       <c r="W74" s="1"/>
       <c r="X74" s="1"/>
@@ -13119,7 +13350,10 @@
       <c r="T76" s="10">
         <v>-1253</v>
       </c>
-      <c r="U76" s="10"/>
+      <c r="U76" s="10">
+        <f>-2783-T76</f>
+        <v>-1530</v>
+      </c>
       <c r="V76" s="10"/>
       <c r="Z76" s="10"/>
       <c r="AA76" s="10">
@@ -13221,7 +13455,10 @@
       <c r="T77" s="10">
         <v>-5</v>
       </c>
-      <c r="U77" s="10"/>
+      <c r="U77" s="10">
+        <f>-10-T77</f>
+        <v>-5</v>
+      </c>
       <c r="V77" s="10"/>
       <c r="Z77" s="10"/>
       <c r="AA77" s="10">
@@ -13317,7 +13554,10 @@
       <c r="T78" s="10">
         <v>7</v>
       </c>
-      <c r="U78" s="10"/>
+      <c r="U78" s="10">
+        <f>54-T78</f>
+        <v>47</v>
+      </c>
       <c r="V78" s="10"/>
       <c r="Z78" s="10"/>
       <c r="AA78" s="10">
@@ -13413,7 +13653,10 @@
       <c r="T79" s="10">
         <v>280</v>
       </c>
-      <c r="U79" s="10"/>
+      <c r="U79" s="10">
+        <f>302-T79</f>
+        <v>22</v>
+      </c>
       <c r="V79" s="10"/>
       <c r="Z79" s="10"/>
       <c r="AA79" s="10">
@@ -13523,7 +13766,10 @@
         <f>SUM(T76:T79)</f>
         <v>-971</v>
       </c>
-      <c r="U80" s="9"/>
+      <c r="U80" s="9">
+        <f>SUM(U76:U79)</f>
+        <v>-1466</v>
+      </c>
       <c r="V80" s="10"/>
       <c r="W80" s="1"/>
       <c r="X80" s="1"/>
@@ -13668,7 +13914,10 @@
       <c r="T82" s="10">
         <v>-2994</v>
       </c>
-      <c r="U82" s="10"/>
+      <c r="U82" s="10">
+        <f>(-2994-83)-T82</f>
+        <v>-83</v>
+      </c>
       <c r="V82" s="10"/>
       <c r="Z82" s="10"/>
       <c r="AA82" s="10">
@@ -13765,7 +14014,10 @@
       <c r="T83" s="10">
         <v>1990</v>
       </c>
-      <c r="U83" s="10"/>
+      <c r="U83" s="10">
+        <f>3655-T83</f>
+        <v>1665</v>
+      </c>
       <c r="V83" s="10"/>
       <c r="Z83" s="10"/>
       <c r="AA83" s="10">
@@ -13862,7 +14114,10 @@
       <c r="T84" s="10">
         <v>-128</v>
       </c>
-      <c r="U84" s="10"/>
+      <c r="U84" s="10">
+        <f>-983-T84</f>
+        <v>-855</v>
+      </c>
       <c r="V84" s="10"/>
       <c r="Z84" s="10"/>
       <c r="AA84" s="10">
@@ -13958,7 +14213,10 @@
       <c r="T85" s="10">
         <v>-266</v>
       </c>
-      <c r="U85" s="10"/>
+      <c r="U85" s="10">
+        <f>-529-T85</f>
+        <v>-263</v>
+      </c>
       <c r="V85" s="10"/>
       <c r="Z85" s="10"/>
       <c r="AA85" s="10">
@@ -14054,7 +14312,10 @@
       <c r="T86" s="10">
         <v>894</v>
       </c>
-      <c r="U86" s="10"/>
+      <c r="U86" s="10">
+        <f>32-T86</f>
+        <v>-862</v>
+      </c>
       <c r="V86" s="10"/>
       <c r="Z86" s="10"/>
       <c r="AA86" s="10">
@@ -14147,7 +14408,10 @@
       <c r="T87" s="10">
         <v>0</v>
       </c>
-      <c r="U87" s="10"/>
+      <c r="U87" s="10">
+        <f>-5956-T87</f>
+        <v>-5956</v>
+      </c>
       <c r="V87" s="10"/>
       <c r="Z87" s="10"/>
       <c r="AA87" s="10">
@@ -14240,7 +14504,10 @@
       <c r="T88" s="10">
         <v>0</v>
       </c>
-      <c r="U88" s="10"/>
+      <c r="U88" s="10">
+        <f>0-T88</f>
+        <v>0</v>
+      </c>
       <c r="V88" s="10"/>
       <c r="Z88" s="10"/>
       <c r="AA88" s="10">
@@ -14275,7 +14542,7 @@
       </c>
       <c r="AK88" s="12"/>
       <c r="AL88" s="10"/>
-      <c r="AM88" s="46"/>
+      <c r="AM88" s="45"/>
       <c r="AN88" s="10"/>
     </row>
     <row r="89" spans="3:40" x14ac:dyDescent="0.25">
@@ -14336,7 +14603,10 @@
       <c r="T89" s="10">
         <v>-612</v>
       </c>
-      <c r="U89" s="10"/>
+      <c r="U89" s="10">
+        <f>-1166-T89</f>
+        <v>-554</v>
+      </c>
       <c r="V89" s="10"/>
       <c r="Z89" s="10"/>
       <c r="AA89" s="10">
@@ -14446,7 +14716,10 @@
         <f>SUM(T82:T89)</f>
         <v>-1116</v>
       </c>
-      <c r="U90" s="9"/>
+      <c r="U90" s="9">
+        <f>SUM(U82:U89)</f>
+        <v>-6908</v>
+      </c>
       <c r="V90" s="10"/>
       <c r="W90" s="1"/>
       <c r="X90" s="1"/>
@@ -14594,7 +14867,10 @@
       <c r="T92" s="10">
         <v>102</v>
       </c>
-      <c r="U92" s="10"/>
+      <c r="U92" s="10">
+        <f>157-T92</f>
+        <v>55</v>
+      </c>
       <c r="V92" s="10"/>
       <c r="Z92" s="10"/>
       <c r="AA92" s="10">
@@ -14740,7 +15016,10 @@
         <f>T74+T80+T90+T92</f>
         <v>2254</v>
       </c>
-      <c r="U94" s="10"/>
+      <c r="U94" s="10">
+        <f>U74+U80+U90+U92</f>
+        <v>-5246</v>
+      </c>
       <c r="V94" s="10"/>
       <c r="Z94" s="10">
         <f t="shared" ref="Z94:AI94" si="99">Z74+Z80+Z90+Z92</f>
@@ -14901,7 +15180,10 @@
         <f>T74+T76</f>
         <v>2986</v>
       </c>
-      <c r="U96" s="10"/>
+      <c r="U96" s="10">
+        <f>U74+U76</f>
+        <v>1543</v>
+      </c>
       <c r="V96" s="10"/>
       <c r="Z96" s="10">
         <f t="shared" ref="Z96:AI96" si="103">Z74+Z76</f>
@@ -15080,7 +15362,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{249058E0-3BA5-6740-BE74-082DF7085DA4}">
-  <dimension ref="B4:AA47"/>
+  <dimension ref="B4:AB47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -15238,7 +15520,9 @@
       <c r="W6" s="10">
         <v>6499</v>
       </c>
-      <c r="X6" s="10"/>
+      <c r="X6" s="10">
+        <v>6918</v>
+      </c>
       <c r="Y6" s="10"/>
       <c r="Z6" s="10"/>
       <c r="AA6" s="26"/>
@@ -15320,7 +15604,7 @@
       </c>
       <c r="X7" s="20">
         <f t="shared" ref="X7" si="2">(X6-S6)/S6</f>
-        <v>-1</v>
+        <v>2.9004908522980811E-2</v>
       </c>
       <c r="Y7" s="20">
         <f t="shared" ref="Y7" si="3">(Y6-T6)/T6</f>
@@ -15392,7 +15676,9 @@
       <c r="W8" s="20">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="X8" s="20"/>
+      <c r="X8" s="20">
+        <v>3.1E-2</v>
+      </c>
       <c r="Y8" s="20"/>
       <c r="Z8" s="20"/>
       <c r="AA8" s="23"/>
@@ -15454,7 +15740,9 @@
       <c r="W9" s="20">
         <v>0.44900000000000001</v>
       </c>
-      <c r="X9" s="20"/>
+      <c r="X9" s="20">
+        <v>0.44800000000000001</v>
+      </c>
       <c r="Y9" s="20"/>
       <c r="Z9" s="20"/>
       <c r="AA9" s="23"/>
@@ -15530,12 +15818,14 @@
       <c r="W10" s="10">
         <v>1193</v>
       </c>
-      <c r="X10" s="10"/>
+      <c r="X10" s="10">
+        <v>1310</v>
+      </c>
       <c r="Y10" s="10"/>
       <c r="Z10" s="10"/>
       <c r="AA10" s="26">
         <f>SUM(W10:Z10)</f>
-        <v>1193</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.25">
@@ -15546,7 +15836,7 @@
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
       <c r="F11" s="20"/>
-      <c r="G11" s="59">
+      <c r="G11" s="58">
         <f>G10/G6</f>
         <v>0.11494116248662783</v>
       </c>
@@ -15562,7 +15852,7 @@
       <c r="K11" s="20">
         <v>0.161</v>
       </c>
-      <c r="L11" s="59">
+      <c r="L11" s="58">
         <f>L10/L6</f>
         <v>0.14558765191676584</v>
       </c>
@@ -15578,7 +15868,7 @@
       <c r="P11" s="20">
         <v>0.183</v>
       </c>
-      <c r="Q11" s="59">
+      <c r="Q11" s="58">
         <f>Q10/Q6</f>
         <v>0.19262911290604567</v>
       </c>
@@ -15594,17 +15884,19 @@
       <c r="U11" s="20">
         <v>0.161</v>
       </c>
-      <c r="V11" s="59">
+      <c r="V11" s="58">
         <f>V10/V6</f>
         <v>0.18006407455948739</v>
       </c>
       <c r="W11" s="20">
         <v>0.184</v>
       </c>
-      <c r="X11" s="20"/>
+      <c r="X11" s="20">
+        <v>0.189</v>
+      </c>
       <c r="Y11" s="20"/>
       <c r="Z11" s="20"/>
-      <c r="AA11" s="59" t="e">
+      <c r="AA11" s="58" t="e">
         <f>AA10/AA6</f>
         <v>#DIV/0!</v>
       </c>
@@ -15652,7 +15944,9 @@
       <c r="W12" s="21">
         <v>0.14899999999999999</v>
       </c>
-      <c r="X12" s="21"/>
+      <c r="X12" s="21">
+        <v>0.16</v>
+      </c>
       <c r="Y12" s="21"/>
       <c r="Z12" s="21"/>
       <c r="AA12" s="25"/>
@@ -15661,18 +15955,18 @@
       <c r="B13" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G13" s="50"/>
-      <c r="L13" s="50"/>
-      <c r="Q13" s="50"/>
-      <c r="V13" s="50"/>
-      <c r="AA13" s="50"/>
+      <c r="G13" s="49"/>
+      <c r="L13" s="49"/>
+      <c r="Q13" s="49"/>
+      <c r="V13" s="49"/>
+      <c r="AA13" s="49"/>
     </row>
     <row r="14" spans="2:27" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G14" s="53"/>
-      <c r="L14" s="53">
+      <c r="G14" s="52"/>
+      <c r="L14" s="52">
         <f>SUM(H14:K14)</f>
         <v>0</v>
       </c>
@@ -15688,7 +15982,7 @@
       <c r="P14" s="10">
         <v>8411</v>
       </c>
-      <c r="Q14" s="53">
+      <c r="Q14" s="52">
         <f>SUM(M14:P14)</f>
         <v>33006</v>
       </c>
@@ -15711,9 +16005,12 @@
       <c r="W14" s="10">
         <v>8180</v>
       </c>
+      <c r="X14" s="10">
+        <v>8815</v>
+      </c>
       <c r="AA14" s="26">
         <f>SUM(W14:Z14)</f>
-        <v>8180</v>
+        <v>16995</v>
       </c>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.25">
@@ -15787,7 +16084,7 @@
       </c>
       <c r="X15" s="20">
         <f t="shared" ref="X15" si="16">(X14-S14)/S14</f>
-        <v>-1</v>
+        <v>0.13551462063635192</v>
       </c>
       <c r="Y15" s="20">
         <f t="shared" ref="Y15" si="17">(Y14-T14)/T14</f>
@@ -15799,15 +16096,15 @@
       </c>
       <c r="AA15" s="23">
         <f>(AA14-V14)/V14</f>
-        <v>-0.74079472716902217</v>
+        <v>-0.46146777362317004</v>
       </c>
     </row>
     <row r="16" spans="2:27" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="G16" s="51"/>
-      <c r="L16" s="51"/>
+      <c r="G16" s="50"/>
+      <c r="L16" s="50"/>
       <c r="M16" s="20">
         <v>2.3E-2</v>
       </c>
@@ -15820,7 +16117,7 @@
       <c r="P16" s="20">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="Q16" s="51"/>
+      <c r="Q16" s="50"/>
       <c r="R16" s="20">
         <v>0.03</v>
       </c>
@@ -15837,15 +16134,18 @@
       <c r="W16" s="20">
         <v>4.1000000000000002E-2</v>
       </c>
+      <c r="X16" s="20">
+        <v>3.7999999999999999E-2</v>
+      </c>
       <c r="AA16" s="23"/>
     </row>
-    <row r="17" spans="2:27" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:28" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="G17" s="51"/>
-      <c r="L17" s="51"/>
-      <c r="Q17" s="51"/>
+      <c r="G17" s="50"/>
+      <c r="L17" s="50"/>
+      <c r="Q17" s="50"/>
       <c r="R17" s="20">
         <v>0.42299999999999999</v>
       </c>
@@ -15853,14 +16153,17 @@
       <c r="W17" s="20">
         <v>0.42499999999999999</v>
       </c>
+      <c r="X17" s="20">
+        <v>0.39900000000000002</v>
+      </c>
       <c r="AA17" s="23"/>
     </row>
-    <row r="18" spans="2:27" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:28" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G18" s="53"/>
-      <c r="L18" s="53">
+      <c r="G18" s="52"/>
+      <c r="L18" s="52">
         <f>SUM(H18:K18)</f>
         <v>0</v>
       </c>
@@ -15876,7 +16179,7 @@
       <c r="P18" s="10">
         <v>1221</v>
       </c>
-      <c r="Q18" s="53">
+      <c r="Q18" s="52">
         <f>SUM(M18:P18)</f>
         <v>5045</v>
       </c>
@@ -15899,17 +16202,21 @@
       <c r="W18" s="10">
         <v>1262</v>
       </c>
+      <c r="X18" s="10">
+        <v>1131</v>
+      </c>
       <c r="AA18" s="26">
         <f>SUM(W18:Z18)</f>
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="19" spans="2:27" s="20" customFormat="1" x14ac:dyDescent="0.25">
+        <v>2393</v>
+      </c>
+      <c r="AB18" s="2"/>
+    </row>
+    <row r="19" spans="2:28" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="G19" s="51"/>
-      <c r="L19" s="51" t="e">
+      <c r="G19" s="50"/>
+      <c r="L19" s="50" t="e">
         <f>L18/L14</f>
         <v>#DIV/0!</v>
       </c>
@@ -15925,7 +16232,7 @@
       <c r="P19" s="20">
         <v>0.14499999999999999</v>
       </c>
-      <c r="Q19" s="51">
+      <c r="Q19" s="50">
         <f>Q18/Q14</f>
         <v>0.1528509967884627</v>
       </c>
@@ -15941,19 +16248,22 @@
       <c r="U19" s="20">
         <v>0.126</v>
       </c>
-      <c r="V19" s="59">
+      <c r="V19" s="58">
         <f>V18/V14</f>
         <v>0.13999619747766018</v>
       </c>
       <c r="W19" s="20">
         <v>0.154</v>
       </c>
-      <c r="AA19" s="59">
+      <c r="X19" s="20">
+        <v>0.128</v>
+      </c>
+      <c r="AA19" s="58">
         <f>AA18/AA14</f>
-        <v>0.15427872860635697</v>
-      </c>
-    </row>
-    <row r="20" spans="2:27" s="20" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.14080611944689614</v>
+      </c>
+    </row>
+    <row r="20" spans="2:28" s="20" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="21" t="s">
         <v>146</v>
       </c>
@@ -15996,27 +16306,29 @@
       <c r="W20" s="21">
         <v>0.247</v>
       </c>
-      <c r="X20" s="21"/>
+      <c r="X20" s="21">
+        <v>0.19800000000000001</v>
+      </c>
       <c r="Y20" s="21"/>
       <c r="Z20" s="21"/>
       <c r="AA20" s="25"/>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="G21" s="49"/>
-      <c r="L21" s="49"/>
-      <c r="Q21" s="49"/>
-      <c r="V21" s="49"/>
-      <c r="AA21" s="49"/>
-    </row>
-    <row r="22" spans="2:27" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="54" t="s">
+      <c r="G21" s="48"/>
+      <c r="L21" s="48"/>
+      <c r="Q21" s="48"/>
+      <c r="V21" s="48"/>
+      <c r="AA21" s="48"/>
+    </row>
+    <row r="22" spans="2:28" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="G22" s="53"/>
-      <c r="L22" s="53">
+      <c r="G22" s="52"/>
+      <c r="L22" s="52">
         <f>SUM(H22:K22)</f>
         <v>0</v>
       </c>
@@ -16032,7 +16344,7 @@
       <c r="P22" s="10">
         <v>12061</v>
       </c>
-      <c r="Q22" s="53">
+      <c r="Q22" s="52">
         <f>SUM(M22:P22)</f>
         <v>45886</v>
       </c>
@@ -16055,16 +16367,19 @@
       <c r="W22" s="10">
         <v>10356</v>
       </c>
+      <c r="X22" s="10">
+        <v>10202</v>
+      </c>
       <c r="AA22" s="26">
         <f>SUM(W22:Z22)</f>
-        <v>10356</v>
-      </c>
-    </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B23" s="47" t="s">
+        <v>20558</v>
+      </c>
+    </row>
+    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B23" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="G23" s="50"/>
+      <c r="G23" s="49"/>
       <c r="H23" s="20" t="e">
         <f t="shared" ref="H23" si="18">(H22-C22)/C22</f>
         <v>#DIV/0!</v>
@@ -16131,7 +16446,7 @@
       </c>
       <c r="X23" s="20">
         <f t="shared" ref="X23" si="30">(X22-S22)/S22</f>
-        <v>-1</v>
+        <v>-4.3950894948926997E-2</v>
       </c>
       <c r="Y23" s="20">
         <f t="shared" ref="Y23" si="31">(Y22-T22)/T22</f>
@@ -16143,15 +16458,15 @@
       </c>
       <c r="AA23" s="23">
         <f>(AA22-V22)/V22</f>
-        <v>-0.76213335783356684</v>
-      </c>
-    </row>
-    <row r="24" spans="2:27" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="47" t="s">
+        <v>-0.52780393688127336</v>
+      </c>
+    </row>
+    <row r="24" spans="2:28" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="G24" s="51"/>
-      <c r="L24" s="51"/>
+      <c r="G24" s="50"/>
+      <c r="L24" s="50"/>
       <c r="M24" s="20">
         <v>-0.09</v>
       </c>
@@ -16164,7 +16479,7 @@
       <c r="P24" s="20">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="Q24" s="51"/>
+      <c r="Q24" s="50"/>
       <c r="R24" s="20">
         <v>2.7E-2</v>
       </c>
@@ -16181,15 +16496,18 @@
       <c r="W24" s="20">
         <v>-3.5000000000000003E-2</v>
       </c>
+      <c r="X24" s="20">
+        <v>-5.2999999999999999E-2</v>
+      </c>
       <c r="AA24" s="23"/>
     </row>
-    <row r="25" spans="2:27" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="47" t="s">
+    <row r="25" spans="2:28" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="G25" s="51"/>
-      <c r="L25" s="51"/>
-      <c r="Q25" s="51"/>
+      <c r="G25" s="50"/>
+      <c r="L25" s="50"/>
+      <c r="Q25" s="50"/>
       <c r="R25" s="20">
         <v>0.20499999999999999</v>
       </c>
@@ -16197,14 +16515,17 @@
       <c r="W25" s="20">
         <v>0.20699999999999999</v>
       </c>
+      <c r="X25" s="20">
+        <v>0.19400000000000001</v>
+      </c>
       <c r="AA25" s="23"/>
     </row>
-    <row r="26" spans="2:27" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="54" t="s">
+    <row r="26" spans="2:28" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="G26" s="53"/>
-      <c r="L26" s="53">
+      <c r="G26" s="52"/>
+      <c r="L26" s="52">
         <f>SUM(H26:K26)</f>
         <v>0</v>
       </c>
@@ -16220,7 +16541,7 @@
       <c r="P26" s="10">
         <v>1024</v>
       </c>
-      <c r="Q26" s="53">
+      <c r="Q26" s="52">
         <f>SUM(M26:P26)</f>
         <v>4464</v>
       </c>
@@ -16243,17 +16564,21 @@
       <c r="W26" s="10">
         <v>1112</v>
       </c>
+      <c r="X26" s="10">
+        <v>988</v>
+      </c>
       <c r="AA26" s="26">
         <f>SUM(W26:Z26)</f>
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="27" spans="2:27" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="47" t="s">
+        <v>2100</v>
+      </c>
+      <c r="AB26" s="2"/>
+    </row>
+    <row r="27" spans="2:28" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="G27" s="51"/>
-      <c r="L27" s="51" t="e">
+      <c r="G27" s="50"/>
+      <c r="L27" s="50" t="e">
         <f>L26/L22</f>
         <v>#DIV/0!</v>
       </c>
@@ -16269,7 +16594,7 @@
       <c r="P27" s="20">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="Q27" s="51">
+      <c r="Q27" s="50">
         <f>Q26/Q22</f>
         <v>9.7284574815847971E-2</v>
       </c>
@@ -16285,32 +16610,35 @@
       <c r="U27" s="20">
         <v>0.13200000000000001</v>
       </c>
-      <c r="V27" s="59">
+      <c r="V27" s="58">
         <f>V26/V22</f>
         <v>0.11914004180352344</v>
       </c>
       <c r="W27" s="20">
         <v>0.107</v>
       </c>
-      <c r="AA27" s="59">
+      <c r="X27" s="20">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="AA27" s="58">
         <f>AA26/AA22</f>
-        <v>0.10737736577829278</v>
-      </c>
-    </row>
-    <row r="28" spans="2:27" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="48" t="s">
+        <v>0.10215001459285923</v>
+      </c>
+    </row>
+    <row r="28" spans="2:28" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="47" t="s">
         <v>146</v>
       </c>
       <c r="C28" s="21"/>
       <c r="D28" s="21"/>
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
-      <c r="G28" s="52"/>
+      <c r="G28" s="51"/>
       <c r="H28" s="21"/>
       <c r="I28" s="21"/>
       <c r="J28" s="21"/>
       <c r="K28" s="21"/>
-      <c r="L28" s="52"/>
+      <c r="L28" s="51"/>
       <c r="M28" s="21">
         <v>0.15</v>
       </c>
@@ -16323,7 +16651,7 @@
       <c r="P28" s="21">
         <v>0.114</v>
       </c>
-      <c r="Q28" s="52"/>
+      <c r="Q28" s="51"/>
       <c r="R28" s="21">
         <v>0.14099999999999999</v>
       </c>
@@ -16340,12 +16668,14 @@
       <c r="W28" s="21">
         <v>0.128</v>
       </c>
-      <c r="X28" s="21"/>
+      <c r="X28" s="21">
+        <v>0.111</v>
+      </c>
       <c r="Y28" s="21"/>
       <c r="Z28" s="21"/>
       <c r="AA28" s="25"/>
     </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>134</v>
       </c>
@@ -16355,7 +16685,7 @@
       <c r="V29" s="22"/>
       <c r="AA29" s="22"/>
     </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>51</v>
       </c>
@@ -16413,15 +16743,17 @@
       <c r="W30" s="10">
         <v>8139</v>
       </c>
-      <c r="X30" s="10"/>
+      <c r="X30" s="10">
+        <v>9127</v>
+      </c>
       <c r="Y30" s="10"/>
       <c r="Z30" s="10"/>
       <c r="AA30" s="26">
         <f>SUM(W30:Z30)</f>
-        <v>8139</v>
-      </c>
-    </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.25">
+        <v>17266</v>
+      </c>
+    </row>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B31" s="7" t="s">
         <v>135</v>
       </c>
@@ -16494,7 +16826,7 @@
       </c>
       <c r="X31" s="20">
         <f t="shared" ref="X31" si="44">(X30-S30)/S30</f>
-        <v>-1</v>
+        <v>1.3773186715539265E-2</v>
       </c>
       <c r="Y31" s="20">
         <f t="shared" ref="Y31" si="45">(Y30-T30)/T30</f>
@@ -16506,10 +16838,10 @@
       </c>
       <c r="AA31" s="23">
         <f>(AA30-V30)/V30</f>
-        <v>-0.77331216577540107</v>
-      </c>
-    </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.25">
+        <v>-0.51910650623885923</v>
+      </c>
+    </row>
+    <row r="32" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B32" s="20" t="s">
         <v>130</v>
       </c>
@@ -16566,7 +16898,9 @@
       <c r="W32" s="20">
         <v>1.9E-2</v>
       </c>
-      <c r="X32" s="20"/>
+      <c r="X32" s="20">
+        <v>2.1000000000000001E-2</v>
+      </c>
       <c r="Y32" s="20"/>
       <c r="Z32" s="20"/>
       <c r="AA32" s="23"/>
@@ -16628,7 +16962,9 @@
       <c r="W33" s="20">
         <v>0.313</v>
       </c>
-      <c r="X33" s="20"/>
+      <c r="X33" s="20">
+        <v>0.312</v>
+      </c>
       <c r="Y33" s="20"/>
       <c r="Z33" s="20"/>
       <c r="AA33" s="23"/>
@@ -16704,12 +17040,14 @@
       <c r="W34" s="10">
         <v>1311</v>
       </c>
-      <c r="X34" s="10"/>
+      <c r="X34" s="10">
+        <v>1573</v>
+      </c>
       <c r="Y34" s="10"/>
       <c r="Z34" s="10"/>
       <c r="AA34" s="26">
         <f>SUM(W34:Z34)</f>
-        <v>1311</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="35" spans="2:27" x14ac:dyDescent="0.25">
@@ -16720,7 +17058,7 @@
       <c r="D35" s="20"/>
       <c r="E35" s="20"/>
       <c r="F35" s="20"/>
-      <c r="G35" s="59">
+      <c r="G35" s="58">
         <f>G34/G30</f>
         <v>0.11020656808993742</v>
       </c>
@@ -16736,7 +17074,7 @@
       <c r="K35" s="20">
         <v>0.157</v>
       </c>
-      <c r="L35" s="59">
+      <c r="L35" s="58">
         <f>L34/L30</f>
         <v>0.15926648261188928</v>
       </c>
@@ -16752,7 +17090,7 @@
       <c r="P35" s="20">
         <v>0.183</v>
       </c>
-      <c r="Q35" s="59">
+      <c r="Q35" s="58">
         <f>Q34/Q30</f>
         <v>0.17939422597000027</v>
       </c>
@@ -16768,19 +17106,21 @@
       <c r="U35" s="20">
         <v>0.19500000000000001</v>
       </c>
-      <c r="V35" s="59">
+      <c r="V35" s="58">
         <f>V34/V30</f>
         <v>0.17725044563279857</v>
       </c>
       <c r="W35" s="20">
         <v>0.161</v>
       </c>
-      <c r="X35" s="20"/>
+      <c r="X35" s="20">
+        <v>0.17199999999999999</v>
+      </c>
       <c r="Y35" s="20"/>
       <c r="Z35" s="20"/>
-      <c r="AA35" s="59">
+      <c r="AA35" s="58">
         <f>AA34/AA30</f>
-        <v>0.16107629929966827</v>
+        <v>0.16703347619599213</v>
       </c>
     </row>
     <row r="36" spans="2:27" s="20" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
@@ -16791,12 +17131,12 @@
       <c r="D36" s="21"/>
       <c r="E36" s="21"/>
       <c r="F36" s="21"/>
-      <c r="G36" s="52"/>
+      <c r="G36" s="51"/>
       <c r="H36" s="21"/>
       <c r="I36" s="21"/>
       <c r="J36" s="21"/>
       <c r="K36" s="21"/>
-      <c r="L36" s="52"/>
+      <c r="L36" s="51"/>
       <c r="M36" s="21">
         <v>0.214</v>
       </c>
@@ -16809,7 +17149,7 @@
       <c r="P36" s="21">
         <v>0.28799999999999998</v>
       </c>
-      <c r="Q36" s="52"/>
+      <c r="Q36" s="51"/>
       <c r="R36" s="21">
         <v>0.22</v>
       </c>
@@ -16822,14 +17162,16 @@
       <c r="U36" s="21">
         <v>0.27700000000000002</v>
       </c>
-      <c r="V36" s="52"/>
+      <c r="V36" s="51"/>
       <c r="W36" s="21">
         <v>0.20399999999999999</v>
       </c>
-      <c r="X36" s="21"/>
+      <c r="X36" s="21">
+        <v>0.23499999999999999</v>
+      </c>
       <c r="Y36" s="21"/>
       <c r="Z36" s="21"/>
-      <c r="AA36" s="52"/>
+      <c r="AA36" s="51"/>
     </row>
     <row r="41" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
@@ -17266,7 +17608,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C9AA86-0962-284B-AB06-6FEC823C85AD}">
-  <dimension ref="B7:G18"/>
+  <dimension ref="A3:G18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -17279,7 +17621,22 @@
     <col min="8" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="7" spans="2:7" ht="26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D3" s="10"/>
+    </row>
+    <row r="4" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A4" s="65" t="s">
+        <v>215</v>
+      </c>
+      <c r="D4" s="10"/>
+    </row>
+    <row r="5" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+      <c r="A5" s="66">
+        <f>Modell!AK9</f>
+        <v>18069.179999999989</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="B7" s="30" t="s">
         <v>46</v>
       </c>
@@ -17297,7 +17654,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="B8" s="30" t="s">
         <v>129</v>
       </c>
@@ -17314,30 +17671,30 @@
       </c>
       <c r="G8" s="33">
         <f>F8/Modell!$B$5</f>
-        <v>98.259979529170934</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="26" x14ac:dyDescent="0.3">
+        <v>98.54817421909371</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="B9" s="30" t="s">
         <v>182</v>
       </c>
       <c r="C9" s="29"/>
       <c r="D9" s="32">
-        <v>5050</v>
+        <v>4600</v>
       </c>
       <c r="E9" s="29">
         <v>12</v>
       </c>
       <c r="F9" s="32">
         <f t="shared" ref="F9:F10" si="0">D9*E9</f>
-        <v>60600</v>
+        <v>55200</v>
       </c>
       <c r="G9" s="33">
         <f>F9/Modell!$B$5</f>
-        <v>88.609445825413076</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="26" x14ac:dyDescent="0.3">
+        <v>80.950285965684117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="B10" s="30" t="s">
         <v>181</v>
       </c>
@@ -17354,30 +17711,30 @@
       </c>
       <c r="G10" s="33">
         <f>F10/Modell!$B$5</f>
-        <v>58.561193156894284</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="26" x14ac:dyDescent="0.3">
+        <v>58.732952045754509</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="B11" s="30" t="s">
         <v>134</v>
       </c>
       <c r="C11" s="29"/>
       <c r="D11" s="32">
-        <v>6300</v>
+        <v>5950</v>
       </c>
       <c r="E11" s="29">
         <v>13</v>
       </c>
       <c r="F11" s="32">
         <f t="shared" ref="F11" si="1">D11*E11</f>
-        <v>81900</v>
+        <v>77350</v>
       </c>
       <c r="G11" s="33">
         <f>F11/Modell!$B$5</f>
-        <v>119.75435005117707</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="26" x14ac:dyDescent="0.3">
+        <v>113.43305470010266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="B12" s="31"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
@@ -17385,7 +17742,7 @@
       <c r="F12" s="31"/>
       <c r="G12" s="31"/>
     </row>
-    <row r="13" spans="2:7" ht="26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="B13" s="30" t="s">
         <v>156</v>
       </c>
@@ -17395,18 +17752,18 @@
       <c r="F13" s="28"/>
       <c r="G13" s="36">
         <f>SUM(G8:G11)</f>
-        <v>365.18496856265534</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-    </row>
-    <row r="15" spans="2:7" ht="26" x14ac:dyDescent="0.3">
+        <v>351.664466930635</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+    </row>
+    <row r="15" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="B15" s="29" t="s">
         <v>144</v>
       </c>
@@ -17419,10 +17776,10 @@
       </c>
       <c r="G15" s="33">
         <f>-F15/Modell!$B$5</f>
-        <v>-61.867232051469514</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" ht="26" x14ac:dyDescent="0.3">
+        <v>-62.048687490834432</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="B16" s="29" t="s">
         <v>82</v>
       </c>
@@ -17435,7 +17792,7 @@
       </c>
       <c r="G16" s="33">
         <f>F16/Modell!$B$5</f>
-        <v>15.705512501827753</v>
+        <v>15.751576477489369</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="26" x14ac:dyDescent="0.3">
@@ -17456,7 +17813,7 @@
       <c r="F18" s="30"/>
       <c r="G18" s="36">
         <f>SUM(G13:G16)</f>
-        <v>319.02324901301358</v>
+        <v>305.36735591728996</v>
       </c>
     </row>
   </sheetData>
@@ -17494,15 +17851,15 @@
       </c>
       <c r="D5" s="43">
         <f>Modell!$B$9/Modell!AK9</f>
-        <v>10.208941340376636</v>
+        <v>12.049727768498633</v>
       </c>
       <c r="E5" s="43">
         <f>Modell!$B$9/Modell!AL9</f>
-        <v>9.7228012765491751</v>
+        <v>11.475931208093929</v>
       </c>
       <c r="F5" s="43">
         <f>Modell!$B$9/Modell!AM9</f>
-        <v>9.2598107395706428</v>
+        <v>10.929458293422794</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -17511,15 +17868,15 @@
       </c>
       <c r="D6" s="35">
         <f>Modell!$B$9/Modell!AK11</f>
-        <v>10.744199960558122</v>
+        <v>12.742016660170682</v>
       </c>
       <c r="E6" s="43">
         <f>Modell!$B$9/Modell!AL11</f>
-        <v>10.212174129425911</v>
+        <v>12.108751867474549</v>
       </c>
       <c r="F6" s="43">
         <f>Modell!$B$9/Modell!AM11</f>
-        <v>9.7072671335221798</v>
+        <v>11.507969878462227</v>
       </c>
     </row>
     <row r="7" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -17528,15 +17885,15 @@
       </c>
       <c r="D7" s="35">
         <f>Modell!$B$4/Modell!AK18</f>
-        <v>11.289577971372605</v>
+        <v>13.618078696307126</v>
       </c>
       <c r="E7" s="43">
         <f>Modell!$B$4/Modell!AL18</f>
-        <v>10.730546389179359</v>
+        <v>12.941274544143896</v>
       </c>
       <c r="F7" s="35">
         <f>Modell!$B$4/Modell!AM18</f>
-        <v>10.200010200401042</v>
+        <v>12.299186511778684</v>
       </c>
     </row>
   </sheetData>
@@ -17802,7 +18159,7 @@
     <row r="6" spans="1:225" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <f>AA24</f>
-        <v>-0.22413889381254795</v>
+        <v>-0.29518844566121571</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>53</v>
@@ -19973,7 +20330,7 @@
       </c>
       <c r="AA24" s="16">
         <f>(AA23-Modell!B4)/Modell!B4</f>
-        <v>-0.22413889381254795</v>
+        <v>-0.29518844566121571</v>
       </c>
     </row>
   </sheetData>
